--- a/tables/Flexible CUE/Local_perf_matrix_protection_True_vo_False_CUE_True.xlsx
+++ b/tables/Flexible CUE/Local_perf_matrix_protection_True_vo_False_CUE_True.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -668,10 +668,10 @@
         <v>0.01736455621136393</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2301524983055982</v>
+        <v>0.230173922345163</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2005166087607222</v>
+        <v>0.2039303276315843</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.403789484409526</v>
+        <v>4.404174468294835</v>
       </c>
       <c r="P2" t="n">
-        <v>4.387742447281291</v>
+        <v>4.431424658568242</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9916978405820467</v>
+        <v>0.9919808420851591</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005600915383881509</v>
+        <v>0.00550462654698713</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.9877878725225302</v>
+        <v>0.989012593939857</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.008013969088472978</v>
+        <v>0.007601505006739547</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.9996058439915543</v>
+        <v>0.9996337814991475</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.000130632268585285</v>
+        <v>0.0001259176278805535</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.996836338509993</v>
+        <v>0.9971302898369048</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002373227535879242</v>
+        <v>0.002260285986975398</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9590934496278078</v>
+        <v>0.9580123024268584</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008606278803691214</v>
+        <v>0.008719267721794533</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.7284343020603185</v>
+        <v>0.7265461940978282</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001568181679488971</v>
+        <v>0.00157362376516951</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -772,10 +772,10 @@
         <v>0.02342462405894816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1187964952926874</v>
+        <v>0.1194156710580432</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1403907929281753</v>
+        <v>0.1412911713312739</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -784,16 +784,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.313657841931784</v>
+        <v>4.321674553984673</v>
       </c>
       <c r="P3" t="n">
-        <v>4.323067221038482</v>
+        <v>4.331672379881229</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9889087692566518</v>
+        <v>0.9890493274414625</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006404122630708498</v>
+        <v>0.006363413805213385</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9932613114157544</v>
+        <v>0.9938089452029902</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0052749121994545</v>
+        <v>0.005056032603981899</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>0.9990613298102929</v>
+        <v>0.9985506881791598</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.502401583224268e-05</v>
+        <v>9.322335129396679e-05</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.9700347457933398</v>
+        <v>0.9702088426643016</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.008395681345153092</v>
+        <v>0.008371256538340005</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.8605104815832563</v>
+        <v>0.86011901055974</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.009057759765286491</v>
+        <v>0.009070460956723357</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.3372017767976475</v>
+        <v>0.3364230323123721</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.00332175798744129</v>
+        <v>0.003323708838574652</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -876,10 +876,10 @@
         <v>0.001786449637055907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4340590818808676</v>
+        <v>0.4194869788621236</v>
       </c>
       <c r="L4" t="n">
-        <v>0.218634965933555</v>
+        <v>0.2274530803657387</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.446044591924739</v>
+        <v>4.305760853918062</v>
       </c>
       <c r="P4" t="n">
-        <v>4.429129628934525</v>
+        <v>4.564921173124481</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9507488884412845</v>
+        <v>0.9536209316295791</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0145175084555617</v>
+        <v>0.01408786170356406</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9740127680977293</v>
+        <v>0.9843423537935488</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01419441869078332</v>
+        <v>0.01101795104239198</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.9975712751568483</v>
+        <v>0.9985298065805867</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0006133341803381175</v>
+        <v>0.0004771943002724283</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.3222487182243162</v>
+        <v>0.3113711839625622</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02679430962364581</v>
+        <v>0.02700847069784994</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.9715640987471225</v>
+        <v>0.9653629844485028</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.006994655735588298</v>
+        <v>0.007719747184047252</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.4180319940261502</v>
+        <v>0.3931405180397574</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.003865880230054051</v>
+        <v>0.0039476888140497</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -980,10 +980,10 @@
         <v>0.03029424940398749</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1851828485504524</v>
+        <v>0.1836362466865699</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2252457181040419</v>
+        <v>0.2221862193411329</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.338269228295625</v>
+        <v>4.304261087108948</v>
       </c>
       <c r="P5" t="n">
-        <v>4.405479407606347</v>
+        <v>4.346593411528149</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9972630525612427</v>
+        <v>0.9972858911222</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003096499173623033</v>
+        <v>0.003083552681948773</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.998991075658306</v>
+        <v>0.9990181949649488</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002275081360734</v>
+        <v>0.002244296642787409</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.999999035257473</v>
+        <v>0.9999987889434876</v>
       </c>
       <c r="AD5" t="n">
-        <v>6.052862784477727e-06</v>
+        <v>6.781680446297032e-06</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9965572677870896</v>
+        <v>0.9965148744929723</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002727507170998552</v>
+        <v>0.002744248849540293</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9715276642483411</v>
+        <v>0.9718308028895477</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.005610285848307001</v>
+        <v>0.005580340194535178</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9698789792539597</v>
+        <v>0.9694536755171561</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0008092039258047065</v>
+        <v>0.0008148968121270302</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1084,10 +1084,10 @@
         <v>0.01850467691463906</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1720532088902192</v>
+        <v>0.1696931496494424</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2046292083889516</v>
+        <v>0.2020633708472525</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1096,16 +1096,16 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.423356086505447</v>
+        <v>4.366354518668125</v>
       </c>
       <c r="P6" t="n">
-        <v>4.470166440819003</v>
+        <v>4.383108736724052</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9757575922552905</v>
+        <v>0.9760520083713821</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009412354015277787</v>
+        <v>0.009355024440235398</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9881759081185197</v>
+        <v>0.9891059466813283</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.006272304461362287</v>
+        <v>0.006020575146126068</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.9997048473287546</v>
+        <v>0.9997180534422955</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.58854639480065e-05</v>
+        <v>4.48471827643695e-05</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.9855608618191345</v>
+        <v>0.9866180213500717</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.004928492805350359</v>
+        <v>0.004744644272428088</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.6716927043573255</v>
+        <v>0.6718415671859214</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01861466433409115</v>
+        <v>0.01861044367587232</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.4070870017152558</v>
+        <v>0.4054553102711098</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001814458963926279</v>
+        <v>0.001816953936259278</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1188,10 +1188,10 @@
         <v>0.01739226579276497</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2003712390960208</v>
+        <v>0.2030468160086783</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1569215533283704</v>
+        <v>0.1597185494282334</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.322490428799298</v>
+        <v>4.27650586554834</v>
       </c>
       <c r="P7" t="n">
-        <v>4.317882443252186</v>
+        <v>4.380590881394014</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9895516330396209</v>
+        <v>0.9897531182711853</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006210621814437175</v>
+        <v>0.006150447809433854</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.994759990752045</v>
+        <v>0.9954310588904978</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.005492214144678717</v>
+        <v>0.005128486489318791</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.9958611991095583</v>
+        <v>0.9948359882797434</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0002775519103625067</v>
+        <v>0.0003100277465301282</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9210816594276867</v>
+        <v>0.9208533990654563</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01119913054285779</v>
+        <v>0.01121531481507915</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.9923903757717878</v>
+        <v>0.9924152105846769</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002297127655404453</v>
+        <v>0.002293376132592959</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.3151010643487379</v>
+        <v>0.3138939258353437</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004369067276699516</v>
+        <v>0.004372915835409275</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1292,10 +1292,10 @@
         <v>0.02806021357785015</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1629277668784354</v>
+        <v>0.1640874531430341</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1379637480431914</v>
+        <v>0.1430794454914835</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1304,16 +1304,16 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.395443563473687</v>
+        <v>4.438538840521598</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2792306661915</v>
+        <v>4.409865539855366</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9929788133194221</v>
+        <v>0.9930076741410768</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004514120360724329</v>
+        <v>0.00450483308595234</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.993502908537424</v>
+        <v>0.9934357944339832</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.005378548928005734</v>
+        <v>0.005406257408421359</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9999999896094751</v>
+        <v>0.9999991590059611</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.690765981556741e-07</v>
+        <v>6.019404878017211e-06</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9864868983466553</v>
+        <v>0.9865702423780831</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.005756202336489558</v>
+        <v>0.005738423771090189</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9815805243933564</v>
+        <v>0.9818513664817999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.005746727514829819</v>
+        <v>0.005704320777878968</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.999516307961644</v>
+        <v>0.9994999626470771</v>
       </c>
       <c r="AM8" t="n">
-        <v>8.033849714693148e-05</v>
+        <v>8.168465095646855e-05</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1396,10 +1396,10 @@
         <v>0.03857825619785213</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2032150904583824</v>
+        <v>0.2020811236552771</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1614010781110461</v>
+        <v>0.1615009726569789</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1408,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.324191261447337</v>
+        <v>4.239065410023795</v>
       </c>
       <c r="P9" t="n">
-        <v>4.381819889823304</v>
+        <v>4.366558229667945</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9958613959097616</v>
+        <v>0.995820357114249</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003479273809086868</v>
+        <v>0.003496481662207492</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9965821521673196</v>
+        <v>0.9966083808688867</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004219789452541564</v>
+        <v>0.004203566852493549</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.9996689149221967</v>
+        <v>0.9998247441620277</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0001042071686372987</v>
+        <v>7.581655368627885e-05</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.9987064561931568</v>
+        <v>0.9988237208926457</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001455320321637106</v>
+        <v>0.001387788277997986</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9746831329154121</v>
+        <v>0.9740663353886815</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.006003530017716979</v>
+        <v>0.006076222250240533</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9856865165868591</v>
+        <v>0.9852956626916713</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0007193215007768795</v>
+        <v>0.0007290765007350531</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1500,10 +1500,10 @@
         <v>0.033842442806071</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2213013737149055</v>
+        <v>0.2191421824694482</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1197994201686217</v>
+        <v>0.1215027819228309</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.165105484036478</v>
+        <v>4.12702849534982</v>
       </c>
       <c r="P10" t="n">
-        <v>4.176030717835939</v>
+        <v>4.237101085940126</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9909219062884808</v>
+        <v>0.9909284912375946</v>
       </c>
       <c r="R10" t="n">
-        <v>0.006052400224930136</v>
+        <v>0.006050204721186941</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.9998163182057298</v>
+        <v>0.9998449740607541</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001198792847571142</v>
+        <v>0.001101319356184567</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9999895966226779</v>
+        <v>0.9999906712873906</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.695945791726974e-05</v>
+        <v>2.552906077812141e-05</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9078235256415743</v>
+        <v>0.9076722644710228</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01241420545702967</v>
+        <v>0.01242438710876528</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9699366700719151</v>
+        <v>0.9706491943991797</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002743265725239247</v>
+        <v>0.002710562020625378</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.7903688390352983</v>
+        <v>0.7896840699429435</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.002805643143946528</v>
+        <v>0.002810221784170576</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1604,10 +1604,10 @@
         <v>0.02959337905881725</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1824976994977321</v>
+        <v>0.1802913684560598</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3442039026418102</v>
+        <v>0.3454451373737653</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.094730808965064</v>
+        <v>4.084108994242105</v>
       </c>
       <c r="P11" t="n">
-        <v>4.232687635691097</v>
+        <v>4.259686600344069</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9911618550509542</v>
+        <v>0.9917662493275681</v>
       </c>
       <c r="R11" t="n">
-        <v>0.006993943380844355</v>
+        <v>0.006750569427265237</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.9869388814506904</v>
+        <v>0.9879381491108089</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01428896345066377</v>
+        <v>0.01373148533309165</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.9786517091285843</v>
+        <v>0.97685120556387</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.001029149000182645</v>
+        <v>0.001071669547299549</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9500320341754209</v>
+        <v>0.9495960747069608</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.003962458212150523</v>
+        <v>0.003979706458547583</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.9434010860523809</v>
+        <v>0.9448356481325432</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.002673357997402564</v>
+        <v>0.002639260946079815</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9697636616987892</v>
+        <v>0.9700351307956583</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0007366449153825489</v>
+        <v>0.0007333305720067457</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1708,10 +1708,10 @@
         <v>0.0207241649964606</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1044963800343232</v>
+        <v>0.1045004028531513</v>
       </c>
       <c r="L12" t="n">
-        <v>0.127661721970285</v>
+        <v>0.1276642916850467</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1720,16 +1720,16 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.059116436759205</v>
+        <v>4.089982626528647</v>
       </c>
       <c r="P12" t="n">
-        <v>4.061377368008549</v>
+        <v>4.108452396394811</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9584150299219674</v>
+        <v>0.9584149295163737</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02219374056813975</v>
+        <v>0.02219376736116556</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.7676473559260636</v>
+        <v>0.7676464151403437</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.04764844279102066</v>
+        <v>0.04764853925415615</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.5000000000000011</v>
+        <v>0.5000000000000211</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.00166056575747603</v>
+        <v>0.001660565757475997</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.9944816256647016</v>
+        <v>0.9944841727217379</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.002808983092770152</v>
+        <v>0.002808334761805274</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.02161259099572588</v>
+        <v>0.02161263295731597</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.004297444884855062</v>
+        <v>0.00429744479269953</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9871973189760078</v>
+        <v>0.9871973237432586</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0002288897286725876</v>
+        <v>0.0002288896860574952</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1812,10 +1812,10 @@
         <v>0.05578662037324268</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1317909138787342</v>
+        <v>0.1443570250143755</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2004981980636171</v>
+        <v>0.2183137576282809</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.316000860305166</v>
+        <v>4.284315393262775</v>
       </c>
       <c r="P13" t="n">
-        <v>4.2886787006959</v>
+        <v>4.514764624642196</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9977554992845258</v>
+        <v>0.9977621900357057</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002711144091643486</v>
+        <v>0.00270710017913589</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.8348756862825516</v>
+        <v>0.8344403520257577</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.003203806470746031</v>
+        <v>0.003208026953550153</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9948087795552062</v>
+        <v>0.9976562412529824</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.517797708079526e-05</v>
+        <v>3.707554054935967e-05</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.581246856208413</v>
+        <v>0.5828015878772752</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004627441025237273</v>
+        <v>0.004618842738341346</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.9999961404847796</v>
+        <v>0.9999981652181522</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7.936888068819353e-05</v>
+        <v>5.472378073137877e-05</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.9508398756716107</v>
+        <v>0.951345967101802</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002250462409338885</v>
+        <v>0.002238848461881783</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1916,10 +1916,10 @@
         <v>0.008819171744597891</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1869492898432139</v>
+        <v>0.1882369422267624</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2741706290261194</v>
+        <v>0.2760699035485194</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1928,16 +1928,16 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.329492817556477</v>
+        <v>4.399378232032912</v>
       </c>
       <c r="P14" t="n">
-        <v>4.326739196365456</v>
+        <v>4.358938554688334</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9699465125078917</v>
+        <v>0.9700345595166494</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01032387194531143</v>
+        <v>0.0103087380481273</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.9008775642876619</v>
+        <v>0.9012439821253293</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01565378647858255</v>
+        <v>0.0156248266514631</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.7660424412087493</v>
+        <v>0.7620854194242346</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.002372111653866536</v>
+        <v>0.002392087798763316</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9702619982639273</v>
+        <v>0.9703718260310285</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.007452891412107069</v>
+        <v>0.007439116250331635</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.5623610787148221</v>
+        <v>0.5634268865807381</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01494900238012961</v>
+        <v>0.01493078819044134</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.1724869976652313</v>
+        <v>0.172802592055436</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001795954436698915</v>
+        <v>0.001795611936221911</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2020,10 +2020,10 @@
         <v>0.02024626170970604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1960420645582539</v>
+        <v>0.1874830231703039</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2792991729616273</v>
+        <v>0.2737265099064331</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.259694900513283</v>
+        <v>4.085204214067701</v>
       </c>
       <c r="P15" t="n">
-        <v>4.32659567731145</v>
+        <v>4.241274189635918</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9712742952609386</v>
+        <v>0.9712445023950077</v>
       </c>
       <c r="R15" t="n">
-        <v>0.00895692582655825</v>
+        <v>0.008961569460840967</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9147279795603812</v>
+        <v>0.9145422215504312</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01437899295171563</v>
+        <v>0.0143946461521398</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-0.3674310730420616</v>
+        <v>-0.3452385109333218</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.003059937882951814</v>
+        <v>0.003035005859951621</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9186147393804118</v>
+        <v>0.9185682072038268</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.010446154224258</v>
+        <v>0.01044914010173467</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.6076061642336401</v>
+        <v>0.607386875813883</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.007010679705472117</v>
+        <v>0.007012638383216577</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999998106277576</v>
+        <v>0.9999997189716415</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.61033957194876e-06</v>
+        <v>1.961708065212662e-06</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2124,10 +2124,10 @@
         <v>0.01569855494294647</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5421174973423735</v>
+        <v>0.5161649251798621</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5485039621940153</v>
+        <v>0.5289014976348139</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.551455588325581</v>
+        <v>4.346437810309332</v>
       </c>
       <c r="P16" t="n">
-        <v>4.64273504780356</v>
+        <v>4.497205496280733</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9757252005830671</v>
+        <v>0.9761601107018996</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009476330870915355</v>
+        <v>0.009391057682706113</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9942128773895915</v>
+        <v>0.9940557304405625</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005607840063656768</v>
+        <v>0.005683469384110759</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.9580074322594889</v>
+        <v>0.9590590977589639</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004223567489552747</v>
+        <v>0.004170344451248162</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.9102878943193156</v>
+        <v>0.9097484832765053</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003596372452124203</v>
+        <v>0.003607168184178011</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8407783477616961</v>
+        <v>0.8444101086152463</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01808083834779744</v>
+        <v>0.01787344174117467</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2226,10 +2226,10 @@
         <v>0.07189096045701066</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1754324955076012</v>
+        <v>0.1472285974082657</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2654781907703478</v>
+        <v>0.2359948067231339</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2238,16 +2238,16 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.075120312358837</v>
+        <v>3.853984103588437</v>
       </c>
       <c r="P17" t="n">
-        <v>4.199244266229439</v>
+        <v>4.011967618629121</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9894281156122543</v>
+        <v>0.9898180380649964</v>
       </c>
       <c r="R17" t="n">
-        <v>0.00477280010907736</v>
+        <v>0.004683955689167002</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9675507131731813</v>
+        <v>0.9683230105806354</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.00906222615371963</v>
+        <v>0.00895373564125705</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.6706414472608533</v>
+        <v>0.5709242059875356</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.00177492915937712</v>
+        <v>0.002025879262344993</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9939882065285525</v>
+        <v>0.9940667262164319</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.00209690013827192</v>
+        <v>0.002083161384663532</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>0.1027324698514874</v>
+        <v>0.2212695580093317</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.004874665535054547</v>
+        <v>0.004541271040539759</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9950360058096311</v>
+        <v>0.9950734361635877</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0006814937677951335</v>
+        <v>0.0006789195483155269</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>0.03009288922194302</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2393672981629223</v>
+        <v>0.2424607087442707</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2619826533862505</v>
+        <v>0.2651836289186233</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.246963527162229</v>
+        <v>4.298420190621356</v>
       </c>
       <c r="P18" t="n">
-        <v>4.250728850929033</v>
+        <v>4.300141674142705</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9826182446224555</v>
+        <v>0.9826304224726914</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006818445911916567</v>
+        <v>0.006816056954067184</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9152165076409337</v>
+        <v>0.9152792494398896</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0149529946725015</v>
+        <v>0.01494746086284035</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.9897499981441324</v>
+        <v>0.9890578547182047</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0002788496689964799</v>
+        <v>0.0002881107079800557</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9973251938557485</v>
+        <v>0.9973079279727923</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.00155230677329529</v>
+        <v>0.001557308787083497</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9777183202870661</v>
+        <v>0.9777848320257698</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002511214460882848</v>
+        <v>0.002507463619992367</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.995048314955018</v>
+        <v>0.9950045809964476</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0002652584926734241</v>
+        <v>0.0002664273171593902</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2434,10 +2434,10 @@
         <v>0.01254934055241822</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1872651872905624</v>
+        <v>0.161033465819801</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2369652039641418</v>
+        <v>0.2232994455997759</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.597747250805167</v>
+        <v>3.990866149206148</v>
       </c>
       <c r="P19" t="n">
-        <v>4.654580273629279</v>
+        <v>4.375458080650116</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9868556896403132</v>
+        <v>0.9869099488292812</v>
       </c>
       <c r="R19" t="n">
-        <v>0.008077799172500922</v>
+        <v>0.008061109514708967</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.6242906599571725</v>
+        <v>0.6274750871000984</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.009126666723345816</v>
+        <v>0.00908790663969649</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>-0.0167814312972463</v>
+        <v>0.003989528014871735</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.003004144813477837</v>
+        <v>0.002973301930883142</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7304437190212312</v>
+        <v>0.7305638330194407</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01465393174481852</v>
+        <v>0.01465066649266402</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.8560008921894704</v>
+        <v>0.8587258722118825</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.004377967449063088</v>
+        <v>0.004336346172917609</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9966130663101296</v>
+        <v>0.9963810197870483</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.0001701506686823837</v>
+        <v>0.0001758828188849516</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2538,10 +2538,10 @@
         <v>0.005481236733903614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2655681489740055</v>
+        <v>0.2706740016525256</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2867527403576336</v>
+        <v>0.292740499899429</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.545581196261954</v>
+        <v>4.627752525577289</v>
       </c>
       <c r="P20" t="n">
-        <v>4.509499226600938</v>
+        <v>4.593240864814092</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9734477743280838</v>
+        <v>0.9734668925685214</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009566656290347928</v>
+        <v>0.009563211558973351</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.8684397880780379</v>
+        <v>0.8668274204847926</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.01056648990541221</v>
+        <v>0.01063104279203551</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.8345420782509959</v>
+        <v>0.8317276085052017</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.002775572037550959</v>
+        <v>0.002799078990648457</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9329551879037299</v>
+        <v>0.9346148841799236</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.006909354220955615</v>
+        <v>0.006823297667878534</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7849271182929354</v>
+        <v>0.7854085969175137</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01703042449634398</v>
+        <v>0.01701135100923516</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.4684714032388693</v>
+        <v>0.4660248096489776</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006895792595088596</v>
+        <v>0.0006911644829887301</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2642,10 +2642,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1248690725745343</v>
+        <v>0.1202941340488625</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1391849686632676</v>
+        <v>0.137931315746043</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.25389152450637</v>
+        <v>4.107682434211664</v>
       </c>
       <c r="P21" t="n">
-        <v>4.340556887373432</v>
+        <v>4.121104552990844</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8775282290456505</v>
+        <v>0.8678897471651907</v>
       </c>
       <c r="R21" t="n">
-        <v>0.02277501650379183</v>
+        <v>0.02365423805969597</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9478622042758609</v>
+        <v>0.9532826462626094</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.008969414976336925</v>
+        <v>0.008490375570638316</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9955326288839087</v>
+        <v>0.9946418745541423</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.002206289391927377</v>
+        <v>0.002416255744214073</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>-3.437834220437437</v>
+        <v>-3.873668893466444</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.04614178076741202</v>
+        <v>0.04835449193264897</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>-0.3038157083104938</v>
+        <v>-0.3120718465706824</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.01945834246620811</v>
+        <v>0.01951985317088758</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.534979457748169</v>
+        <v>0.5248689173044851</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0007055082714829284</v>
+        <v>0.0007131366589121639</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2746,10 +2746,10 @@
         <v>0.02704531936448205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2818072516144415</v>
+        <v>0.2818005832925195</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3250550672829111</v>
+        <v>0.3216433438608675</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2758,16 +2758,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.357078932018656</v>
+        <v>4.137156494914622</v>
       </c>
       <c r="P22" t="n">
-        <v>4.394707438164093</v>
+        <v>4.309235793842331</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9817843591927093</v>
+        <v>0.9818126345681508</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006822572520820602</v>
+        <v>0.006817275267719821</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.893680058409403</v>
+        <v>0.8940320756762027</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.009612945508834772</v>
+        <v>0.009597018447656281</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9283213051609481</v>
+        <v>0.930553311445966</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001483934841194792</v>
+        <v>0.001460647965992682</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3421965133825251</v>
+        <v>0.3428678973005703</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01119449143418417</v>
+        <v>0.01118877717423164</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.9566381748498411</v>
+        <v>0.955938824717361</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.002981675143758117</v>
+        <v>0.003005623561871168</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.7807139109676775</v>
+        <v>0.7808382624574699</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001979815624651865</v>
+        <v>0.001979254193838229</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
         <v>0.0237900385797033</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2103762298263011</v>
+        <v>0.208871687187535</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2745467794666898</v>
+        <v>0.2714033361257319</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2862,16 +2862,16 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.105159995358824</v>
+        <v>3.863994820752609</v>
       </c>
       <c r="P23" t="n">
-        <v>4.198017983388694</v>
+        <v>4.107886035032053</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9821942105939481</v>
+        <v>0.9822077574114273</v>
       </c>
       <c r="R23" t="n">
-        <v>0.009990084699123155</v>
+        <v>0.009986283699303411</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.8997687988177058</v>
+        <v>0.8998417840638929</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02219497566609639</v>
+        <v>0.02218689334870085</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-0.6418630859581935</v>
+        <v>-0.5987192848937495</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001223639281273118</v>
+        <v>0.001207455260083879</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9833882392154751</v>
+        <v>0.9834080510051557</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.002170843407783038</v>
+        <v>0.002169548508207122</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.9355197529427949</v>
+        <v>0.9263185838948745</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0004122695001951342</v>
+        <v>0.0004407038478542581</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.9994380828152195</v>
+        <v>0.9994487253649298</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0001104369823978187</v>
+        <v>0.0001093861607215465</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2954,10 +2954,10 @@
         <v>0.01655830938827357</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3675699485021797</v>
+        <v>0.3875416039382416</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4425008213088856</v>
+        <v>0.4583294648523437</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.176595398310353</v>
+        <v>4.305819674281706</v>
       </c>
       <c r="P24" t="n">
-        <v>4.305229542862342</v>
+        <v>4.374016760011923</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9930117879337974</v>
+        <v>0.9930288636682071</v>
       </c>
       <c r="R24" t="n">
-        <v>0.004964433306356851</v>
+        <v>0.004958364286698705</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.9998994639859518</v>
+        <v>0.9998817939976682</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.0008046062455553467</v>
+        <v>0.0008724535878225165</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.9569167365386136</v>
+        <v>0.955596081366228</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003277201839878174</v>
+        <v>0.003327051647853078</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8434868172361002</v>
+        <v>0.8450195515293615</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.009749534855424144</v>
+        <v>0.009701678784436861</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.9921853444736654</v>
+        <v>0.9872147780043223</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.0005972592044761169</v>
+        <v>0.0007639449575686116</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         <v>0.05553965571423582</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2172140991091026</v>
+        <v>0.215848059616466</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2288600004876191</v>
+        <v>0.2284773528280685</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.335750152080124</v>
+        <v>4.310157944037903</v>
       </c>
       <c r="P25" t="n">
-        <v>4.343858134200834</v>
+        <v>4.340625818175276</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9844606436067111</v>
+        <v>0.984507854515332</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0206738044475156</v>
+        <v>0.02064237548974292</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.1784868489677363</v>
+        <v>-0.1747078635040595</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03996827854756024</v>
+        <v>0.03990414511207344</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.5414934749891305</v>
+        <v>0.5431757325751052</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0008591893592865932</v>
+        <v>0.0008576117306741309</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.8917081150836333</v>
+        <v>0.8914663041449947</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.01134453944735743</v>
+        <v>0.01135719830938619</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.6613851571956257</v>
+        <v>0.661272200372327</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.002851680356677807</v>
+        <v>0.00285215595587576</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.979112405224479</v>
+        <v>0.9797649579601903</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.002367461527634041</v>
+        <v>0.002330186967735424</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.9738778607727459</v>
+        <v>0.9702799629899451</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.001009485155863295</v>
+        <v>0.001076763288601591</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.02189032935739443</v>
+        <v>-0.02132222006607809</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003347444676746949</v>
+        <v>0.003346514058875605</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3168,10 +3168,10 @@
         <v>0.05246774739927379</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3294247814180385</v>
+        <v>0.3197948172394026</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3152821057620078</v>
+        <v>0.307729191614642</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.343361074649197</v>
+        <v>4.224153844393832</v>
       </c>
       <c r="P26" t="n">
-        <v>4.388959776362458</v>
+        <v>4.29966176391435</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9811299599040499</v>
+        <v>0.9813081611594732</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02111415666511614</v>
+        <v>0.02101422326656706</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.3125442851664189</v>
+        <v>0.3194873422489407</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04071700359685655</v>
+        <v>0.04051086820879415</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.3346691692462636</v>
+        <v>-0.3167759222675097</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0008098727164863159</v>
+        <v>0.0008044256175139636</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9478603516527522</v>
+        <v>0.9473966963069762</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01232782958756913</v>
+        <v>0.01238252129801991</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.255237910558362</v>
+        <v>-0.2443036383060944</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.003841552743827162</v>
+        <v>0.003824784425081982</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9169856801721336</v>
+        <v>0.9173235934568205</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.003856646938879104</v>
+        <v>0.003848789612945321</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.9819167181042554</v>
+        <v>0.981903816046003</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.001143927637383856</v>
+        <v>0.001144335649310885</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.4708558234012146</v>
+        <v>0.4672117928240014</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.00100799117736772</v>
+        <v>0.001011456063301109</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3280,10 +3280,10 @@
         <v>0.07321928484019485</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2426473726089903</v>
+        <v>0.2439507965539418</v>
       </c>
       <c r="L27" t="n">
-        <v>0.307398751289812</v>
+        <v>0.3066785751360043</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.128901529664978</v>
+        <v>4.149671453558346</v>
       </c>
       <c r="P27" t="n">
-        <v>4.155660369250016</v>
+        <v>4.151144737685096</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9964520342592126</v>
+        <v>0.9964585972545316</v>
       </c>
       <c r="R27" t="n">
-        <v>0.009667581563723408</v>
+        <v>0.009658635921927991</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.9041170421987085</v>
+        <v>0.9043392085180965</v>
       </c>
       <c r="U27" t="n">
-        <v>0.01625518984846173</v>
+        <v>0.01623634682286491</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.7055811351248327</v>
+        <v>0.7029069180802154</v>
       </c>
       <c r="X27" t="n">
-        <v>0.000608071719338092</v>
+        <v>0.0006108270453513888</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.9250324382481839</v>
+        <v>0.9251622015904822</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.01161037276988822</v>
+        <v>0.01160032006669633</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.9445619526742078</v>
+        <v>0.9436921249261397</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.0008609988449865865</v>
+        <v>0.00086772712896629</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.8862508529185191</v>
+        <v>0.8860893034683536</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.009421613264955164</v>
+        <v>0.009428301299323778</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.577053472379077</v>
+        <v>0.5798331579529565</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.003503710906979478</v>
+        <v>0.003492178397757696</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4436342281651862</v>
+        <v>0.4433156051319086</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.004856746569558771</v>
+        <v>0.004858137066522915</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3392,10 +3392,10 @@
         <v>0.02087465183044777</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4028027310904022</v>
+        <v>0.3989356014586465</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3961948048246954</v>
+        <v>0.4105437724275827</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.152089315711887</v>
+        <v>4.114744299841788</v>
       </c>
       <c r="P28" t="n">
-        <v>4.168356604476411</v>
+        <v>4.293035136087989</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9430652991481623</v>
+        <v>0.9447350251236333</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02484804224358994</v>
+        <v>0.02448097123631105</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.6056224084768422</v>
+        <v>0.6190449241646123</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.05145842343915712</v>
+        <v>0.05057515743764571</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.824901186601135</v>
+        <v>0.845679985962686</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.005004706859034984</v>
+        <v>0.004698380335830545</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.503098412960501</v>
+        <v>0.4997008500170632</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01178367209740987</v>
+        <v>0.01182388887831986</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.4040942881838469</v>
+        <v>0.4022427977723326</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01677450722417051</v>
+        <v>0.01680054637075701</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9889585105301313</v>
+        <v>0.9896186095558721</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003637788900959682</v>
+        <v>0.0003527373313012608</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3498,10 +3498,10 @@
         <v>0.03864752444133265</v>
       </c>
       <c r="K29" t="n">
-        <v>0.512131704883432</v>
+        <v>0.5337507387871602</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3338013518955662</v>
+        <v>0.3454522295906396</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.093722495858296</v>
+        <v>4.255427909449321</v>
       </c>
       <c r="P29" t="n">
-        <v>4.104304029444438</v>
+        <v>4.201654647402672</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9483658110096799</v>
+        <v>0.9510114840119204</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01466346976076592</v>
+        <v>0.01428286099957423</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.77566206986804</v>
+        <v>0.7866406000590361</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03086476682239346</v>
+        <v>0.03010007215515761</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.927213008331135</v>
+        <v>0.9290719133346621</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009344714343725158</v>
+        <v>0.009224615380400224</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.5960492644107308</v>
+        <v>0.6458639343134771</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.008983235887299929</v>
+        <v>0.008411117137283838</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9928714174282394</v>
+        <v>0.9914430584326879</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.002193756948084203</v>
+        <v>0.002403511476839721</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.9053142069579798</v>
+        <v>0.905411353343703</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001836423088512983</v>
+        <v>0.001835480773710733</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3604,10 +3604,10 @@
         <v>0.0191674492264043</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4712108421979429</v>
+        <v>0.4912707336485012</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3826452802596559</v>
+        <v>0.4026087684288571</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3616,16 +3616,16 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.182807504896132</v>
+        <v>4.515175522261403</v>
       </c>
       <c r="P30" t="n">
-        <v>4.107852201914656</v>
+        <v>4.313607561377583</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9723957261665733</v>
+        <v>0.9728981023027231</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01369474822455569</v>
+        <v>0.01356955918456474</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.8654923460275059</v>
+        <v>0.867287971057757</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02498143887048781</v>
+        <v>0.02481413236353701</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9926156716809288</v>
+        <v>0.9846077079275032</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0003872468481133878</v>
+        <v>0.0005590929815818638</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>-0.04558767024775601</v>
+        <v>0.002836550550473271</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.0138284246210469</v>
+        <v>0.01350441126879013</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8363903823001664</v>
+        <v>0.8343668855930195</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.008466007012947909</v>
+        <v>0.008518199220361183</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.4748783507204263</v>
+        <v>0.4739234315342599</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.001948907923042655</v>
+        <v>0.001950679135743517</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3710,10 +3710,10 @@
         <v>0.02030227596285282</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5036033975236921</v>
+        <v>0.4902078464552742</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4304956211490192</v>
+        <v>0.4306016586812278</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.35839592105136</v>
+        <v>4.249538389327932</v>
       </c>
       <c r="P31" t="n">
-        <v>4.404017411239503</v>
+        <v>4.410030188172075</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9858232890223656</v>
+        <v>0.9859206503437857</v>
       </c>
       <c r="R31" t="n">
-        <v>0.007775787064515909</v>
+        <v>0.007749040197655582</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9470191990119275</v>
+        <v>0.9485192219064569</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01229409179958901</v>
+        <v>0.01211880347787228</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.9006410868993017</v>
+        <v>0.899301487818288</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.007674051872437552</v>
+        <v>0.007725611082399673</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>-0.009324264556901163</v>
+        <v>-0.03053000177468723</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.009135035430233401</v>
+        <v>0.009230499413846684</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.9719680862886577</v>
+        <v>0.9731950440372746</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002627218280954633</v>
+        <v>0.002569078251395795</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.05750339939584348</v>
+        <v>0.04864669288554757</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.004080462825917504</v>
+        <v>0.00409959019304732</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3816,10 +3816,10 @@
         <v>0.02773752553385222</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4586807473470598</v>
+        <v>0.5003204670714311</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3970710215831935</v>
+        <v>0.4277157292674033</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.175457408489923</v>
+        <v>4.53028971271256</v>
       </c>
       <c r="P32" t="n">
-        <v>4.108392129153427</v>
+        <v>4.425992246404511</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9792069787698368</v>
+        <v>0.9797092855898777</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01388521934223277</v>
+        <v>0.01371647812577785</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.8905977097054126</v>
+        <v>0.9019187053601531</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.009433410599240778</v>
+        <v>0.008931998180194519</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.2263478857507</v>
+        <v>0.227125782583355</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.0174594429321092</v>
+        <v>0.01745066310661357</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.653267241492739</v>
+        <v>-0.5421892580542693</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.01635172288448259</v>
+        <v>0.0157928614398565</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.2378540265935969</v>
+        <v>0.2311239848234773</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01808881656459832</v>
+        <v>0.01816850662788654</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.07916749393971889</v>
+        <v>0.07382372874138743</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004877591713439125</v>
+        <v>0.004891724033596115</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3920,10 +3920,10 @@
         <v>0.02495281852103528</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2751054178962024</v>
+        <v>0.2851358817564152</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3042294682802154</v>
+        <v>0.318877189205591</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.166252496298712</v>
+        <v>4.308512879316226</v>
       </c>
       <c r="P33" t="n">
-        <v>4.145865324787048</v>
+        <v>4.271057230087922</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9657376324354282</v>
+        <v>0.9655580660003291</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005872318287096084</v>
+        <v>0.005887686362091251</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.9331222512501116</v>
+        <v>0.9329657134926262</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01045006212430854</v>
+        <v>0.01046228497280141</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.09038453464474583</v>
+        <v>0.1136216779889698</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.006120543298630392</v>
+        <v>0.006041859472656011</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.8547215110296592</v>
+        <v>0.8419596117641139</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.004546406562272</v>
+        <v>0.004741891982336572</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.7996824906554103</v>
+        <v>0.8087275627461875</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.002123692716123653</v>
+        <v>0.00207519263564663</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.4108863354325747</v>
+        <v>0.41811019654445</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0007588664378608386</v>
+        <v>0.0007541993802418439</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4024,10 +4024,10 @@
         <v>0.008784365836720525</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5165578838213738</v>
+        <v>0.5350531219152354</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4269943795072076</v>
+        <v>0.4496288558276344</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.125711815458049</v>
+        <v>4.263995602912937</v>
       </c>
       <c r="P34" t="n">
-        <v>4.121567441380877</v>
+        <v>4.285493285403806</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8963689749147581</v>
+        <v>0.8874123644329036</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0224490005745028</v>
+        <v>0.02339900894059084</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.8317388427930651</v>
+        <v>0.8163313485894672</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.04910475167357138</v>
+        <v>0.05130374898203999</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9928960382843387</v>
+        <v>0.9926351345987787</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.001993769156175944</v>
+        <v>0.002030051118949896</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.6228066868572515</v>
+        <v>0.6403832964109917</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004728081865882822</v>
+        <v>0.004616607184114195</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.3320590188781217</v>
+        <v>0.3490818289130715</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.009072112940066183</v>
+        <v>0.008955763179533109</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.07709921955381505</v>
+        <v>0.06473814985066573</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.000933899958844064</v>
+        <v>0.0009401333509796495</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4130,10 +4130,10 @@
         <v>0.033117285160876</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3001566209783726</v>
+        <v>0.3019486698931895</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2387610009058003</v>
+        <v>0.24751949465167</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.027064102812506</v>
+        <v>4.049554670774522</v>
       </c>
       <c r="P35" t="n">
-        <v>4.028273149140009</v>
+        <v>4.155419422183499</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.996696331550898</v>
+        <v>0.9968026647702138</v>
       </c>
       <c r="R35" t="n">
-        <v>0.005726011423256976</v>
+        <v>0.005633107882523141</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9845721903497994</v>
+        <v>0.9860265812062683</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.006777922190600907</v>
+        <v>0.006450535663099629</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6256994668594258</v>
+        <v>0.6263632103869095</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.009136797958337366</v>
+        <v>0.009128693265875511</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.7266532779088982</v>
+        <v>0.7259764031024614</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002112801543597493</v>
+        <v>0.002115415838542737</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5263675665208019</v>
+        <v>0.5278624330597163</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002336748267560888</v>
+        <v>0.002333057760814093</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4232,10 +4232,10 @@
         <v>0.02290841461070009</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4200622561347667</v>
+        <v>0.4306133506575378</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3842170973366046</v>
+        <v>0.3952277307226713</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.208803672383319</v>
+        <v>4.307865273041947</v>
       </c>
       <c r="P36" t="n">
-        <v>4.208370513294874</v>
+        <v>4.321519067505179</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9835100219792995</v>
+        <v>0.9835354887150053</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01163616115699152</v>
+        <v>0.01162717237780395</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.8079645586487443</v>
+        <v>0.8084317089137957</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01904943476840007</v>
+        <v>0.01902625059212809</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.3717385458786803</v>
+        <v>0.3717595996132993</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.008130975314783554</v>
+        <v>0.008130839074664459</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.06868358318826084</v>
+        <v>0.06964126973225437</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01346426915943055</v>
+        <v>0.01345734462455408</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.7293098918225451</v>
+        <v>0.728509641823178</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.006095125915584966</v>
+        <v>0.006104128876372306</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.1648704835151593</v>
+        <v>0.1670701935279308</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004041209743356386</v>
+        <v>0.004035884011984705</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4338,10 +4338,10 @@
         <v>0.007462828179086988</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1057540787127461</v>
+        <v>0.1032759135620988</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1082833480351216</v>
+        <v>0.1052974555473489</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.325915956550759</v>
+        <v>4.230764125716685</v>
       </c>
       <c r="P37" t="n">
-        <v>4.363108308494082</v>
+        <v>4.263232513024087</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9931768556422819</v>
+        <v>0.9931562102604981</v>
       </c>
       <c r="R37" t="n">
-        <v>0.005504033253222641</v>
+        <v>0.005512353980038237</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>0.02213131017157455</v>
+        <v>0.02232969103987603</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0004230470303942787</v>
+        <v>0.0004230041163021422</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9983945672884703</v>
+        <v>0.9984068109743827</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.001902329413126887</v>
+        <v>0.00189506155895734</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.5024126061334153</v>
+        <v>-0.5007957506550722</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.007760830944242138</v>
+        <v>0.007756653822795167</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9123580339123846</v>
+        <v>0.9118017575571626</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009634021853115517</v>
+        <v>0.009664547763306183</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.9405286457972025</v>
+        <v>0.940625407252214</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.002187919986795259</v>
+        <v>0.002186139360582258</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9999999828682329</v>
+        <v>0.9999996806026822</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.288418123788941e-07</v>
+        <v>5.563157774895456e-07</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>0.003185097564105027</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1483762115382365</v>
+        <v>0.1416438943560188</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1145173439330902</v>
+        <v>0.1094955221332978</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.296526671931293</v>
+        <v>4.113546643685265</v>
       </c>
       <c r="P38" t="n">
-        <v>4.354332778840533</v>
+        <v>4.195575058726416</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9537566371124399</v>
+        <v>0.9538747494938609</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01206632146546173</v>
+        <v>0.01205090202935683</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.1898619657267673</v>
+        <v>0.1856746702867531</v>
       </c>
       <c r="X38" t="n">
-        <v>0.001179768030053185</v>
+        <v>0.001182812986735585</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.8110566128695375</v>
+        <v>0.8117400695136249</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02096509654714988</v>
+        <v>0.02092714413211252</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.3930104832538854</v>
+        <v>-0.3889791861968517</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01713062726933477</v>
+        <v>0.01710582175510812</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.9655307968817377</v>
+        <v>0.9638846440510584</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.004309627963402</v>
+        <v>0.004411335700999675</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-1.201048055958978</v>
+        <v>-1.16109724143762</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.004900831290951427</v>
+        <v>0.004856150575323175</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.9999971243826041</v>
+        <v>0.9999973457512438</v>
       </c>
       <c r="AM38" t="n">
-        <v>6.796466770352051e-07</v>
+        <v>6.529628274818922e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4554,10 +4554,10 @@
         <v>0.03277409385829239</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1491847814540822</v>
+        <v>0.1514776863482813</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1315190608579613</v>
+        <v>0.1340732886312007</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.198070974628081</v>
+        <v>4.258531293425802</v>
       </c>
       <c r="P39" t="n">
-        <v>4.189041007434728</v>
+        <v>4.266000771504852</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9829561396814041</v>
+        <v>0.9829587365995249</v>
       </c>
       <c r="R39" t="n">
-        <v>0.008738539804861039</v>
+        <v>0.008737874047912922</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.8831099684226863</v>
+        <v>0.8831627197684985</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.01144300007671734</v>
+        <v>0.01144041772745747</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.125328563772693</v>
+        <v>0.1261866791231349</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001391409866112907</v>
+        <v>0.001390727162238847</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.04780206648583341</v>
+        <v>-0.04784161916678453</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.01466174213525816</v>
+        <v>0.0146620188601067</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.7520587042010333</v>
+        <v>0.7521066762451492</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005403376423162519</v>
+        <v>0.005402853671293663</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1201814015724485</v>
+        <v>-0.1202639646824426</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002183794455355543</v>
+        <v>0.002183874932294108</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4658,10 +4658,10 @@
         <v>0.003165060709665684</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2450518885796167</v>
+        <v>0.2425659656922763</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4075334177323975</v>
+        <v>0.3987876566146299</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4670,16 +4670,16 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4.568405641987668</v>
+        <v>4.328296976830683</v>
       </c>
       <c r="P40" t="n">
-        <v>4.622079128455577</v>
+        <v>4.516222119821735</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9926755437677104</v>
+        <v>0.9926179059151392</v>
       </c>
       <c r="R40" t="n">
-        <v>0.005140765085249818</v>
+        <v>0.00516095238751394</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.9755713310170135</v>
+        <v>0.9749198582663106</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.009432169677195439</v>
+        <v>0.009557112442325669</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.9491416343220319</v>
+        <v>0.9529782610715386</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0005130546575546429</v>
+        <v>0.0004933234697556976</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9820419879082634</v>
+        <v>0.9822407656566788</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.003365986978914297</v>
+        <v>0.003347306037122141</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.9908939524440173</v>
+        <v>0.9915343214985948</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.004285402795005661</v>
+        <v>0.004131973972221811</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999993559582013</v>
+        <v>0.9999996564976324</v>
       </c>
       <c r="AM40" t="n">
-        <v>4.879538566895861e-07</v>
+        <v>3.563580675576409e-07</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4762,10 +4762,10 @@
         <v>0.01422966781757511</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2672649319402196</v>
+        <v>0.2579668642380593</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2888215069123369</v>
+        <v>0.2827779486933421</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4774,16 +4774,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.586833780976132</v>
+        <v>4.436658074738552</v>
       </c>
       <c r="P41" t="n">
-        <v>4.61304727947481</v>
+        <v>4.506800454719634</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9934763239901251</v>
+        <v>0.9935662715399209</v>
       </c>
       <c r="R41" t="n">
-        <v>0.006259810673720248</v>
+        <v>0.006216506181144936</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8660037872230628</v>
+        <v>0.8657216065040257</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.0106599086719844</v>
+        <v>0.0106711270439813</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.646956652828012</v>
+        <v>0.6406310632877251</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001481789058232114</v>
+        <v>0.001495004964743306</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.9689663956182989</v>
+        <v>0.9709982038957142</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.00472342442177614</v>
+        <v>0.00456618295428893</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9454319706837282</v>
+        <v>0.9468870582876832</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.007531123964789992</v>
+        <v>0.00743003465383836</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.8995948043769113</v>
+        <v>0.9002451043225806</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001033552226401625</v>
+        <v>0.001030199756548226</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>0.01067227249555984</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3163391884519726</v>
+        <v>0.317014523922711</v>
       </c>
       <c r="L42" t="n">
-        <v>0.407174894376521</v>
+        <v>0.3992774395657734</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -4878,16 +4878,16 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.524889107463629</v>
+        <v>4.517744602412055</v>
       </c>
       <c r="P42" t="n">
-        <v>4.593161240766435</v>
+        <v>4.483499745310579</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9578918948125854</v>
+        <v>0.9576260208619269</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01358883397783133</v>
+        <v>0.01363166696486196</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.8261982532319065</v>
+        <v>0.8251353637313272</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.02287806466390041</v>
+        <v>0.0229479137615669</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.9791431099891025</v>
+        <v>0.9707069539571168</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.0007718895729072464</v>
+        <v>0.0009147715850875558</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.6850600680353142</v>
+        <v>0.6837119960478947</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01637875709589411</v>
+        <v>0.01641377356131514</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.9917263532065946</v>
+        <v>0.9912430412372571</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.002812904462639025</v>
+        <v>0.00289389750923357</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         <v>0.0240059836138475</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1604370972748382</v>
+        <v>0.1593858374334936</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2982113627119158</v>
+        <v>0.2953606878173711</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -4980,16 +4980,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4.103051778684014</v>
+        <v>3.921309732134107</v>
       </c>
       <c r="P43" t="n">
-        <v>4.275452415020345</v>
+        <v>4.231892326870648</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9531841704695202</v>
+        <v>0.9531804648397209</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01322048834498649</v>
+        <v>0.01322101155761209</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.9195844322662858</v>
+        <v>0.9196726141488445</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.02438788777278316</v>
+        <v>0.02437451250350367</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.7465870349261532</v>
+        <v>0.7515166694804631</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.002377375346150541</v>
+        <v>0.002354138279213153</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.7309765873128016</v>
+        <v>0.7300542704882629</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01643708261824782</v>
+        <v>0.01646523486372967</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.9068566948694333</v>
+        <v>0.910083480921537</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.001710842275336603</v>
+        <v>0.001680946510196186</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.9758810459412044</v>
+        <v>0.9754722971342382</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0006171795160928588</v>
+        <v>0.0006223872777695342</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5072,10 +5072,10 @@
         <v>0.02192364384915694</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1778728783246155</v>
+        <v>0.1743546614482898</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3789954072656637</v>
+        <v>0.3607161911403574</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.33244628845221</v>
+        <v>4.252007996567885</v>
       </c>
       <c r="P44" t="n">
-        <v>4.593102175455646</v>
+        <v>4.379876703707501</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9319435325001026</v>
+        <v>0.9322289901765384</v>
       </c>
       <c r="R44" t="n">
-        <v>0.008885591275339017</v>
+        <v>0.00886693672513535</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9114145470133936</v>
+        <v>0.9118343741510551</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.01334680746483308</v>
+        <v>0.01331514308618879</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.7652805407589276</v>
+        <v>0.7629989410251768</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.005373114137091154</v>
+        <v>0.005399165764861191</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.9086325102962264</v>
+        <v>0.9073004518172708</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.01057204818929559</v>
+        <v>0.01064883496157211</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.8417278495763652</v>
+        <v>0.8476536494680851</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.008642656904038181</v>
+        <v>0.008479320456552345</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.7108236323566857</v>
+        <v>0.6941211503297948</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.001138997476144957</v>
+        <v>0.001171429311538728</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5176,10 +5176,10 @@
         <v>0.02487778863857871</v>
       </c>
       <c r="K45" t="n">
-        <v>0.399617491041528</v>
+        <v>0.3961005288343256</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2473413361404831</v>
+        <v>0.2489886367685431</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.249422615389083</v>
+        <v>4.214350986480778</v>
       </c>
       <c r="P45" t="n">
-        <v>4.265284514468885</v>
+        <v>4.320122892021073</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9701727369930268</v>
+        <v>0.9702313440706339</v>
       </c>
       <c r="R45" t="n">
-        <v>0.008434644776220935</v>
+        <v>0.008426354157252566</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9783731783928503</v>
+        <v>0.9784347599200411</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01257838147251187</v>
+        <v>0.01256046048187576</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.9261968972661794</v>
+        <v>0.9263908096369194</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007124885096100127</v>
+        <v>0.007115518876935951</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8721309957354996</v>
+        <v>0.8721738592106956</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008497673186995562</v>
+        <v>0.008496248798279732</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9199584716917025</v>
+        <v>0.9200557691923775</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008609731654165306</v>
+        <v>0.008604497120791905</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9793279731510041</v>
+        <v>0.9793660680563808</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.0006313205641957952</v>
+        <v>0.0006307385896372336</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5280,10 +5280,10 @@
         <v>0.04354702384994095</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4729359869420497</v>
+        <v>0.4197523519087317</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3613876143166579</v>
+        <v>0.3538478146508492</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.220017038479095</v>
+        <v>3.774562388265622</v>
       </c>
       <c r="P46" t="n">
-        <v>4.495836855358798</v>
+        <v>4.469631474021861</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9665267445317528</v>
+        <v>0.9691700565078264</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008723186907028606</v>
+        <v>0.008371678975015451</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9832186455653973</v>
+        <v>0.9852529476931888</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.00998911376145646</v>
+        <v>0.009364100463556499</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9291294401075613</v>
+        <v>0.9337676750333243</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.009881332818604354</v>
+        <v>0.009552512080250805</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9829081762135977</v>
+        <v>0.9846233103721167</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.002140044233702968</v>
+        <v>0.00202983142116043</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8382040096312283</v>
+        <v>0.8483107869021425</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.01332019707833567</v>
+        <v>0.01289745800054248</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9860668030814878</v>
+        <v>0.9862790930877983</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.001019498668720425</v>
+        <v>0.001011702176816321</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5384,10 +5384,10 @@
         <v>0.01548193654302897</v>
       </c>
       <c r="K47" t="n">
-        <v>0.251984504906933</v>
+        <v>0.2493695583752376</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3439320392361471</v>
+        <v>0.334323690586066</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.262041686410713</v>
+        <v>4.220558446554917</v>
       </c>
       <c r="P47" t="n">
-        <v>4.414315573316022</v>
+        <v>4.34135409092813</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9419684170552493</v>
+        <v>0.9415799702410498</v>
       </c>
       <c r="R47" t="n">
-        <v>0.009052995132189677</v>
+        <v>0.009083243677576116</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.933883964156669</v>
+        <v>0.9337982099239828</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01416756260572894</v>
+        <v>0.01417674747859337</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.810896173029635</v>
+        <v>0.812072719846809</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.006794620159821748</v>
+        <v>0.006773450144281096</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.8256260049952657</v>
+        <v>0.8225035807354626</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.01245077240543421</v>
+        <v>0.01256175254053157</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9685601463200485</v>
+        <v>0.9685788529767632</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.002749805806420708</v>
+        <v>0.002748987619929098</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9140451364309301</v>
+        <v>0.9144623201650787</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.000560129939208636</v>
+        <v>0.0005587689846373318</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5488,10 +5488,10 @@
         <v>0.04054047652094685</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1259930651411941</v>
+        <v>0.109062118721277</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4829909521356937</v>
+        <v>0.4819694991065029</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.090716553477905</v>
+        <v>3.575232101365941</v>
       </c>
       <c r="P48" t="n">
-        <v>4.395585492355544</v>
+        <v>4.350282899258956</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9812143299570286</v>
+        <v>0.9799807072945712</v>
       </c>
       <c r="R48" t="n">
-        <v>0.007067105085269524</v>
+        <v>0.007295458123566167</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.9699694946918054</v>
+        <v>0.9670514601319901</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.01267145679418735</v>
+        <v>0.01327282333452833</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.8497517749665638</v>
+        <v>0.8511299313845332</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.006547809298516494</v>
+        <v>0.006517710128062508</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.9883541968936689</v>
+        <v>0.9879783933259402</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.006258134678794291</v>
+        <v>0.006358306232025789</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.8959851579885433</v>
+        <v>0.8971030179730674</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.002665168722003858</v>
+        <v>0.002650808591286444</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9997852655776804</v>
+        <v>0.9997445041281109</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0001134617109012748</v>
+        <v>0.0001237628887575433</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5592,10 +5592,10 @@
         <v>0.02297528417150188</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3561331923175848</v>
+        <v>0.3590159275296237</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4677753213263283</v>
+        <v>0.4629775088466354</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -5604,16 +5604,16 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.312452942874997</v>
+        <v>4.039760162263589</v>
       </c>
       <c r="P49" t="n">
-        <v>4.422424367816371</v>
+        <v>4.387464439778952</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9274202986103939</v>
+        <v>0.9272204229533172</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01276976386294409</v>
+        <v>0.01278733496122558</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9291197632989757</v>
+        <v>0.9269537702078596</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.01795830721269345</v>
+        <v>0.0182306317978539</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.9360008684128864</v>
+        <v>0.9384545262801669</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.002426034172106633</v>
+        <v>0.002379073901348844</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.4421909813955671</v>
+        <v>0.4456852453913365</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01378852649983466</v>
+        <v>0.01374527115471176</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.3886404093522196</v>
+        <v>0.4014699385906918</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01717941954345423</v>
+        <v>0.01699820666149585</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8732121432218598</v>
+        <v>0.8731931914353145</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001300763983356462</v>
+        <v>0.001300861196452567</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5696,10 +5696,10 @@
         <v>0.02365077480082941</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5222632463286973</v>
+        <v>0.509975097271933</v>
       </c>
       <c r="L50" t="n">
-        <v>0.558864380711351</v>
+        <v>0.5505848201746671</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.388186391172322</v>
+        <v>4.291212719785222</v>
       </c>
       <c r="P50" t="n">
-        <v>4.624207671445591</v>
+        <v>4.500481878863585</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9597193127310113</v>
+        <v>0.9643131386676767</v>
       </c>
       <c r="R50" t="n">
-        <v>0.01072704208676341</v>
+        <v>0.01009684583614506</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9769797146358428</v>
+        <v>0.9847225923342044</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.0127643494824429</v>
+        <v>0.01039843948697537</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9364263585488526</v>
+        <v>0.9360197628461002</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005372529332951925</v>
+        <v>0.005389682398801431</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.949144313253234</v>
+        <v>0.9495182886766423</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.002303998394603033</v>
+        <v>0.002295511352826723</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.8187384805901008</v>
+        <v>0.8194325120806389</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.017086368483732</v>
+        <v>0.01705362614871232</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         <v>0.05173441476315732</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5242408860059533</v>
+        <v>0.4767246818589526</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5518822913381483</v>
+        <v>0.5516625159727202</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -5810,16 +5810,16 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4.210145903626906</v>
+        <v>3.852084868275818</v>
       </c>
       <c r="P51" t="n">
-        <v>4.426453653178759</v>
+        <v>4.425021504494057</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.9283579700480439</v>
+        <v>0.928518635689824</v>
       </c>
       <c r="R51" t="n">
-        <v>0.0107497320965611</v>
+        <v>0.01073767156444199</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.9301420016690471</v>
+        <v>0.9298020078864232</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.01562595348684905</v>
+        <v>0.01566393252059432</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.7951343353028146</v>
+        <v>0.7959709183259848</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01445228090470585</v>
+        <v>0.01442274227687904</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-0.8405882887785427</v>
+        <v>-0.8079856495807261</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003403411922600078</v>
+        <v>0.003373134653022638</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.890539712934876</v>
+        <v>0.8918970998225999</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01062239004004227</v>
+        <v>0.01055632191053338</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9952384828488746</v>
+        <v>0.9956288507792258</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0005713774057479274</v>
+        <v>0.0005474547176660709</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5902,10 +5902,10 @@
         <v>0.004631983561397277</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1593376026831239</v>
+        <v>0.1577619308753721</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2352477480477142</v>
+        <v>0.2332576237530504</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.33297137534801</v>
+        <v>4.292754697312242</v>
       </c>
       <c r="P52" t="n">
-        <v>4.404387304977933</v>
+        <v>4.285138203429157</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9431726924890186</v>
+        <v>0.9438578508547878</v>
       </c>
       <c r="R52" t="n">
-        <v>0.0115114970100075</v>
+        <v>0.01144189036378144</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9212031885323204</v>
+        <v>0.9213683409175074</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.01285434277218719</v>
+        <v>0.01284086482256702</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.8500631302283324</v>
+        <v>0.8528322432347442</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.002739222663720225</v>
+        <v>0.002713810080924104</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.7596250133477815</v>
+        <v>0.7649466021748099</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01760536682327913</v>
+        <v>0.01740939618453367</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.3414044449178425</v>
+        <v>0.3437539527154617</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.0133793609951092</v>
+        <v>0.01335547456094254</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.05421815294112897</v>
+        <v>0.05764133052217757</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0009376068104866502</v>
+        <v>0.0009359084779877782</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>0.00319007047444387</v>
       </c>
       <c r="K53" t="n">
-        <v>0.331297244801841</v>
+        <v>0.3306984100273074</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2184691391702042</v>
+        <v>0.2222187220843617</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6018,16 +6018,16 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.395968424017083</v>
+        <v>4.388506524434447</v>
       </c>
       <c r="P53" t="n">
-        <v>4.340674242517582</v>
+        <v>4.433029285114089</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9878832504193947</v>
+        <v>0.987816836719875</v>
       </c>
       <c r="R53" t="n">
-        <v>0.004732668188865793</v>
+        <v>0.004745620692211202</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9849241668188445</v>
+        <v>0.9846901797282983</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.007115984680691062</v>
+        <v>0.007170994494039955</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.9244877951192282</v>
+        <v>0.9248878354650139</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.002820903767059357</v>
+        <v>0.002813421705909762</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9764946329923102</v>
+        <v>0.9762568144864854</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.003785135465830205</v>
+        <v>0.003804235567470246</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.9605361989413794</v>
+        <v>0.9608967543252724</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.005785122295770583</v>
+        <v>0.005758634183792521</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.9892768664341907</v>
+        <v>0.987966082527848</v>
       </c>
       <c r="AM53" t="n">
-        <v>4.586025858959441e-05</v>
+        <v>4.858242130553261e-05</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6110,10 +6110,10 @@
         <v>0.02695043454293275</v>
       </c>
       <c r="K54" t="n">
-        <v>0.18838029624573</v>
+        <v>0.1828418750194339</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4433158994606008</v>
+        <v>0.4220001080464181</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -6122,16 +6122,16 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>4.248018727268365</v>
+        <v>4.170489229158358</v>
       </c>
       <c r="P54" t="n">
-        <v>4.483513146781694</v>
+        <v>4.303014583111808</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9083608318741466</v>
+        <v>0.9067625262141346</v>
       </c>
       <c r="R54" t="n">
-        <v>0.01099238378969048</v>
+        <v>0.01108783010979986</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.8629659697709542</v>
+        <v>0.8595447656427713</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.01907238850542566</v>
+        <v>0.01930900227717032</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.3992814370864877</v>
+        <v>0.4067551151670381</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.004469690278759028</v>
+        <v>0.004441799033481543</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.8146451132608939</v>
+        <v>0.8112952659055621</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.01276787518521222</v>
+        <v>0.01288273300476303</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.6559621678207481</v>
+        <v>0.6639692896586624</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.007515890455301813</v>
+        <v>0.007427913290475918</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8938798367436397</v>
+        <v>0.8854808721867133</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.0009597532641621493</v>
+        <v>0.0009970103321812248</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6214,10 +6214,10 @@
         <v>0.00266683139341308</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1380087468264854</v>
+        <v>0.1383001117129508</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4699118445300672</v>
+        <v>0.469718806022866</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6226,16 +6226,16 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4.345610810250299</v>
+        <v>4.460797912271313</v>
       </c>
       <c r="P55" t="n">
-        <v>4.386110827641003</v>
+        <v>4.390400264149273</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.841180839859498</v>
+        <v>0.8410234317987829</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01607047425866486</v>
+        <v>0.01607843613086387</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.6883519404601299</v>
+        <v>0.6886028526186868</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.02694745835235714</v>
+        <v>0.02693660828251536</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.004015600666432917</v>
+        <v>0.002049653051881539</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.00436966449802699</v>
+        <v>0.004373974955361549</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.490328083173049</v>
+        <v>0.4887791626445642</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.0228682292243871</v>
+        <v>0.02290295175637864</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.8880522571513708</v>
+        <v>0.8868827687464473</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.004778838093914024</v>
+        <v>0.004803734867970931</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.8707829123903331</v>
+        <v>0.8713466335423119</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.0004980297458522144</v>
+        <v>0.0004969422086845115</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6318,10 +6318,10 @@
         <v>0.03893815066809572</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2182594007781727</v>
+        <v>0.2039298221414741</v>
       </c>
       <c r="L56" t="n">
-        <v>0.335541790913484</v>
+        <v>0.3222654196083304</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.242619804626787</v>
+        <v>3.981252851815452</v>
       </c>
       <c r="P56" t="n">
-        <v>4.372697484806177</v>
+        <v>4.305313728523216</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8124689049990117</v>
+        <v>0.8140026743624541</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01270606835282853</v>
+        <v>0.01265400181587147</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.6261173282359895</v>
+        <v>0.6320085494266621</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.02134839635525885</v>
+        <v>0.02117953657030387</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>-0.05774371905414344</v>
+        <v>-0.02810911562099561</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.009013991418768817</v>
+        <v>0.00888682273930924</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.6546224018602105</v>
+        <v>0.6507137560021403</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.01553769722558264</v>
+        <v>0.0156253701047111</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.8770267244106206</v>
+        <v>0.8767529975207164</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.005098441735980837</v>
+        <v>0.005104112906601275</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.8753680333446563</v>
+        <v>0.8724483612498279</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001673515307912398</v>
+        <v>0.001693004009184952</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6422,10 +6422,10 @@
         <v>0.02444228773888892</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3849234920957109</v>
+        <v>0.3806411666965068</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4515835818708642</v>
+        <v>0.446908871038932</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.301673038976071</v>
+        <v>4.256768970266466</v>
       </c>
       <c r="P57" t="n">
-        <v>4.401172320762215</v>
+        <v>4.367295926384822</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.8999657343795482</v>
+        <v>0.9003983522957966</v>
       </c>
       <c r="R57" t="n">
-        <v>0.009617639111789407</v>
+        <v>0.009596819889347217</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.7848222517245842</v>
+        <v>0.7858990746237033</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01755750577520807</v>
+        <v>0.01751351879881869</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.6369852556544864</v>
+        <v>0.6377957646282724</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.008686045664944197</v>
+        <v>0.008676343508065438</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.7509875234641659</v>
+        <v>0.7497121235996479</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.007660706695063084</v>
+        <v>0.007680300061801535</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9452285711474302</v>
+        <v>0.9469764606982166</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.004306806324629269</v>
+        <v>0.004237528805731705</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6904617340249063</v>
+        <v>0.6899976100324631</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.00124358525943944</v>
+        <v>0.001244517230741319</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6526,10 +6526,10 @@
         <v>0.02625641629885448</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1253615278418693</v>
+        <v>0.1189716300414537</v>
       </c>
       <c r="L58" t="n">
-        <v>0.509013344645974</v>
+        <v>0.4893927656651046</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -6538,16 +6538,16 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>4.317748846014766</v>
+        <v>4.137219511845506</v>
       </c>
       <c r="P58" t="n">
-        <v>4.752824031853959</v>
+        <v>4.399918490664566</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.955634005818801</v>
+        <v>0.9543845781816904</v>
       </c>
       <c r="R58" t="n">
-        <v>0.008857177796968095</v>
+        <v>0.008981029054341408</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9790503018877302</v>
+        <v>0.9774854388160339</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.008398216097131917</v>
+        <v>0.008706225352617539</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.9520039599335451</v>
+        <v>0.9615695805706699</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.00201631663551071</v>
+        <v>0.001804237029368015</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.9751265810186747</v>
+        <v>0.9749377991538332</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.00605984842571643</v>
+        <v>0.006082801182041506</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.573950537516027</v>
+        <v>0.5644150435155564</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.01674550464884162</v>
+        <v>0.01693185986705981</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9586443804597866</v>
+        <v>0.955957926644607</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.000720234239484466</v>
+        <v>0.0007432593409593535</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6630,10 +6630,10 @@
         <v>0.02080322163891103</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4698313368793378</v>
+        <v>0.4654669130886756</v>
       </c>
       <c r="L59" t="n">
-        <v>0.516075818012792</v>
+        <v>0.5135266407365338</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.228884151391346</v>
+        <v>4.192052202289072</v>
       </c>
       <c r="P59" t="n">
-        <v>4.398744795083564</v>
+        <v>4.383827840564227</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7983709160949124</v>
+        <v>0.8047445056530412</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01922000481717597</v>
+        <v>0.01891378881081737</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.7634652650741987</v>
+        <v>0.781230944941273</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.03048872505260014</v>
+        <v>0.02932140296772496</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.4532647019856167</v>
+        <v>0.4412019164161227</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02285060587555387</v>
+        <v>0.02310131047756706</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.1460292584628687</v>
+        <v>0.1387715782668283</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.01072074809752247</v>
+        <v>0.01076620816955282</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-0.7811709725098634</v>
+        <v>-0.7744006991037902</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.01655467171269097</v>
+        <v>0.01652317940717141</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.5643374143447497</v>
+        <v>-0.5584973427889075</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.002517694652433166</v>
+        <v>0.002512990659079899</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6734,10 +6734,10 @@
         <v>0.0151609171982884</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3312705578089989</v>
+        <v>0.3195516907355711</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2457567089453432</v>
+        <v>0.2337909910577463</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.180622353107697</v>
+        <v>4.041987989944264</v>
       </c>
       <c r="P60" t="n">
-        <v>4.305866015917143</v>
+        <v>4.211312034823191</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.8851495450092283</v>
+        <v>0.8938767987070141</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02107846123653512</v>
+        <v>0.02026178555644128</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.5811682826861864</v>
+        <v>0.6153863286901591</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.0453404368628236</v>
+        <v>0.04344884916800898</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.440366373384316</v>
+        <v>-1.405634905383364</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.008279440950596427</v>
+        <v>0.008220313021881646</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.6256141297198461</v>
+        <v>0.618216638052747</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.006747956299305848</v>
+        <v>0.006814296643099133</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-9.38569717272434</v>
+        <v>-9.226993784798434</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.007170565834450304</v>
+        <v>0.007115568369428657</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9333603701438665</v>
+        <v>0.9316574957294248</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0005013527011342862</v>
+        <v>0.0005077179470773505</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6838,10 +6838,10 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K61" t="n">
-        <v>0.2919016638915633</v>
+        <v>0.2918937862084307</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2564267803757707</v>
+        <v>0.2592866857253662</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -6850,16 +6850,16 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4.076109010387499</v>
+        <v>3.826202503798687</v>
       </c>
       <c r="P61" t="n">
-        <v>4.186117162931888</v>
+        <v>4.250481613740231</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.9853382331310594</v>
+        <v>0.9854262650018197</v>
       </c>
       <c r="R61" t="n">
-        <v>0.008632927715136298</v>
+        <v>0.008606971874534824</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.975040581224661</v>
+        <v>0.9752119446031777</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.01760733509318497</v>
+        <v>0.01754678782678737</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.4517040819655626</v>
+        <v>0.4549475854479135</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.004013946128335518</v>
+        <v>0.004002056052950329</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.669364675865431</v>
+        <v>0.6691623413986479</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.005826000931596781</v>
+        <v>0.005827783288800277</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.8766077617633488</v>
+        <v>0.8770649536774233</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.002807889072876457</v>
+        <v>0.002802682361596211</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.2115790795741771</v>
+        <v>0.2124452246588369</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.002418848943302878</v>
+        <v>0.00241751992615767</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6944,10 +6944,10 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1508447051269653</v>
+        <v>0.1532581908813461</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2025471648920435</v>
+        <v>0.205888269250832</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -6956,16 +6956,16 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.099154174190237</v>
+        <v>4.148400063035928</v>
       </c>
       <c r="P62" t="n">
-        <v>4.118726539643117</v>
+        <v>4.187206950687719</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.988034483616918</v>
+        <v>0.9879952491638674</v>
       </c>
       <c r="R62" t="n">
-        <v>0.007214122118195001</v>
+        <v>0.007225939848626735</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.9822179261869673</v>
+        <v>0.9821729147992779</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01390889197791779</v>
+        <v>0.01392648449424006</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>0.2217832959259977</v>
+        <v>0.2171056861960092</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.00293675697248994</v>
+        <v>0.002945569699425672</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.7214825149706289</v>
+        <v>0.7197751873727491</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.007065929531747776</v>
+        <v>0.007087553712570922</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.9766579132741288</v>
+        <v>0.9766334051031885</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.002268169817182275</v>
+        <v>0.0022693602443811</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.8473949565263715</v>
+        <v>0.8473824521030451</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.001957044214209076</v>
+        <v>0.001957124392450518</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7050,10 +7050,10 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K63" t="n">
-        <v>0.269759348861875</v>
+        <v>0.2693602879820832</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2758786565549628</v>
+        <v>0.2793775025536183</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -7062,16 +7062,16 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.076109010387499</v>
+        <v>3.977065693514069</v>
       </c>
       <c r="P63" t="n">
-        <v>4.193665355386001</v>
+        <v>4.244548958727303</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9884623194411201</v>
+        <v>0.9884784553519506</v>
       </c>
       <c r="R63" t="n">
-        <v>0.007856218182123549</v>
+        <v>0.007850722641286927</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.976221837705202</v>
+        <v>0.9762472684388346</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.01697965618295741</v>
+        <v>0.01697057388669265</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.930586230487621</v>
+        <v>0.9351969766443148</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.001150448980594496</v>
+        <v>0.001111583733859145</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9885994830537536</v>
+        <v>0.9884700934306769</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.0011874811368537</v>
+        <v>0.001194200754899445</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.8217356196596761</v>
+        <v>0.8222616305817994</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.003765424141262803</v>
+        <v>0.003759864652942834</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.2077777822390513</v>
+        <v>0.210003811879761</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.00205549059328317</v>
+        <v>0.002052600746476849</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7156,10 +7156,10 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1942409677162144</v>
+        <v>0.2066785242826841</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2587788459278033</v>
+        <v>0.2647111967065329</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -7168,16 +7168,16 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>4.099154174190237</v>
+        <v>3.70690274747437</v>
       </c>
       <c r="P64" t="n">
-        <v>4.151133446189498</v>
+        <v>4.231895232607643</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9835792210455478</v>
+        <v>0.9835394022992645</v>
       </c>
       <c r="R64" t="n">
-        <v>0.008585735551919339</v>
+        <v>0.008596139023805634</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9764489757229852</v>
+        <v>0.9764635681404795</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.01620739517551933</v>
+        <v>0.01620237327667081</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.6518756848322415</v>
+        <v>0.6398359905773952</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.003186386819241781</v>
+        <v>0.003241018231091507</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.4305515879161358</v>
+        <v>0.4255190091363108</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.009182583637956191</v>
+        <v>0.009223070556417044</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9660184253521629</v>
+        <v>0.9661375902218116</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.002660448346695223</v>
+        <v>0.002655779487025484</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8300643183016871</v>
+        <v>0.8306508125883827</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002330163037932967</v>
+        <v>0.002326138549123357</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7262,10 +7262,10 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K65" t="n">
-        <v>0.2848721463559863</v>
+        <v>0.2856673816535896</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3352234634579414</v>
+        <v>0.3398983205520008</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -7274,16 +7274,16 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>4.076109010387499</v>
+        <v>3.911375026612862</v>
       </c>
       <c r="P65" t="n">
-        <v>4.212379921819044</v>
+        <v>4.265875734099185</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9787302844479959</v>
+        <v>0.9787530097409418</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01050494123794405</v>
+        <v>0.01049932781855502</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.964513365584206</v>
+        <v>0.9645502345986847</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02153613720108769</v>
+        <v>0.02152494675556764</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.7181571484968812</v>
+        <v>0.7181168119953099</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003594899174799692</v>
+        <v>0.00359515641117737</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.667964138560295</v>
+        <v>0.6683665106236629</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008110499950047409</v>
+        <v>0.008105584173975852</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.9148455575577417</v>
+        <v>0.9151777346320565</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.00251771346475438</v>
+        <v>0.002512798020149233</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.5528063515988806</v>
+        <v>0.5535815122448711</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001910940838930693</v>
+        <v>0.001909283918479396</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7368,10 +7368,10 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2502564140929327</v>
+        <v>0.252410987791241</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2703624992545066</v>
+        <v>0.2761950151118719</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -7380,16 +7380,16 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>4.099154174190237</v>
+        <v>3.951261926227352</v>
       </c>
       <c r="P66" t="n">
-        <v>4.152805292084193</v>
+        <v>4.237208873362007</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9815435923413264</v>
+        <v>0.9814948522944399</v>
       </c>
       <c r="R66" t="n">
-        <v>0.009188976285349832</v>
+        <v>0.009201101500784705</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9707542637742512</v>
+        <v>0.970699643601635</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.01800164135180533</v>
+        <v>0.01801844370020395</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.7299271923115542</v>
+        <v>0.7248711456326986</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.003203576330182584</v>
+        <v>0.003233424438140572</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.6888246911808487</v>
+        <v>0.6872153313053242</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.008522740650959811</v>
+        <v>0.008544751503997802</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.9410918214317338</v>
+        <v>0.9413728331013935</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.003375602854815469</v>
+        <v>0.00336754185387246</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8436537473620959</v>
+        <v>0.8438067066347505</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002188786868425362</v>
+        <v>0.002187715921193056</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.4199481606275527</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3865240626503288</v>
+        <v>0.3946866443520776</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.262792264471607</v>
+        <v>4.396330197414215</v>
       </c>
       <c r="P67" t="n">
-        <v>4.256195267146585</v>
+        <v>4.347009083049031</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8515369365835526</v>
+        <v>0.8548503604283604</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02786898032347026</v>
+        <v>0.02755623317484084</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.8032306402925337</v>
+        <v>0.80378112428995</v>
       </c>
       <c r="X67" t="n">
-        <v>0.000771064358006296</v>
+        <v>0.0007699850337809299</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.5853032470520374</v>
+        <v>0.595704131102072</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.06635513358543516</v>
+        <v>0.06551773306075803</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7648127106625204</v>
+        <v>0.7655115302033604</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.002656859431617373</v>
+        <v>0.002652909289289455</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6418818040155725</v>
+        <v>0.6425545208618427</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01312593446015509</v>
+        <v>0.01311360028112063</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8204561633892353</v>
+        <v>0.8046679413695343</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.008775242345500294</v>
+        <v>0.009152940352235572</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.8376884940850516</v>
+        <v>0.8180787262487923</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.0001075201838215004</v>
+        <v>0.0001138300924851284</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7582,10 +7582,10 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.4285023488478826</v>
       </c>
       <c r="L68" t="n">
-        <v>0.372462219851643</v>
+        <v>0.3889409181159572</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.262792264471607</v>
+        <v>4.480408325582514</v>
       </c>
       <c r="P68" t="n">
-        <v>4.186812683786204</v>
+        <v>4.346259938439426</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.7735329316166938</v>
+        <v>0.7773944471011516</v>
       </c>
       <c r="R68" t="n">
-        <v>0.03174567189841233</v>
+        <v>0.03147385872425638</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.4936834779598284</v>
+        <v>0.4874330963895895</v>
       </c>
       <c r="X68" t="n">
-        <v>0.00116365972005364</v>
+        <v>0.001170820268360175</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.3834972166057897</v>
+        <v>0.3955701583959702</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.07637773415060863</v>
+        <v>0.07562618598838711</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.4776882068514769</v>
+        <v>0.469554711490021</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003857003206000577</v>
+        <v>0.003886918030831972</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.7569274866885075</v>
+        <v>0.7501050205864542</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.007250025423921962</v>
+        <v>0.007351066799483733</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.7174909839973393</v>
+        <v>0.6990502232559257</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01198577982446735</v>
+        <v>0.01237078195200235</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.2963340280777604</v>
+        <v>0.2480682877727682</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.0007455254830615566</v>
+        <v>0.0007706699380659424</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7690,10 +7690,10 @@
         <v>0.04611530568392795</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1547738540766385</v>
+        <v>0.1574541057329026</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2025031954442694</v>
+        <v>0.2051976353952231</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.262919614482086</v>
+        <v>4.332138796392004</v>
       </c>
       <c r="P69" t="n">
-        <v>4.256992567054649</v>
+        <v>4.301408134638223</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.9719546034895027</v>
+        <v>0.971964674427934</v>
       </c>
       <c r="R69" t="n">
-        <v>0.009815159215614109</v>
+        <v>0.009813396774144721</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9656971587970086</v>
+        <v>0.9659052190880125</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01026071843651978</v>
+        <v>0.0102295534510854</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.4366510386648796</v>
+        <v>0.4411317996927842</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.004766440075608007</v>
+        <v>0.004747446593787831</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8488168599107225</v>
+        <v>0.8485263686173259</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01574511563283986</v>
+        <v>0.01576023512306844</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9050013298882867</v>
+        <v>0.9048103366427537</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.0093518373706827</v>
+        <v>0.009361233507072192</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5185568192149187</v>
+        <v>0.5187109619344599</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004280178712644847</v>
+        <v>0.004279493469577684</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7794,10 +7794,10 @@
         <v>0.03389921553245138</v>
       </c>
       <c r="K70" t="n">
-        <v>0.153202753067615</v>
+        <v>0.1548184556465437</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2829461371138142</v>
+        <v>0.2818792756835835</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.3508196972905</v>
+        <v>4.393884558299479</v>
       </c>
       <c r="P70" t="n">
-        <v>4.368878097748527</v>
+        <v>4.357184331136191</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.9633290487570927</v>
+        <v>0.9634331301343807</v>
       </c>
       <c r="R70" t="n">
-        <v>0.009397531928199023</v>
+        <v>0.009384186172923768</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.9213868276056124</v>
+        <v>0.9218597383630527</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01251949645226193</v>
+        <v>0.01248178308088512</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.9263895488967253</v>
+        <v>0.9266093425400458</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.003147169632922407</v>
+        <v>0.00314246754918454</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9390317879240819</v>
+        <v>0.9388867506727477</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.01121200146802888</v>
+        <v>0.01122532965866805</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8157953710477228</v>
+        <v>0.8165577140446746</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.0120209432961576</v>
+        <v>0.0119960427732964</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7687066856381957</v>
+        <v>0.7678154532435362</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.002171061708587313</v>
+        <v>0.002175240515435225</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7898,10 +7898,10 @@
         <v>0.02861063360823382</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3261006684563419</v>
+        <v>0.3259372932035616</v>
       </c>
       <c r="L71" t="n">
-        <v>0.350136524559429</v>
+        <v>0.3494710513158307</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4.438072623193317</v>
+        <v>4.435983776929537</v>
       </c>
       <c r="P71" t="n">
-        <v>4.457128641909661</v>
+        <v>4.438832259590852</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9611305042515533</v>
+        <v>0.9612297414408516</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01076489133871906</v>
+        <v>0.01075114070648084</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9440241059700356</v>
+        <v>0.9443525028410662</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.0140808925876428</v>
+        <v>0.01403952725295853</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.7402077604487627</v>
+        <v>0.7407701143739539</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004514960258675317</v>
+        <v>0.004510071003479276</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9068047700686745</v>
+        <v>0.9068221352270809</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.009736465706338474</v>
+        <v>0.009735558561486977</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.8422984907553334</v>
+        <v>0.8424493369054318</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01627629587451095</v>
+        <v>0.01626850963332324</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9317629233060265</v>
+        <v>0.9318214537722059</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.001020516351982907</v>
+        <v>0.001020078583288297</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -8002,10 +8002,10 @@
         <v>0.03450948851818413</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3263018165925168</v>
+        <v>0.3247916833722452</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4177627411276522</v>
+        <v>0.4124836133381382</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.547889869855799</v>
+        <v>4.528094939538367</v>
       </c>
       <c r="P72" t="n">
-        <v>4.560646051212577</v>
+        <v>4.500901129508024</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9564257444158158</v>
+        <v>0.9568065162032868</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01192050933930236</v>
+        <v>0.01186831162414009</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.874132867017217</v>
+        <v>0.8752494535083658</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01481743398670033</v>
+        <v>0.01475156371906827</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.7955435151964435</v>
+        <v>0.7983015200767887</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.004980617926090328</v>
+        <v>0.004946910977776198</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.9510609888060759</v>
+        <v>0.9507928490029101</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006932623072027246</v>
+        <v>0.006951589258913556</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8432330043974766</v>
+        <v>0.8448082008498964</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.02039542268726629</v>
+        <v>0.02029269727636362</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.8992162206224754</v>
+        <v>0.8996920647228908</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001447508347125764</v>
+        <v>0.001444087145549991</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8106,10 +8106,10 @@
         <v>0.01985208116188355</v>
       </c>
       <c r="K73" t="n">
-        <v>0.07823057899988078</v>
+        <v>0.08004889403840529</v>
       </c>
       <c r="L73" t="n">
-        <v>0.07897309760181233</v>
+        <v>0.08114029233833665</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.248593316158351</v>
+        <v>4.341167164957967</v>
       </c>
       <c r="P73" t="n">
-        <v>4.219470583051419</v>
+        <v>4.328595964617172</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9939675031331556</v>
+        <v>0.99396379112802</v>
       </c>
       <c r="R73" t="n">
-        <v>0.005165361105751143</v>
+        <v>0.005166950074523005</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9488204343271356</v>
+        <v>0.9488331545213385</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007767489263112943</v>
+        <v>0.007766523935344358</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.6123178230645259</v>
+        <v>0.6127159826583171</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001244669200602377</v>
+        <v>0.001244029882727097</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9645209311436876</v>
+        <v>0.9644744443477057</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.006319749855966329</v>
+        <v>0.00632388875759245</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8260423998221404</v>
+        <v>0.8257202694666327</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005099602343430179</v>
+        <v>0.005104321817953664</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>-0.07132944660011598</v>
+        <v>-0.07098117044569197</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.002361462171923441</v>
+        <v>0.002361078299427955</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8210,10 +8210,10 @@
         <v>0.03595872786204279</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08513405677699858</v>
+        <v>0.08447253359755409</v>
       </c>
       <c r="L74" t="n">
-        <v>0.165596761809484</v>
+        <v>0.1625861730063674</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.431244325415121</v>
+        <v>4.398896242437559</v>
       </c>
       <c r="P74" t="n">
-        <v>4.456983300004629</v>
+        <v>4.385988636559583</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9698695865506609</v>
+        <v>0.9699037097953491</v>
       </c>
       <c r="R74" t="n">
-        <v>0.008222765843617412</v>
+        <v>0.008218108308150958</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.8556890014392282</v>
+        <v>0.8562060852926054</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.009075961358886105</v>
+        <v>0.0090596866307125</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8691785473562783</v>
+        <v>0.869576474525089</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.001201951448845736</v>
+        <v>0.001200122034053473</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.8769933176062485</v>
+        <v>0.876850564028685</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01381020105060188</v>
+        <v>0.01381821233874606</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.854648287872009</v>
+        <v>0.8554129943330487</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.0077085956979441</v>
+        <v>0.007688291201432815</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.7051922523621772</v>
+        <v>0.7046206404802793</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.002026703734891284</v>
+        <v>0.002028667602754216</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8314,10 +8314,10 @@
         <v>0.05396179716059933</v>
       </c>
       <c r="K75" t="n">
-        <v>0.210319821056764</v>
+        <v>0.2074205046880389</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2634236320263108</v>
+        <v>0.2623019147692786</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.252039103170227</v>
+        <v>4.197065933067138</v>
       </c>
       <c r="P75" t="n">
-        <v>4.299044240918827</v>
+        <v>4.282679100501563</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9696019120289238</v>
+        <v>0.9696018005531949</v>
       </c>
       <c r="R75" t="n">
-        <v>0.006885532135907475</v>
+        <v>0.006885544761191853</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.8981176638451563</v>
+        <v>0.897979515517643</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.01140568167166028</v>
+        <v>0.0114134118736275</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8464564021054091</v>
+        <v>0.8477274891773257</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002364376622409393</v>
+        <v>0.002354569719791642</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9213426443923648</v>
+        <v>0.9214214556774813</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.007360748371424778</v>
+        <v>0.007357059870722868</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8715144130483571</v>
+        <v>0.8717190818218886</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.006799276671228964</v>
+        <v>0.006793859121008478</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9745507186122653</v>
+        <v>0.9745856468645073</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.0009808837473821448</v>
+        <v>0.0009802104018786931</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8418,10 +8418,10 @@
         <v>0.03136066852465918</v>
       </c>
       <c r="K76" t="n">
-        <v>0.01998426772365844</v>
+        <v>0.02053193225236777</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02450667311167247</v>
+        <v>0.02513713782882519</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>4.249893838573551</v>
+        <v>4.359073588567345</v>
       </c>
       <c r="P76" t="n">
-        <v>4.216642809237026</v>
+        <v>4.318198983664887</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9931713199438743</v>
+        <v>0.9931707686457668</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005185356578337882</v>
+        <v>0.005185565888156932</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.9367594680947009</v>
+        <v>0.93675925131047</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.007154817342219517</v>
+        <v>0.007154829605321983</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.8856600773462358</v>
+        <v>0.8857275559793568</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.00093227609923423</v>
+        <v>0.0009320009634825621</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.955006079167025</v>
+        <v>0.9550001528143828</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.008954420086463181</v>
+        <v>0.008955009780613477</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9887315529800376</v>
+        <v>0.9887224260797791</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.0008921749815623726</v>
+        <v>0.0008925362178492035</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.5683681122286992</v>
+        <v>0.5683726274645649</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001183828118541758</v>
+        <v>0.001183821926602156</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8522,10 +8522,10 @@
         <v>0.02805201336700053</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03972700182767472</v>
+        <v>0.03782537579660925</v>
       </c>
       <c r="L77" t="n">
-        <v>0.08804516698121599</v>
+        <v>0.0810297545649466</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.469822402045478</v>
+        <v>4.268656568147811</v>
       </c>
       <c r="P77" t="n">
-        <v>4.55307111873607</v>
+        <v>4.245264030884003</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9705445854393938</v>
+        <v>0.9704404554184087</v>
       </c>
       <c r="R77" t="n">
-        <v>0.01029178288752789</v>
+        <v>0.010309958460805</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.5346676032385946</v>
+        <v>0.5341118493949091</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.01242830609820438</v>
+        <v>0.01243572554487824</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-0.5717452542310675</v>
+        <v>-0.582295642587052</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.001226016424303441</v>
+        <v>0.00123012437861722</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.900418690646708</v>
+        <v>0.8994691169864605</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01367974076813794</v>
+        <v>0.01374480870856579</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.1665199098083074</v>
+        <v>0.1670451556864152</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01363367037938438</v>
+        <v>0.01362937384140957</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8781589789734061</v>
+        <v>0.8761432611718952</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0007910693898610829</v>
+        <v>0.0007975862080373175</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8626,10 +8626,10 @@
         <v>0.01052672116974796</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02841134719532212</v>
+        <v>0.02723295651487582</v>
       </c>
       <c r="L78" t="n">
-        <v>0.08118741286254531</v>
+        <v>0.07672500489828572</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.592870244659815</v>
+        <v>4.413573948301897</v>
       </c>
       <c r="P78" t="n">
-        <v>4.641336080836021</v>
+        <v>4.378228133504346</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9793835072922771</v>
+        <v>0.9788302541138123</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01042651816742387</v>
+        <v>0.0105654922158259</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.115391647462593</v>
+        <v>0.113949239312316</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.0114018097590613</v>
+        <v>0.01141110164775913</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.7309757485715342</v>
+        <v>0.7001184909678355</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.0006066841172578765</v>
+        <v>0.0006405333600049204</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8390898097169524</v>
+        <v>0.8316565248884472</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01649631478944097</v>
+        <v>0.01687303880176016</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.2176747054823913</v>
+        <v>-0.2331874867252572</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.01162528458276387</v>
+        <v>0.01169910140580508</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-1.714044742363709</v>
+        <v>-1.732284807928274</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.00243237143865109</v>
+        <v>0.002440531274866863</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8730,10 +8730,10 @@
         <v>3.234988232153624e-17</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2899193890845111</v>
+        <v>0.2905655997701949</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3127446858319459</v>
+        <v>0.3193146508064549</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.375531902801428</v>
+        <v>4.384688376048642</v>
       </c>
       <c r="P79" t="n">
-        <v>4.432576077918742</v>
+        <v>4.414698453051978</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9810108722602041</v>
+        <v>0.9815531322839578</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0202704360161466</v>
+        <v>0.01997891499838656</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.9170676741277637</v>
+        <v>0.9196623074491694</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04473029024035887</v>
+        <v>0.04402501071364347</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.3527071299709108</v>
+        <v>0.3516903794273151</v>
       </c>
       <c r="X79" t="n">
-        <v>0.002264327602742231</v>
+        <v>0.002266105277930717</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9942276521231063</v>
+        <v>0.9944839157949258</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.005937655902928306</v>
+        <v>0.005804358405889685</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.5708832177632863</v>
+        <v>0.5717723827826132</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.004951052288711787</v>
+        <v>0.004945920136422913</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.9911652911557122</v>
+        <v>0.9905129846447099</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.003015716966370638</v>
+        <v>0.003125066478163995</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.8676387263675818</v>
+        <v>0.8635593018077488</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.00972203502580646</v>
+        <v>0.009870716514327103</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         <v>7.592549229303372e-17</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1594873656769697</v>
+        <v>0.1624757209231998</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2379926598142801</v>
+        <v>0.2461187518334399</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -8850,58 +8850,58 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.443827784785064</v>
+        <v>4.522041228329741</v>
       </c>
       <c r="P80" t="n">
-        <v>4.462778301728683</v>
+        <v>4.467278865581495</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9950458050695046</v>
+        <v>0.9950344922844104</v>
       </c>
       <c r="R80" t="n">
-        <v>0.009728520625944322</v>
+        <v>0.009739621713846859</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.9834578043093579</v>
+        <v>0.983543339462064</v>
       </c>
       <c r="U80" t="n">
-        <v>0.02042400759812824</v>
+        <v>0.02037113569480754</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.7804146988233094</v>
+        <v>0.7897403724063593</v>
       </c>
       <c r="X80" t="n">
-        <v>0.001253471854430479</v>
+        <v>0.001226565936104548</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.9987612981391422</v>
+        <v>0.998808074989621</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.00225966372002814</v>
+        <v>0.002216587522656439</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.8089427781448492</v>
+        <v>0.8188547743234074</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.003636840723033805</v>
+        <v>0.00354124519466525</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9877841139018675</v>
+        <v>0.9865905088871375</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.00586242248404211</v>
+        <v>0.006142155035295631</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.9635739665804065</v>
+        <v>0.9619852004538377</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.006252755606507725</v>
+        <v>0.006387661091562089</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8946,10 +8946,10 @@
         <v>9.901399624920571e-18</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2784130221473442</v>
+        <v>0.2764885304045394</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2484823804617849</v>
+        <v>0.2568286701518031</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -8958,54 +8958,54 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.554087837697824</v>
+        <v>4.543506980364979</v>
       </c>
       <c r="P81" t="n">
-        <v>4.556615964272195</v>
+        <v>4.588445430399664</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9916243775940839</v>
+        <v>0.9918002331716165</v>
       </c>
       <c r="R81" t="n">
-        <v>0.0124372658982394</v>
+        <v>0.01230600608964529</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9755092543332992</v>
+        <v>0.9763557255443277</v>
       </c>
       <c r="U81" t="n">
-        <v>0.02345246357231253</v>
+        <v>0.02304360710559567</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9810137022332038</v>
+        <v>0.9798635035761157</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.009081262233797387</v>
+        <v>0.009352291342153818</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.7552547526052173</v>
+        <v>0.7584733060188198</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.003004084685337982</v>
+        <v>0.002984266516061312</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9655674177436366</v>
+        <v>0.9655619273180496</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.005953161107730974</v>
+        <v>0.00595363571757831</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.9590002872823877</v>
+        <v>0.95989773350931</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.009822214199284182</v>
+        <v>0.009714119759908293</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         <v>1.336850539002381e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1863539639022372</v>
+        <v>0.1873857992577476</v>
       </c>
       <c r="L82" t="n">
-        <v>0.144614343630289</v>
+        <v>0.1460921444003908</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -9062,54 +9062,54 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>4.554008665274212</v>
+        <v>4.465612453484066</v>
       </c>
       <c r="P82" t="n">
-        <v>4.541162821986655</v>
+        <v>4.594217847754331</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9712742940170933</v>
+        <v>0.9714687721076888</v>
       </c>
       <c r="R82" t="n">
-        <v>0.02286337914685651</v>
+        <v>0.02278585315533167</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.9205866167080384</v>
+        <v>0.9212106949275343</v>
       </c>
       <c r="U82" t="n">
-        <v>0.04399697263503802</v>
+        <v>0.04382375428874774</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.9495710710755466</v>
+        <v>0.949703879837641</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.01503635331525526</v>
+        <v>0.01501654052092727</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>0.2972119048241455</v>
+        <v>0.3185226822350521</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.00246046086577958</v>
+        <v>0.002422869185144003</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.7278742675153239</v>
+        <v>0.727865715427144</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.01876742038577705</v>
+        <v>0.01876771528507156</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9664825783543899</v>
+        <v>0.9670968389740151</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.009673420924708104</v>
+        <v>0.009584370547650798</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9152,10 +9152,10 @@
         <v>0.002282733977536599</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1872142165502269</v>
+        <v>0.1900383461359677</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1772856146487613</v>
+        <v>0.1856317839407446</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9164,54 +9164,54 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.516876761044007</v>
+        <v>4.580927191812872</v>
       </c>
       <c r="P83" t="n">
-        <v>4.496978800745321</v>
+        <v>4.571235328818583</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.9756557465620812</v>
+        <v>0.9757404407581288</v>
       </c>
       <c r="R83" t="n">
-        <v>0.0186801778776956</v>
+        <v>0.01864765519030246</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9246272290043949</v>
+        <v>0.9249197679761967</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03558079340781971</v>
+        <v>0.03551167767854237</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.9588429002158336</v>
+        <v>0.9595537246507585</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.009782693923165123</v>
+        <v>0.009697847508947198</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.2706377311692613</v>
+        <v>0.2748498321819083</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.009545153594210294</v>
+        <v>0.009517551833251826</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.9194893463950172</v>
+        <v>0.9182823089316973</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.01089227453347397</v>
+        <v>0.0109736207374806</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.8753081213351324</v>
+        <v>0.87585213908829</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.01316433310645966</v>
+        <v>0.0131355844042773</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9254,10 +9254,10 @@
         <v>0.001579598306755124</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1659043674747134</v>
+        <v>0.1700871734410854</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2246133380102152</v>
+        <v>0.230632505156051</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9266,54 +9266,54 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.44868884650036</v>
+        <v>4.554043371413063</v>
       </c>
       <c r="P84" t="n">
-        <v>4.427867387048924</v>
+        <v>4.502795030495846</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9931423054468013</v>
+        <v>0.9948887639565135</v>
       </c>
       <c r="R84" t="n">
-        <v>0.009724780627055927</v>
+        <v>0.008395638170334084</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.9859308616308792</v>
+        <v>0.9920505547613314</v>
       </c>
       <c r="U84" t="n">
-        <v>0.01586415409375104</v>
+        <v>0.01192481307821156</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9951750783690448</v>
+        <v>0.9949403542211152</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.004738890957035947</v>
+        <v>0.00485279159118447</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.2545535877646719</v>
+        <v>0.26012084473174</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.007816830767515095</v>
+        <v>0.007787586637965768</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.921557783877419</v>
+        <v>0.9283595202945578</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.01154295585124645</v>
+        <v>0.01103116421793434</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9957730490350364</v>
+        <v>0.9958075410492805</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.002094193299831946</v>
+        <v>0.002085631465824958</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9356,10 +9356,10 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2307899480131057</v>
+        <v>0.234087371719241</v>
       </c>
       <c r="L85" t="n">
-        <v>0.271167086757682</v>
+        <v>0.2801892349008259</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -9368,54 +9368,54 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.429178952661008</v>
+        <v>4.488615918273156</v>
       </c>
       <c r="P85" t="n">
-        <v>4.43994582376336</v>
+        <v>4.486831162584882</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.97985006746092</v>
+        <v>0.9818367647150974</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01774038604421447</v>
+        <v>0.01684313277916491</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9456307928860657</v>
+        <v>0.9556639838304075</v>
       </c>
       <c r="U85" t="n">
-        <v>0.02993496664281876</v>
+        <v>0.02703215146365415</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9958862822495433</v>
+        <v>0.9930839207702232</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.004942661777912991</v>
+        <v>0.006408754386141705</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>-0.1892640510990242</v>
+        <v>-0.17773506303766</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.01704145130355583</v>
+        <v>0.01695864834316122</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.6546605816140657</v>
+        <v>0.6562344056870232</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.01898024103914263</v>
+        <v>0.01893694208448688</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9970373945599537</v>
+        <v>0.9994565910971632</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.00155362131675181</v>
+        <v>0.0006653829039369449</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9458,10 +9458,10 @@
         <v>0.001282293415705915</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1218510305567165</v>
+        <v>0.1246919775437176</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1509599798149005</v>
+        <v>0.1551042893757214</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -9470,54 +9470,54 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.469780948890098</v>
+        <v>4.567691173450372</v>
       </c>
       <c r="P86" t="n">
-        <v>4.396928523311477</v>
+        <v>4.512783918100642</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.9908000537962977</v>
+        <v>0.9909039273174141</v>
       </c>
       <c r="R86" t="n">
-        <v>0.01143967245848712</v>
+        <v>0.01137490837087109</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.9861205437420999</v>
+        <v>0.9863386789774761</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01637592225660886</v>
+        <v>0.01624672726569851</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9966267204910166</v>
+        <v>0.9964264413668207</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.003378422419369597</v>
+        <v>0.003477268628531569</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>-0.4067486938097016</v>
+        <v>-0.3971742526560873</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.0177535630609126</v>
+        <v>0.01769304384414355</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.9866654374177412</v>
+        <v>0.9870512751829403</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.005903818132130146</v>
+        <v>0.005817777186068403</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.9766126777232114</v>
+        <v>0.977272647402363</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.004970099807255247</v>
+        <v>0.004899472054219723</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9560,10 +9560,10 @@
         <v>1.327388309752159e-16</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1823831187847791</v>
+        <v>0.183694725148222</v>
       </c>
       <c r="L87" t="n">
-        <v>0.2641974203227942</v>
+        <v>0.2688474743262207</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -9572,54 +9572,54 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>4.595558295125066</v>
+        <v>4.672692369942369</v>
       </c>
       <c r="P87" t="n">
-        <v>4.55388462327085</v>
+        <v>4.61659166222085</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9452136794123609</v>
+        <v>0.9489765942097669</v>
       </c>
       <c r="R87" t="n">
-        <v>0.02624004179320121</v>
+        <v>0.02532288468306964</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.8753156198577354</v>
+        <v>0.8878441276801524</v>
       </c>
       <c r="U87" t="n">
-        <v>0.04578531538616521</v>
+        <v>0.04342413674544995</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.8495600958043553</v>
+        <v>0.8462759144958198</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.02167810037115321</v>
+        <v>0.02191344498156324</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.6259881646174972</v>
+        <v>0.624274520849071</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.007168519871279942</v>
+        <v>0.007184923430444914</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.3809325784633417</v>
+        <v>0.4004261644671419</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.0277995508953904</v>
+        <v>0.02735836512242576</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9793528642315863</v>
+        <v>0.9840845622868911</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.007229185203187446</v>
+        <v>0.006347003500815207</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9662,10 +9662,10 @@
         <v>1.912261794240524e-16</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2319557577696864</v>
+        <v>0.2274032847723464</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1673527144248157</v>
+        <v>0.1675068427290309</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -9674,54 +9674,54 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.602089508487431</v>
+        <v>4.517087837474207</v>
       </c>
       <c r="P88" t="n">
-        <v>4.56263530668584</v>
+        <v>4.646604940518612</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9907165119540572</v>
+        <v>0.9909630568523573</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01129653511176997</v>
+        <v>0.01114552268937772</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.972588497479963</v>
+        <v>0.9736241675452526</v>
       </c>
       <c r="U88" t="n">
-        <v>0.02086708278530094</v>
+        <v>0.02046908389554157</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9839012237999651</v>
+        <v>0.9848870200707512</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.00717893437999707</v>
+        <v>0.006955664161586903</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>0.5443888025655939</v>
+        <v>0.5478493839436035</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.004210472585961957</v>
+        <v>0.004194451846699765</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.9649687300980558</v>
+        <v>0.9639096713033238</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.005578753371356808</v>
+        <v>0.005662453394593703</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.950720960119347</v>
+        <v>0.9498262460345144</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.01011116789895162</v>
+        <v>0.01020254457992885</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9764,10 +9764,10 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3258478558501788</v>
+        <v>0.3272038829542777</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3107026279895493</v>
+        <v>0.3219674696609041</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -9776,54 +9776,54 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4.568276553466714</v>
+        <v>4.487315914632268</v>
       </c>
       <c r="P89" t="n">
-        <v>4.618073252894472</v>
+        <v>4.608123537931807</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9949378777845769</v>
+        <v>0.9958059891449169</v>
       </c>
       <c r="R89" t="n">
-        <v>0.00841971279347733</v>
+        <v>0.007663827826780576</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9907027641518502</v>
+        <v>0.9944415435805271</v>
       </c>
       <c r="U89" t="n">
-        <v>0.01317708664720602</v>
+        <v>0.01018871889114236</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.995526905119877</v>
+        <v>0.995533289421654</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.005096858342044021</v>
+        <v>0.005093219753805592</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.775589161797302</v>
+        <v>0.7638270589650684</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.004590890701401946</v>
+        <v>0.004709665993263534</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9839373269383456</v>
+        <v>0.9804964205878667</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.003079218911219799</v>
+        <v>0.003393038729608771</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9399829868200529</v>
+        <v>0.9371144262296756</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.01114837986529692</v>
+        <v>0.01141169308650897</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9866,10 +9866,10 @@
         <v>0.03004752976171331</v>
       </c>
       <c r="K90" t="n">
-        <v>0.1998835850923684</v>
+        <v>0.2282474838080587</v>
       </c>
       <c r="L90" t="n">
-        <v>0.3854229449332482</v>
+        <v>0.4815095950712526</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -9878,54 +9878,54 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4.174898420666395</v>
+        <v>4.491846084938333</v>
       </c>
       <c r="P90" t="n">
-        <v>3.535706316825924</v>
+        <v>4.281860044428253</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9842754757335125</v>
+        <v>0.9854607249708324</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01658168059058919</v>
+        <v>0.01594450949846223</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.9664583677841866</v>
+        <v>0.9687393740684985</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02966046690040496</v>
+        <v>0.02863417809017151</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9907752875875886</v>
+        <v>0.9923311350084326</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.01240741987625291</v>
+        <v>0.01131281298188015</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.8186183659345619</v>
+        <v>0.7968267709119459</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.00485225348095126</v>
+        <v>0.005135468464758191</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9954481195900572</v>
+        <v>0.9880354695611064</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.000513884544609314</v>
+        <v>0.0008331399577912225</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9861602482736744</v>
+        <v>0.9875934251901958</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.003856068900644412</v>
+        <v>0.003650955881924697</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>

--- a/tables/Flexible CUE/Local_perf_matrix_protection_True_vo_False_CUE_True.xlsx
+++ b/tables/Flexible CUE/Local_perf_matrix_protection_True_vo_False_CUE_True.xlsx
@@ -653,25 +653,25 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.230173922345163</v>
+        <v>0.1675307491422628</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2039303276315843</v>
+        <v>0.2048496140238626</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.404174468294835</v>
+        <v>4.389847264452648</v>
       </c>
       <c r="P2" t="n">
-        <v>4.431424658568242</v>
+        <v>4.431226008153687</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9919808420851591</v>
+        <v>0.9902217196923657</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00550462654698713</v>
+        <v>0.0060784761752644</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.989012593939857</v>
+        <v>0.9873378392308745</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007601505006739547</v>
+        <v>0.008160295957658209</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.9996337814991475</v>
+        <v>0.9996362738175321</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0001259176278805535</v>
+        <v>0.0001254884270293408</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9971302898369048</v>
+        <v>0.996481263395114</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002260285986975398</v>
+        <v>0.002502866896806431</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9580123024268584</v>
+        <v>0.9467710326029583</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008719267721794533</v>
+        <v>0.009817321261213867</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.7265461940978282</v>
+        <v>0.6490201288851479</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.00157362376516951</v>
+        <v>0.001782789312492061</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -757,25 +757,25 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1194156710580432</v>
+        <v>0.0672899438830301</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1412911713312739</v>
+        <v>0.11466862663517</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -784,16 +784,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.321674553984673</v>
+        <v>4.320004150219157</v>
       </c>
       <c r="P3" t="n">
-        <v>4.331672379881229</v>
+        <v>4.325855031722586</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9890493274414625</v>
+        <v>0.9890090877709611</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006363413805213385</v>
+        <v>0.006375094679283832</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9938089452029902</v>
+        <v>0.9954166559740565</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005056032603981899</v>
+        <v>0.00435029562241384</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>0.9985506881791598</v>
+        <v>0.9990197318377565</v>
       </c>
       <c r="AD3" t="n">
-        <v>9.322335129396679e-05</v>
+        <v>7.666837227273145e-05</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.9702088426643016</v>
+        <v>0.9708450618528435</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.008371256538340005</v>
+        <v>0.008281385954651948</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.86011901055974</v>
+        <v>0.8460122108463636</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.009070460956723357</v>
+        <v>0.009516848431131739</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.3364230323123721</v>
+        <v>0.3043408589799896</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003323708838574652</v>
+        <v>0.003403106723703393</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -861,25 +861,25 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4194869788621236</v>
+        <v>0.3790979175914365</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2274530803657387</v>
+        <v>0.318938560757029</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.305760853918062</v>
+        <v>4.287350971919315</v>
       </c>
       <c r="P4" t="n">
-        <v>4.564921173124481</v>
+        <v>4.555849600042944</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9536209316295791</v>
+        <v>0.9512030366020853</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01408786170356406</v>
+        <v>0.01445041992943422</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9843423537935488</v>
+        <v>0.9800542679859405</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01101795104239198</v>
+        <v>0.0124354810580779</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.9985298065805867</v>
+        <v>0.9963622527897376</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0004771943002724283</v>
+        <v>0.0007506271498789661</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.3113711839625622</v>
+        <v>0.2734628705172097</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02700847069784994</v>
+        <v>0.02774190655732305</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.9653629844485028</v>
+        <v>0.9816567224573727</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.007719747184047252</v>
+        <v>0.005617865198997841</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.3931405180397574</v>
+        <v>0.2882560517512804</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0039476888140497</v>
+        <v>0.004275242283819573</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -965,25 +965,25 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1836362466865699</v>
+        <v>0.1248471298400898</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2221862193411329</v>
+        <v>0.2037895454657308</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.304261087108948</v>
+        <v>4.305018687016936</v>
       </c>
       <c r="P5" t="n">
-        <v>4.346593411528149</v>
+        <v>4.340671886397947</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9972858911222</v>
+        <v>0.996495250442237</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003083552681948773</v>
+        <v>0.003504017243413972</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.9990181949649488</v>
+        <v>0.9983403704372971</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002244296642787409</v>
+        <v>0.002917918876615053</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9999987889434876</v>
+        <v>0.99999954112447</v>
       </c>
       <c r="AD5" t="n">
-        <v>6.781680446297032e-06</v>
+        <v>4.174481750345881e-06</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9965148744929723</v>
+        <v>0.9969587538316632</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002744248849540293</v>
+        <v>0.002563539812088799</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9718308028895477</v>
+        <v>0.9623083935483009</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.005580340194535178</v>
+        <v>0.006454992846722038</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9694536755171561</v>
+        <v>0.9749283640437796</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0008148968121270302</v>
+        <v>0.0007382687332962134</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1069,25 +1069,25 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1696931496494424</v>
+        <v>0.1072256716299761</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2020633708472525</v>
+        <v>0.167983605494081</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1096,16 +1096,16 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.366354518668125</v>
+        <v>4.368954957723821</v>
       </c>
       <c r="P6" t="n">
-        <v>4.383108736724052</v>
+        <v>4.375989516697527</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9760520083713821</v>
+        <v>0.975472027444464</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009355024440235398</v>
+        <v>0.00946762839207882</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9891059466813283</v>
+        <v>0.9912898028199175</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.006020575146126068</v>
+        <v>0.005383407142092903</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.9997180534422955</v>
+        <v>0.9995300187978544</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.48471827643695e-05</v>
+        <v>5.790179295470889e-05</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.9866180213500717</v>
+        <v>0.9866717109524676</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.004744644272428088</v>
+        <v>0.004735116758855954</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.6718415671859214</v>
+        <v>0.6557726639326178</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01861044367587232</v>
+        <v>0.01906064619953975</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.4054553102711098</v>
+        <v>0.3537540558462872</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001816953936259278</v>
+        <v>0.001894307946367164</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1173,25 +1173,25 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2030468160086783</v>
+        <v>0.1333701387526627</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1597185494282334</v>
+        <v>0.162405256057174</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.27650586554834</v>
+        <v>4.248251975604964</v>
       </c>
       <c r="P7" t="n">
-        <v>4.380590881394014</v>
+        <v>4.381618046758974</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9897531182711853</v>
+        <v>0.9900859304576147</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006150447809433854</v>
+        <v>0.006049742032793611</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9954310588904978</v>
+        <v>0.997441511412553</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.005128486489318791</v>
+        <v>0.003837719047050118</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.9948359882797434</v>
+        <v>0.9951377228587773</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0003100277465301282</v>
+        <v>0.0003008339240061167</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9208533990654563</v>
+        <v>0.9156743765920043</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01121531481507915</v>
+        <v>0.01157644239617339</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.9924152105846769</v>
+        <v>0.9984817241541085</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002293376132592959</v>
+        <v>0.001026074432328003</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.3138939258353437</v>
+        <v>0.2486129768560648</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004372915835409275</v>
+        <v>0.004576224603213282</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1277,25 +1277,25 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1640874531430341</v>
+        <v>0.1151420749833156</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1430794454914835</v>
+        <v>0.1535624632239113</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1304,16 +1304,16 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.438538840521598</v>
+        <v>4.414720542971803</v>
       </c>
       <c r="P8" t="n">
-        <v>4.409865539855366</v>
+        <v>4.414487640260068</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9930076741410768</v>
+        <v>0.9947196566145985</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00450483308595234</v>
+        <v>0.003914704250227865</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9934357944339832</v>
+        <v>0.9957709712593213</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.005406257408421359</v>
+        <v>0.004339362703067664</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9999991590059611</v>
+        <v>0.9999958302149348</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.019404878017211e-06</v>
+        <v>1.340336769948622e-05</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9865702423780831</v>
+        <v>0.9878518749662355</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.005738423771090189</v>
+        <v>0.005457743932593084</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9818513664817999</v>
+        <v>0.9872346234587129</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.005704320777878968</v>
+        <v>0.004784083923082309</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9994999626470771</v>
+        <v>0.9991286224894446</v>
       </c>
       <c r="AM8" t="n">
-        <v>8.168465095646855e-05</v>
+        <v>0.0001078306961868389</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1381,25 +1381,25 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2020811236552771</v>
+        <v>0.1394388633541007</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1615009726569789</v>
+        <v>0.1652209154254441</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1408,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.239065410023795</v>
+        <v>4.219037933743781</v>
       </c>
       <c r="P9" t="n">
-        <v>4.366558229667945</v>
+        <v>4.365317878470576</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.995820357114249</v>
+        <v>0.9953507176146675</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003496481662207492</v>
+        <v>0.003687691896784813</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9966083808688867</v>
+        <v>0.998566284492862</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004203566852493549</v>
+        <v>0.002733039521663439</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.9998247441620277</v>
+        <v>0.9998138055175863</v>
       </c>
       <c r="AD9" t="n">
-        <v>7.581655368627885e-05</v>
+        <v>7.814679946406887e-05</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.9988237208926457</v>
+        <v>0.9987654370177346</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001387788277997986</v>
+        <v>0.001421754620609743</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9740663353886815</v>
+        <v>0.9626484911255409</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.006076222250240533</v>
+        <v>0.00729215314882149</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9852956626916713</v>
+        <v>0.9780943980497639</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0007290765007350531</v>
+        <v>0.0008898728732877889</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1485,25 +1485,25 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2191421824694482</v>
+        <v>0.1601968509094092</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1215027819228309</v>
+        <v>0.1312018211755326</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.12702849534982</v>
+        <v>4.10267319021357</v>
       </c>
       <c r="P10" t="n">
-        <v>4.237101085940126</v>
+        <v>4.238136940900282</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9909284912375946</v>
+        <v>0.9903058632248739</v>
       </c>
       <c r="R10" t="n">
-        <v>0.006050204721186941</v>
+        <v>0.006254388858497945</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.9998449740607541</v>
+        <v>0.9989146204000847</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001101319356184567</v>
+        <v>0.002914082977585314</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9999906712873906</v>
+        <v>0.999964011293147</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.552906077812141e-05</v>
+        <v>5.01426290884575e-05</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9076722644710228</v>
+        <v>0.902811016192557</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01242438710876528</v>
+        <v>0.01274727639295332</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9706491943991797</v>
+        <v>0.989165408431551</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002710562020625378</v>
+        <v>0.00164685593236345</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.7896840699429435</v>
+        <v>0.7643396455214284</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.002810221784170576</v>
+        <v>0.00297473151942979</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1589,25 +1589,25 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1802913684560598</v>
+        <v>0.1526494909041163</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3454451373737653</v>
+        <v>0.3607268469615829</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.084108994242105</v>
+        <v>4.071785132257231</v>
       </c>
       <c r="P11" t="n">
-        <v>4.259686600344069</v>
+        <v>4.25866291072809</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9917662493275681</v>
+        <v>0.9948561362865457</v>
       </c>
       <c r="R11" t="n">
-        <v>0.006750569427265237</v>
+        <v>0.00533563704217795</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.9879381491108089</v>
+        <v>0.9923784930122844</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01373148533309165</v>
+        <v>0.01091518160239533</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.97685120556387</v>
+        <v>0.9953689039281897</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.001071669547299549</v>
+        <v>0.000479334398037299</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9495960747069608</v>
+        <v>0.9676683747103003</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.003979706458547583</v>
+        <v>0.003187371088893412</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.9448356481325432</v>
+        <v>0.9761855063814672</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.002639260946079815</v>
+        <v>0.001734098436511033</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9700351307956583</v>
+        <v>0.9780103813074453</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0007333305720067457</v>
+        <v>0.0006282065303963701</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1693,25 +1693,25 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1045004028531513</v>
+        <v>0.08829076404957915</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1276642916850467</v>
+        <v>0.1562879116635941</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1720,16 +1720,16 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.089982626528647</v>
+        <v>4.076006435080762</v>
       </c>
       <c r="P12" t="n">
-        <v>4.108452396394811</v>
+        <v>4.119010382796667</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9584149295163737</v>
+        <v>0.9491960846672365</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02219376736116556</v>
+        <v>0.02453075416536009</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.7676464151403437</v>
+        <v>0.7170249707604057</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.04764853925415615</v>
+        <v>0.05258343576694743</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.5000000000000211</v>
+        <v>0.9994548201123679</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.001660565757475997</v>
+        <v>5.483287138795045e-05</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.9944841727217379</v>
+        <v>0.9813561633341537</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.002808334761805274</v>
+        <v>0.005163107784080083</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.02161263295731597</v>
+        <v>0.1259258830921562</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.00429744479269953</v>
+        <v>0.004061898060195989</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9871973237432586</v>
+        <v>0.99337423351391</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0002288896860574952</v>
+        <v>0.0001646621962864411</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1797,25 +1797,25 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1443570250143755</v>
+        <v>0.1269149850337687</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2183137576282809</v>
+        <v>0.1953879886081414</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.284315393262775</v>
+        <v>4.279020890353953</v>
       </c>
       <c r="P13" t="n">
-        <v>4.514764624642196</v>
+        <v>4.518020440402362</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9977621900357057</v>
+        <v>0.9978145956219875</v>
       </c>
       <c r="R13" t="n">
-        <v>0.00270710017913589</v>
+        <v>0.002675214628464874</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.8344403520257577</v>
+        <v>0.8503007683543569</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.003208026953550153</v>
+        <v>0.00305049659584736</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9976562412529824</v>
+        <v>0.9992656586273637</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.707554054935967e-05</v>
+        <v>2.075295943406628e-05</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.5828015878772752</v>
+        <v>0.5817591647689185</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004618842738341346</v>
+        <v>0.004624609504689172</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.9999981652181522</v>
+        <v>0.9999952407697528</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5.472378073137877e-05</v>
+        <v>8.813577664332713e-05</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.951345967101802</v>
+        <v>0.9506598720332502</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002238848461881783</v>
+        <v>0.002254578760916265</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1901,25 +1901,25 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1882369422267624</v>
+        <v>0.1438330238577966</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2760699035485194</v>
+        <v>0.2259744818263331</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1928,16 +1928,16 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.399378232032912</v>
+        <v>4.392368297887129</v>
       </c>
       <c r="P14" t="n">
-        <v>4.358938554688334</v>
+        <v>4.350267039998489</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9700345595166494</v>
+        <v>0.9668473764354523</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0103087380481273</v>
+        <v>0.01084311645576572</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.9012439821253293</v>
+        <v>0.8853263755131153</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0156248266514631</v>
+        <v>0.01683701863648314</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.7620854194242346</v>
+        <v>0.8999919874169244</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.002392087798763316</v>
+        <v>0.001550900675032002</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9703718260310285</v>
+        <v>0.9593209862580233</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.007439116250331635</v>
+        <v>0.008716740352249314</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.5634268865807381</v>
+        <v>0.563818478452192</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01493078819044134</v>
+        <v>0.0149240905182485</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.172802592055436</v>
+        <v>0.1622528239297816</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001795611936221911</v>
+        <v>0.001807025935615041</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2005,25 +2005,25 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1874830231703039</v>
+        <v>0.1307591005177591</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2737265099064331</v>
+        <v>0.2272711616521533</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.085204214067701</v>
+        <v>4.079261036110907</v>
       </c>
       <c r="P15" t="n">
-        <v>4.241274189635918</v>
+        <v>4.223223841031757</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9712445023950077</v>
+        <v>0.9694304685738983</v>
       </c>
       <c r="R15" t="n">
-        <v>0.008961569460840967</v>
+        <v>0.009239915987418593</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9145422215504312</v>
+        <v>0.9069081310186005</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0143946461521398</v>
+        <v>0.01502384416913792</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-0.3452385109333218</v>
+        <v>-0.2042450790744863</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.003035005859951621</v>
+        <v>0.002871556252226525</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9185682072038268</v>
+        <v>0.9165244550217656</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01044914010173467</v>
+        <v>0.01057945228498054</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.607386875813883</v>
+        <v>0.5805784843102495</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.007012638383216577</v>
+        <v>0.007248103627623186</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999997189716415</v>
+        <v>0.9999990127455193</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.961708065212662e-06</v>
+        <v>3.676832638433941e-06</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2109,25 +2109,25 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5161649251798621</v>
+        <v>0.5129655543643412</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5289014976348139</v>
+        <v>0.5570648930193127</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.346437810309332</v>
+        <v>4.407580888704488</v>
       </c>
       <c r="P16" t="n">
-        <v>4.497205496280733</v>
+        <v>4.533248426339919</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9761601107018996</v>
+        <v>0.9772531111522044</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009391057682706113</v>
+        <v>0.009173253465776601</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9940557304405625</v>
+        <v>0.9942457559178858</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005683469384110759</v>
+        <v>0.005591887390113188</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.9590590977589639</v>
+        <v>0.9592775241567592</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004170344451248162</v>
+        <v>0.00415920483919991</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.9097484832765053</v>
+        <v>0.903678497459134</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003607168184178011</v>
+        <v>0.003726496878166753</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8444101086152463</v>
+        <v>0.8528218055756928</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01787344174117467</v>
+        <v>0.01738358060098302</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2211,25 +2211,25 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1472285974082657</v>
+        <v>0.1557936046085961</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2359948067231339</v>
+        <v>0.2186325185453777</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2238,16 +2238,16 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.853984103588437</v>
+        <v>3.843478583732289</v>
       </c>
       <c r="P17" t="n">
-        <v>4.011967618629121</v>
+        <v>4.003719165031207</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9898180380649964</v>
+        <v>0.9887922887941479</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004683955689167002</v>
+        <v>0.004914230343642085</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9683230105806354</v>
+        <v>0.9645849319296694</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.00895373564125705</v>
+        <v>0.009467304770567786</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.5709242059875356</v>
+        <v>0.7759965842772603</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.002025879262344993</v>
+        <v>0.001463773470828168</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9940667262164319</v>
+        <v>0.9936973707271253</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.002083161384663532</v>
+        <v>0.002147022541762534</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>0.2212695580093317</v>
+        <v>0.09993223714009614</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.004541271040539759</v>
+        <v>0.004882266102609818</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9950734361635877</v>
+        <v>0.9943397171283372</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0006789195483155269</v>
+        <v>0.0007277216965418811</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2315,25 +2315,25 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2424607087442707</v>
+        <v>0.1816593812827441</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2651836289186233</v>
+        <v>0.2297352108863215</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.298420190621356</v>
+        <v>4.289171463703494</v>
       </c>
       <c r="P18" t="n">
-        <v>4.300141674142705</v>
+        <v>4.290050057097835</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9826304224726914</v>
+        <v>0.9831534514354511</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006816056954067184</v>
+        <v>0.006712650750531434</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9152792494398896</v>
+        <v>0.9176001397679907</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01494746086284035</v>
+        <v>0.01474129936032057</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.9890578547182047</v>
+        <v>0.9945932509422459</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0002881107079800557</v>
+        <v>0.0002025238934296109</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9973079279727923</v>
+        <v>0.9966815848087611</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.001557308787083497</v>
+        <v>0.001729007014834954</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9777848320257698</v>
+        <v>0.9827759611838005</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002507463619992367</v>
+        <v>0.002207889531238888</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.9950045809964476</v>
+        <v>0.9938608021566676</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0002664273171593902</v>
+        <v>0.0002953579109332178</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2419,25 +2419,25 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.161033465819801</v>
+        <v>0.107691775349662</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2232994455997759</v>
+        <v>0.175768878345028</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.990866149206148</v>
+        <v>3.99750997059567</v>
       </c>
       <c r="P19" t="n">
-        <v>4.375458080650116</v>
+        <v>4.366276846972445</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9869099488292812</v>
+        <v>0.9867131417466308</v>
       </c>
       <c r="R19" t="n">
-        <v>0.008061109514708967</v>
+        <v>0.00812148226279768</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.6274750871000984</v>
+        <v>0.6052939879003358</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.00908790663969649</v>
+        <v>0.009354553561437724</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>0.003989528014871735</v>
+        <v>-0.07127706281254875</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.002973301930883142</v>
+        <v>0.003083599479894748</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7305638330194407</v>
+        <v>0.730330564852065</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01465066649266402</v>
+        <v>0.014657007148279</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.8587258722118825</v>
+        <v>0.8654478225841407</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.004336346172917609</v>
+        <v>0.004231925295112624</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9963810197870483</v>
+        <v>0.9954301895032418</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.0001758828188849516</v>
+        <v>0.0001976420763814884</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2523,25 +2523,25 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2706740016525256</v>
+        <v>0.2057022057339838</v>
       </c>
       <c r="L20" t="n">
-        <v>0.292740499899429</v>
+        <v>0.2460155482071384</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.627752525577289</v>
+        <v>4.630732926731516</v>
       </c>
       <c r="P20" t="n">
-        <v>4.593240864814092</v>
+        <v>4.596123110829812</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9734668925685214</v>
+        <v>0.9739197975232899</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009563211558973351</v>
+        <v>0.009481240982862297</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.8668274204847926</v>
+        <v>0.8655988856614829</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.01063104279203551</v>
+        <v>0.01067996660660704</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.8317276085052017</v>
+        <v>0.8516988751596797</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.002799078990648457</v>
+        <v>0.002627731236034267</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9346148841799236</v>
+        <v>0.9471838630083684</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.006823297667878534</v>
+        <v>0.006132508891023972</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7854085969175137</v>
+        <v>0.7846625705889961</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01701135100923516</v>
+        <v>0.01704089531515587</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.4660248096489776</v>
+        <v>0.437512436021801</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006911644829887301</v>
+        <v>0.0007093773804379569</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2627,25 +2627,25 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1202941340488625</v>
+        <v>0.07261609984294198</v>
       </c>
       <c r="L21" t="n">
-        <v>0.137931315746043</v>
+        <v>0.1313628159483958</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.107682434211664</v>
+        <v>4.163497628306884</v>
       </c>
       <c r="P21" t="n">
-        <v>4.121104552990844</v>
+        <v>4.13089638658079</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8678897471651907</v>
+        <v>0.8036222950424927</v>
       </c>
       <c r="R21" t="n">
-        <v>0.02365423805969597</v>
+        <v>0.02883943790158101</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9532826462626094</v>
+        <v>0.9717485679318847</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.008490375570638316</v>
+        <v>0.006602494021151395</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9946418745541423</v>
+        <v>0.9881406375564401</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.002416255744214073</v>
+        <v>0.003594737083855108</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>-3.873668893466444</v>
+        <v>-6.704116566711466</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.04835449193264897</v>
+        <v>0.06079533245275909</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>-0.3120718465706824</v>
+        <v>-0.3958334788459246</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.01951985317088758</v>
+        <v>0.02013328042520356</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.5248689173044851</v>
+        <v>0.4119749711134348</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0007131366589121639</v>
+        <v>0.0007933483931838523</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2731,25 +2731,25 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2818005832925195</v>
+        <v>0.2535748896970105</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3216433438608675</v>
+        <v>0.2788840742338105</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2758,16 +2758,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.137156494914622</v>
+        <v>4.130086663000351</v>
       </c>
       <c r="P22" t="n">
-        <v>4.309235793842331</v>
+        <v>4.298037864574065</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9818126345681508</v>
+        <v>0.9816645829256813</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006817275267719821</v>
+        <v>0.006844966554480691</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.8940320756762027</v>
+        <v>0.894696765827208</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.009597018447656281</v>
+        <v>0.009566872155521081</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.930553311445966</v>
+        <v>0.8808353626570743</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001460647965992682</v>
+        <v>0.001913345877976869</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3428678973005703</v>
+        <v>0.3405662750325011</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01118877717423164</v>
+        <v>0.01120835455402986</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.955938824717361</v>
+        <v>0.9538585707465665</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.003005623561871168</v>
+        <v>0.003075757331038508</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.7808382624574699</v>
+        <v>0.7765328336879411</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001979254193838229</v>
+        <v>0.001998600861268104</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2835,25 +2835,25 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.208871687187535</v>
+        <v>0.164483483710421</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2714033361257319</v>
+        <v>0.2356365439777174</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2862,16 +2862,16 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.863994820752609</v>
+        <v>3.861994256796289</v>
       </c>
       <c r="P23" t="n">
-        <v>4.107886035032053</v>
+        <v>4.087699207501991</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9822077574114273</v>
+        <v>0.9834987849311843</v>
       </c>
       <c r="R23" t="n">
-        <v>0.009986283699303411</v>
+        <v>0.009617152802415894</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.8998417840638929</v>
+        <v>0.9072842154832755</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02218689334870085</v>
+        <v>0.0213466655012142</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-0.5987192848937495</v>
+        <v>-0.5210529087869615</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001207455260083879</v>
+        <v>0.001177760816248533</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9834080510051557</v>
+        <v>0.9829970487640071</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.002169548508207122</v>
+        <v>0.002196255263537692</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.9263185838948745</v>
+        <v>0.7914370966498618</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0004407038478542581</v>
+        <v>0.0007414577306073622</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.9994487253649298</v>
+        <v>0.9996500866945152</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0001093861607215465</v>
+        <v>8.714823673500832e-05</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2939,25 +2939,25 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3875416039382416</v>
+        <v>0.3446324318476313</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4583294648523437</v>
+        <v>0.4517279862819904</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.305819674281706</v>
+        <v>4.315611646840071</v>
       </c>
       <c r="P24" t="n">
-        <v>4.374016760011923</v>
+        <v>4.364852064870672</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9930288636682071</v>
+        <v>0.9931053841207508</v>
       </c>
       <c r="R24" t="n">
-        <v>0.004958364286698705</v>
+        <v>0.004931075828299149</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.9998817939976682</v>
+        <v>0.999844678512584</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.0008724535878225165</v>
+        <v>0.001000088281498305</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.955596081366228</v>
+        <v>0.9561997570489625</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003327051647853078</v>
+        <v>0.00330435845611347</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8450195515293615</v>
+        <v>0.849908364736977</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.009701678784436861</v>
+        <v>0.009547434376895647</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.9872147780043223</v>
+        <v>0.9497289807407813</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.0007639449575686116</v>
+        <v>0.001514840040229435</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3041,25 +3041,25 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.215848059616466</v>
+        <v>0.1556201893189063</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2284773528280685</v>
+        <v>0.1790082363919602</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.310157944037903</v>
+        <v>4.317303423812332</v>
       </c>
       <c r="P25" t="n">
-        <v>4.340625818175276</v>
+        <v>4.341410043232657</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.984507854515332</v>
+        <v>0.9852686721979196</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02064237548974292</v>
+        <v>0.02012912223434183</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.1747078635040595</v>
+        <v>-0.1041191953581047</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03990414511207344</v>
+        <v>0.03868664366379083</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.5431757325751052</v>
+        <v>0.5617326875108888</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0008576117306741309</v>
+        <v>0.0008400123475412664</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.8914663041449947</v>
+        <v>0.8844143000396868</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.01135719830938619</v>
+        <v>0.01172036040256918</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.661272200372327</v>
+        <v>0.5141961807851072</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.00285215595587576</v>
+        <v>0.003415688920036788</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.9797649579601903</v>
+        <v>0.8961335738561573</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.002330186967735424</v>
+        <v>0.005279299632849382</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.9702799629899451</v>
+        <v>0.849319849722135</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.001076763288601591</v>
+        <v>0.002424507765002992</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.02132222006607809</v>
+        <v>-0.01480890467144746</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003346514058875605</v>
+        <v>0.003335826041153304</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3153,25 +3153,25 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3197948172394026</v>
+        <v>0.2658710797035032</v>
       </c>
       <c r="L26" t="n">
-        <v>0.307729191614642</v>
+        <v>0.267295589751696</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.224153844393832</v>
+        <v>4.209752341131509</v>
       </c>
       <c r="P26" t="n">
-        <v>4.29966176391435</v>
+        <v>4.288503334795399</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9813081611594732</v>
+        <v>0.98209868352588</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02101422326656706</v>
+        <v>0.0205650520661613</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.3194873422489407</v>
+        <v>0.3492905135958023</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04051086820879415</v>
+        <v>0.03961384665857288</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.3167759222675097</v>
+        <v>-0.3419665329242021</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0008044256175139636</v>
+        <v>0.0008120837061757484</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9473966963069762</v>
+        <v>0.9478005965134833</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01238252129801991</v>
+        <v>0.01233489176985998</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.2443036383060944</v>
+        <v>-0.2480601128404065</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.003824784425081982</v>
+        <v>0.003830553466249932</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9173235934568205</v>
+        <v>0.9185393677134852</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.003848789612945321</v>
+        <v>0.003820386155343175</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.981903816046003</v>
+        <v>0.9826956173426886</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.001144335649310885</v>
+        <v>0.001119020349643972</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.4672117928240014</v>
+        <v>0.4408496392470302</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.001011456063301109</v>
+        <v>0.001036177184194751</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3265,25 +3265,25 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2439507965539418</v>
+        <v>0.1853792209497878</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3066785751360043</v>
+        <v>0.2583351741645584</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.149671453558346</v>
+        <v>4.135160058706046</v>
       </c>
       <c r="P27" t="n">
-        <v>4.151144737685096</v>
+        <v>4.129396968057459</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9964585972545316</v>
+        <v>0.9964887188604876</v>
       </c>
       <c r="R27" t="n">
-        <v>0.009658635921927991</v>
+        <v>0.00961747216149119</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.9043392085180965</v>
+        <v>0.9044653629726629</v>
       </c>
       <c r="U27" t="n">
-        <v>0.01623634682286491</v>
+        <v>0.0162256372981169</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.7029069180802154</v>
+        <v>0.7479131096932732</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0006108270453513888</v>
+        <v>0.0005626613953324784</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.9251622015904822</v>
+        <v>0.929344340969139</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.01160032006669633</v>
+        <v>0.01127153193964718</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.9436921249261397</v>
+        <v>0.9618722636930784</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.00086772712896629</v>
+        <v>0.0007140343701769467</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.8860893034683536</v>
+        <v>0.8860631075603903</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.009428301299323778</v>
+        <v>0.009429385375398469</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.5798331579529565</v>
+        <v>0.5569803504220125</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.003492178397757696</v>
+        <v>0.003585890514541132</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4433156051319086</v>
+        <v>0.4443088628636985</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.004858137066522915</v>
+        <v>0.004853801102128594</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3377,25 +3377,25 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3989356014586465</v>
+        <v>0.3642355136098986</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4105437724275827</v>
+        <v>0.4012500131057793</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.114744299841788</v>
+        <v>4.119195147734761</v>
       </c>
       <c r="P28" t="n">
-        <v>4.293035136087989</v>
+        <v>4.288479296104665</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9447350251236333</v>
+        <v>0.9436086480828073</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02448097123631105</v>
+        <v>0.02472919096844255</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.6190449241646123</v>
+        <v>0.6116331747935022</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.05057515743764571</v>
+        <v>0.0510647751074394</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.845679985962686</v>
+        <v>0.8070346400623355</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.004698380335830545</v>
+        <v>0.005253838536222881</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.4997008500170632</v>
+        <v>0.4792699814102419</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01182388887831986</v>
+        <v>0.01206290099489441</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.4022427977723326</v>
+        <v>0.3991449255984524</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01680054637075701</v>
+        <v>0.01684402445551991</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9896186095558721</v>
+        <v>0.9902948924792865</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003527373313012608</v>
+        <v>0.0003410545423197547</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3483,25 +3483,25 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5337507387871602</v>
+        <v>0.541363956397434</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3454522295906396</v>
+        <v>0.5235586967604516</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.255427909449321</v>
+        <v>4.316787024057529</v>
       </c>
       <c r="P29" t="n">
-        <v>4.201654647402672</v>
+        <v>4.269495680096157</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9510114840119204</v>
+        <v>0.9371892656395286</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01428286099957423</v>
+        <v>0.01617279207781879</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.7866406000590361</v>
+        <v>0.7206565206622865</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03010007215515761</v>
+        <v>0.03444140935709698</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.9290719133346621</v>
+        <v>0.9309243689582459</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009224615380400224</v>
+        <v>0.009103357019039344</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.6458639343134771</v>
+        <v>0.6254273555169021</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.008411117137283838</v>
+        <v>0.008650408706614061</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9914430584326879</v>
+        <v>0.9600792266793866</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.002403511476839721</v>
+        <v>0.005191422666438352</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.905411353343703</v>
+        <v>0.9347622362789099</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001835480773710733</v>
+        <v>0.001524333050086481</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3589,25 +3589,25 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4912707336485012</v>
+        <v>0.4591268398364413</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4026087684288571</v>
+        <v>0.4566142486229761</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3616,16 +3616,16 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.515175522261403</v>
+        <v>4.522217691948997</v>
       </c>
       <c r="P30" t="n">
-        <v>4.313607561377583</v>
+        <v>4.322882264987834</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9728981023027231</v>
+        <v>0.9731165159487302</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01356955918456474</v>
+        <v>0.01351477017351402</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.867287971057757</v>
+        <v>0.8681108103201534</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02481413236353701</v>
+        <v>0.02473708663502364</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9846077079275032</v>
+        <v>0.9654025049028722</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0005590929815818638</v>
+        <v>0.0008382136540913968</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>0.002836550550473271</v>
+        <v>-0.04254370587906098</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.01350441126879013</v>
+        <v>0.01380828102729162</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8343668855930195</v>
+        <v>0.8608162393105251</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.008518199220361183</v>
+        <v>0.007808515791687281</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.4739234315342599</v>
+        <v>0.4930906840177888</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.001950679135743517</v>
+        <v>0.001914813555541662</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3695,25 +3695,25 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4902078464552742</v>
+        <v>0.4761534586665042</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4306016586812278</v>
+        <v>0.4435937749479988</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.249538389327932</v>
+        <v>4.256876131451557</v>
       </c>
       <c r="P31" t="n">
-        <v>4.410030188172075</v>
+        <v>4.406214783744725</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9859206503437857</v>
+        <v>0.9861409780642537</v>
       </c>
       <c r="R31" t="n">
-        <v>0.007749040197655582</v>
+        <v>0.007688168757415434</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9485192219064569</v>
+        <v>0.9497635023137877</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01211880347787228</v>
+        <v>0.01197145310566209</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.899301487818288</v>
+        <v>0.9090348845965792</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.007725611082399673</v>
+        <v>0.007342750171641711</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>-0.03053000177468723</v>
+        <v>-0.07237371460497255</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.009230499413846684</v>
+        <v>0.009416032778659647</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.9731950440372746</v>
+        <v>0.9753948227631314</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002569078251395795</v>
+        <v>0.002461404730596016</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.04864669288554757</v>
+        <v>0.03391823878889433</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.00409959019304732</v>
+        <v>0.004131202385804385</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3801,25 +3801,25 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5003204670714311</v>
+        <v>0.4784259818721357</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4277157292674033</v>
+        <v>0.4396002722871774</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.53028971271256</v>
+        <v>4.54395154441503</v>
       </c>
       <c r="P32" t="n">
-        <v>4.425992246404511</v>
+        <v>4.423053759280506</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9797092855898777</v>
+        <v>0.9796796490207097</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01371647812577785</v>
+        <v>0.01372649159866854</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.9019187053601531</v>
+        <v>0.8824526577231863</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.008931998180194519</v>
+        <v>0.00977826804544208</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.227125782583355</v>
+        <v>0.224021570840371</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.01745066310661357</v>
+        <v>0.01748567290604329</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.5421892580542693</v>
+        <v>-0.5501752516722134</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.0157928614398565</v>
+        <v>0.01583369914951323</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.2311239848234773</v>
+        <v>0.2701411407221971</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01816850662788654</v>
+        <v>0.01770151823585247</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.07382372874138743</v>
+        <v>0.07982392336394573</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004891724033596115</v>
+        <v>0.004875852888111583</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3905,25 +3905,25 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2851358817564152</v>
+        <v>0.2262549868912993</v>
       </c>
       <c r="L33" t="n">
-        <v>0.318877189205591</v>
+        <v>0.2964580981939559</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.308512879316226</v>
+        <v>4.301098115789768</v>
       </c>
       <c r="P33" t="n">
-        <v>4.271057230087922</v>
+        <v>4.263093428599172</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9655580660003291</v>
+        <v>0.9639693762745506</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005887686362091251</v>
+        <v>0.006021945102291516</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.9329657134926262</v>
+        <v>0.930968249733922</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01046228497280141</v>
+        <v>0.01061701649445812</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.1136216779889698</v>
+        <v>-0.004604854245426004</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.006041859472656011</v>
+        <v>0.006432187423387583</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.8419596117641139</v>
+        <v>0.8367644164105619</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.004741891982336572</v>
+        <v>0.004819200890245548</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.8087275627461875</v>
+        <v>0.8452926361595079</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.00207519263564663</v>
+        <v>0.001866326887070679</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.41811019654445</v>
+        <v>0.4709474565375992</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0007541993802418439</v>
+        <v>0.0007191429009148535</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4009,25 +4009,25 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5350531219152354</v>
+        <v>0.5348911130605229</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4496288558276344</v>
+        <v>0.5384228813419599</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.263995602912937</v>
+        <v>4.266762406485488</v>
       </c>
       <c r="P34" t="n">
-        <v>4.285493285403806</v>
+        <v>4.312154834736841</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8874123644329036</v>
+        <v>0.9361790115277747</v>
       </c>
       <c r="R34" t="n">
-        <v>0.02339900894059084</v>
+        <v>0.01761707800354978</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.8163313485894672</v>
+        <v>0.8974143595677306</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.05130374898203999</v>
+        <v>0.0383420095060048</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9926351345987787</v>
+        <v>0.9955449680120769</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.002030051118949896</v>
+        <v>0.001578883117276267</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.6403832964109917</v>
+        <v>0.7013335067637991</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004616607184114195</v>
+        <v>0.004207229944072429</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.3490818289130715</v>
+        <v>0.5013692040841152</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.008955763179533109</v>
+        <v>0.007838427613536604</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.06473814985066573</v>
+        <v>0.2739821713457488</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.0009401333509796495</v>
+        <v>0.0008283168347656708</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4115,25 +4115,25 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3019486698931895</v>
+        <v>0.2505787503790524</v>
       </c>
       <c r="L35" t="n">
-        <v>0.24751949465167</v>
+        <v>0.2476706744488357</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.049554670774522</v>
+        <v>4.045568310128426</v>
       </c>
       <c r="P35" t="n">
-        <v>4.155419422183499</v>
+        <v>4.150294700229246</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9968026647702138</v>
+        <v>0.996076440994295</v>
       </c>
       <c r="R35" t="n">
-        <v>0.005633107882523141</v>
+        <v>0.006240136307692128</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9860265812062683</v>
+        <v>0.9768829290224819</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.006450535663099629</v>
+        <v>0.008296804297917524</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6263632103869095</v>
+        <v>0.612649554752265</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.009128693265875511</v>
+        <v>0.009294709668357564</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.7259764031024614</v>
+        <v>0.7232978518092175</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002115415838542737</v>
+        <v>0.002125729670816601</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5278624330597163</v>
+        <v>0.5017056365586393</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002333057760814093</v>
+        <v>0.002396813265267494</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4217,25 +4217,25 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4306133506575378</v>
+        <v>0.3956792038623254</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3952277307226713</v>
+        <v>0.3772180634049475</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.307865273041947</v>
+        <v>4.298761590070962</v>
       </c>
       <c r="P36" t="n">
-        <v>4.321519067505179</v>
+        <v>4.314472797017256</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9835354887150053</v>
+        <v>0.9833034591816343</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01162717237780395</v>
+        <v>0.01170881490655285</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.8084317089137957</v>
+        <v>0.8030129752953671</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01902625059212809</v>
+        <v>0.01929346405109096</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.3717595996132993</v>
+        <v>0.3937567515993992</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.008130839074664459</v>
+        <v>0.00798722462225003</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.06964126973225437</v>
+        <v>0.06392330402484447</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01345734462455408</v>
+        <v>0.01349863561353459</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.728509641823178</v>
+        <v>0.7343155153926439</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.006104128876372306</v>
+        <v>0.006038507174148961</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.1670701935279308</v>
+        <v>0.151383502696266</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004035884011984705</v>
+        <v>0.004073710948003456</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4323,25 +4323,25 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1032759135620988</v>
+        <v>0.05738019622196385</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1052974555473489</v>
+        <v>0.07187183413434833</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.230764125716685</v>
+        <v>4.219329310499894</v>
       </c>
       <c r="P37" t="n">
-        <v>4.263232513024087</v>
+        <v>4.254728410727956</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9931562102604981</v>
+        <v>0.9930173872572994</v>
       </c>
       <c r="R37" t="n">
-        <v>0.005512353980038237</v>
+        <v>0.005567981035393577</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>0.02232969103987603</v>
+        <v>0.0932675702980631</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0004230041163021422</v>
+        <v>0.0004073689792571523</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9984068109743827</v>
+        <v>0.9986927389984463</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.00189506155895734</v>
+        <v>0.001716606771902392</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.5007957506550722</v>
+        <v>-0.5161524176848171</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.007756653822795167</v>
+        <v>0.007796237114690461</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9118017575571626</v>
+        <v>0.909420461135821</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009664547763306183</v>
+        <v>0.009794147150674554</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.940625407252214</v>
+        <v>0.9306494066752465</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.002186139360582258</v>
+        <v>0.002362667520562983</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9999996806026822</v>
+        <v>0.9999992472983318</v>
       </c>
       <c r="AM37" t="n">
-        <v>5.563157774895456e-07</v>
+        <v>8.540183106247728e-07</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4431,25 +4431,25 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1416438943560188</v>
+        <v>0.08867237739422326</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1094955221332978</v>
+        <v>0.07327446990607386</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.113546643685265</v>
+        <v>4.086901387408154</v>
       </c>
       <c r="P38" t="n">
-        <v>4.195575058726416</v>
+        <v>4.186586613491636</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9538747494938609</v>
+        <v>0.9589512985719434</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01205090202935683</v>
+        <v>0.0113684144483331</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.1856746702867531</v>
+        <v>0.02144122315033237</v>
       </c>
       <c r="X38" t="n">
-        <v>0.001182812986735585</v>
+        <v>0.001296613594212609</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.8117400695136249</v>
+        <v>0.847912062457137</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02092714413211252</v>
+        <v>0.01880954994763496</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.3889791861968517</v>
+        <v>-0.3387514716347118</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01710582175510812</v>
+        <v>0.01679368659617104</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.9638846440510584</v>
+        <v>0.941950636522371</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.004411335700999675</v>
+        <v>0.005592717556323321</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-1.16109724143762</v>
+        <v>-0.9297900459974751</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.004856150575323175</v>
+        <v>0.004588915366316424</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.9999973457512438</v>
+        <v>0.9999950238400729</v>
       </c>
       <c r="AM38" t="n">
-        <v>6.529628274818922e-07</v>
+        <v>8.940562082327667e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4539,25 +4539,25 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1514776863482813</v>
+        <v>0.09605755582229301</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1340732886312007</v>
+        <v>0.09760678814077213</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.258531293425802</v>
+        <v>4.239319110069875</v>
       </c>
       <c r="P39" t="n">
-        <v>4.266000771504852</v>
+        <v>4.257342768848647</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9829587365995249</v>
+        <v>0.9837605775358461</v>
       </c>
       <c r="R39" t="n">
-        <v>0.008737874047912922</v>
+        <v>0.008529826070278492</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.8831627197684985</v>
+        <v>0.8980761680671179</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.01144041772745747</v>
+        <v>0.01068535694470511</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.1261866791231349</v>
+        <v>0.108801178015107</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001390727162238847</v>
+        <v>0.001404494064848107</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.04784161916678453</v>
+        <v>-0.04529134157407189</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.0146620188601067</v>
+        <v>0.01464416549569893</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.7521066762451492</v>
+        <v>0.7583287512379153</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005402853671293663</v>
+        <v>0.005334617473796769</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1202639646824426</v>
+        <v>-0.111143401374113</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002183874932294108</v>
+        <v>0.002174966821564137</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4643,25 +4643,25 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2425659656922763</v>
+        <v>0.2142256566055332</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3987876566146299</v>
+        <v>0.393812032158156</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4670,16 +4670,16 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4.328296976830683</v>
+        <v>4.344681894901522</v>
       </c>
       <c r="P40" t="n">
-        <v>4.516222119821735</v>
+        <v>4.512890762059443</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9926179059151392</v>
+        <v>0.9918423001861221</v>
       </c>
       <c r="R40" t="n">
-        <v>0.00516095238751394</v>
+        <v>0.005425302078893494</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.9749198582663106</v>
+        <v>0.9733658947756055</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.009557112442325669</v>
+        <v>0.009848741940377865</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.9529782610715386</v>
+        <v>0.9649206865602558</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0004933234697556976</v>
+        <v>0.0004260965098638273</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9822407656566788</v>
+        <v>0.9806647988869065</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.003347306037122141</v>
+        <v>0.003492670759635476</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.9915343214985948</v>
+        <v>0.9885585884573755</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.004131973972221811</v>
+        <v>0.004803596228536713</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999996564976324</v>
+        <v>0.9999994227326788</v>
       </c>
       <c r="AM40" t="n">
-        <v>3.563580675576409e-07</v>
+        <v>4.619662086822549e-07</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4747,25 +4747,25 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2579668642380593</v>
+        <v>0.1960309265200225</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2827779486933421</v>
+        <v>0.2439922858892234</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4774,16 +4774,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.436658074738552</v>
+        <v>4.444022518146278</v>
       </c>
       <c r="P41" t="n">
-        <v>4.506800454719634</v>
+        <v>4.503904933946549</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9935662715399209</v>
+        <v>0.9935283807088948</v>
       </c>
       <c r="R41" t="n">
-        <v>0.006216506181144936</v>
+        <v>0.006234785069395188</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8657216065040257</v>
+        <v>0.8663114295119574</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.0106711270439813</v>
+        <v>0.01064766458188224</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.6406310632877251</v>
+        <v>0.6752960357794721</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001495004964743306</v>
+        <v>0.00142107226359151</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.9709982038957142</v>
+        <v>0.9703868079381348</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.00456618295428893</v>
+        <v>0.004614062497198809</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9468870582876832</v>
+        <v>0.945511891090166</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.00743003465383836</v>
+        <v>0.007525606898205431</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.9002451043225806</v>
+        <v>0.9016668825272562</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001030199756548226</v>
+        <v>0.001022831836996405</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4851,25 +4851,25 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.317014523922711</v>
+        <v>0.2509391170687325</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3992774395657734</v>
+        <v>0.3540760181826904</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -4878,16 +4878,16 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.517744602412055</v>
+        <v>4.41672374136586</v>
       </c>
       <c r="P42" t="n">
-        <v>4.483499745310579</v>
+        <v>4.454828376642536</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9576260208619269</v>
+        <v>0.9562274707647596</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01363166696486196</v>
+        <v>0.01385479690299464</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.8251353637313272</v>
+        <v>0.8171857883461777</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.0229479137615669</v>
+        <v>0.02346373751795033</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.9707069539571168</v>
+        <v>0.9242271168961089</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.0009147715850875558</v>
+        <v>0.001471252808635844</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.6837119960478947</v>
+        <v>0.6825680577083362</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01641377356131514</v>
+        <v>0.01644342913674678</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.9912430412372571</v>
+        <v>0.9908936329892041</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.00289389750923357</v>
+        <v>0.002951066991320317</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4953,25 +4953,25 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1593858374334936</v>
+        <v>0.1205565534842748</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2953606878173711</v>
+        <v>0.2627014101404899</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -4980,16 +4980,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.921309732134107</v>
+        <v>3.918089231682008</v>
       </c>
       <c r="P43" t="n">
-        <v>4.231892326870648</v>
+        <v>4.218531960510607</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9531804648397209</v>
+        <v>0.9571784872545654</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01322101155761209</v>
+        <v>0.01264393163064142</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.9196726141488445</v>
+        <v>0.9317765205054651</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.02437451250350367</v>
+        <v>0.02246317053136041</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.7515166694804631</v>
+        <v>0.842347729962843</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.002354138279213153</v>
+        <v>0.001875138944588392</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.7300542704882629</v>
+        <v>0.7122470476682665</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01646523486372967</v>
+        <v>0.01699963489788116</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.910083480921537</v>
+        <v>0.9434245287750042</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.001680946510196186</v>
+        <v>0.001333362512321841</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.9754722971342382</v>
+        <v>0.9702769026324689</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0006223872777695342</v>
+        <v>0.0006851399628237201</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5057,25 +5057,25 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1743546614482898</v>
+        <v>0.1161247165757327</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3607161911403574</v>
+        <v>0.2747297028918776</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.252007996567885</v>
+        <v>4.226110669456893</v>
       </c>
       <c r="P44" t="n">
-        <v>4.379876703707501</v>
+        <v>4.359820668211799</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9322289901765384</v>
+        <v>0.9311393328987272</v>
       </c>
       <c r="R44" t="n">
-        <v>0.00886693672513535</v>
+        <v>0.008937936067054061</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9118343741510551</v>
+        <v>0.9172164971207226</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.01331514308618879</v>
+        <v>0.0129023283540272</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.7629989410251768</v>
+        <v>0.7922042521305956</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.005399165764861191</v>
+        <v>0.005055566719559172</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.9073004518172708</v>
+        <v>0.8919406831134686</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.01064883496157211</v>
+        <v>0.0114972611626813</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.8476536494680851</v>
+        <v>0.8437722109036985</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.008479320456552345</v>
+        <v>0.008586657968263406</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.6941211503297948</v>
+        <v>0.6685500910030241</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.001171429311538728</v>
+        <v>0.001219411569503721</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5161,25 +5161,25 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3961005288343256</v>
+        <v>0.3561715337841546</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2489886367685431</v>
+        <v>0.4596161945265416</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.214350986480778</v>
+        <v>4.204683775347685</v>
       </c>
       <c r="P45" t="n">
-        <v>4.320122892021073</v>
+        <v>4.422751219522892</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9702313440706339</v>
+        <v>0.9710823779105939</v>
       </c>
       <c r="R45" t="n">
-        <v>0.008426354157252566</v>
+        <v>0.008305033412205348</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9784347599200411</v>
+        <v>0.978201337151219</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01256046048187576</v>
+        <v>0.01262825490661887</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.9263908096369194</v>
+        <v>0.9264574993529273</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007115518876935951</v>
+        <v>0.007112294826646373</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8721738592106956</v>
+        <v>0.8787454696958589</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008496248798279732</v>
+        <v>0.008274968897209712</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9200557691923775</v>
+        <v>0.9287358778670444</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008604497120791905</v>
+        <v>0.008123952952602731</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9793660680563808</v>
+        <v>0.9825409339116216</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.0006307385896372336</v>
+        <v>0.0005801882243384206</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5265,25 +5265,25 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4197523519087317</v>
+        <v>0.4073750266228692</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3538478146508492</v>
+        <v>0.4877311501843291</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.774562388265622</v>
+        <v>3.814004562068153</v>
       </c>
       <c r="P46" t="n">
-        <v>4.469631474021861</v>
+        <v>4.464592034099284</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9691700565078264</v>
+        <v>0.9751493750985125</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008371678975015451</v>
+        <v>0.007516139969041939</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9852529476931888</v>
+        <v>0.9876828141809345</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.009364100463556499</v>
+        <v>0.008557939283508819</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9337676750333243</v>
+        <v>0.9377054773714882</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.009552512080250805</v>
+        <v>0.009264191556377126</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9846233103721167</v>
+        <v>0.9877265388188802</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.00202983142116043</v>
+        <v>0.001813477087712048</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8483107869021425</v>
+        <v>0.8912778190528515</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.01289745800054248</v>
+        <v>0.01091907505098744</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9862790930877983</v>
+        <v>0.9881586569867821</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.001011702176816321</v>
+        <v>0.0009398569470527479</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5369,25 +5369,25 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2493695583752376</v>
+        <v>0.1887746212355711</v>
       </c>
       <c r="L47" t="n">
-        <v>0.334323690586066</v>
+        <v>0.2874926525482054</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.220558446554917</v>
+        <v>4.185310192182019</v>
       </c>
       <c r="P47" t="n">
-        <v>4.34135409092813</v>
+        <v>4.328274446329779</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9415799702410498</v>
+        <v>0.9420537386193443</v>
       </c>
       <c r="R47" t="n">
-        <v>0.009083243677576116</v>
+        <v>0.009046337550908161</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.9337982099239828</v>
+        <v>0.9396134589639014</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01417674747859337</v>
+        <v>0.01353978643124449</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.812072719846809</v>
+        <v>0.8635723001645395</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.006773450144281096</v>
+        <v>0.005771202364270337</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.8225035807354626</v>
+        <v>0.7897414159202871</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.01256175254053157</v>
+        <v>0.01367200798482611</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9685788529767632</v>
+        <v>0.9777742557730912</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.002748987619929098</v>
+        <v>0.002312011144988303</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9144623201650787</v>
+        <v>0.923475328011221</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.0005587689846373318</v>
+        <v>0.0005285113244619222</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5473,25 +5473,25 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.109062118721277</v>
+        <v>0.06767257822732965</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4819694991065029</v>
+        <v>0.3438967560587061</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.575232101365941</v>
+        <v>3.655465587484483</v>
       </c>
       <c r="P48" t="n">
-        <v>4.350282899258956</v>
+        <v>4.37384633338082</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9799807072945712</v>
+        <v>0.9681890667047797</v>
       </c>
       <c r="R48" t="n">
-        <v>0.007295458123566167</v>
+        <v>0.009196369441592829</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.9670514601319901</v>
+        <v>0.9617958914675412</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.01327282333452833</v>
+        <v>0.01429223874010929</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.8511299313845332</v>
+        <v>0.8111865587639752</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.006517710128062508</v>
+        <v>0.007340198439256735</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.9879783933259402</v>
+        <v>0.9520929030577686</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.006358306232025789</v>
+        <v>0.01269287815253036</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.8971030179730674</v>
+        <v>0.9475153302757008</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.002650808591286444</v>
+        <v>0.001893186003532806</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9997445041281109</v>
+        <v>0.9995639084097956</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0001237628887575433</v>
+        <v>0.0001616915594861161</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5577,25 +5577,25 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3590159275296237</v>
+        <v>0.3236571036150679</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4629775088466354</v>
+        <v>0.4680219017957259</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -5604,16 +5604,16 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.039760162263589</v>
+        <v>4.059016345835413</v>
       </c>
       <c r="P49" t="n">
-        <v>4.387464439778952</v>
+        <v>4.380739583085585</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9272204229533172</v>
+        <v>0.9306133851363765</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01278733496122558</v>
+        <v>0.01248570667776224</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9269537702078596</v>
+        <v>0.924569180178753</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.0182306317978539</v>
+        <v>0.0185258110871032</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.9384545262801669</v>
+        <v>0.9409052969664844</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.002379073901348844</v>
+        <v>0.002331224778908566</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.4456852453913365</v>
+        <v>0.469391443993011</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01374527115471176</v>
+        <v>0.01344813982868332</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.4014699385906918</v>
+        <v>0.4854913243846498</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01699820666149585</v>
+        <v>0.01576000940614472</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8731931914353145</v>
+        <v>0.8805764955958068</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001300861196452567</v>
+        <v>0.001262422067757764</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5681,25 +5681,25 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.509975097271933</v>
+        <v>0.5001414823415646</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5505848201746671</v>
+        <v>0.5571628184286667</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.291212719785222</v>
+        <v>4.295513413439029</v>
       </c>
       <c r="P50" t="n">
-        <v>4.500481878863585</v>
+        <v>4.454303535379676</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9643131386676767</v>
+        <v>0.9648334216972402</v>
       </c>
       <c r="R50" t="n">
-        <v>0.01009684583614506</v>
+        <v>0.01002297404035096</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9847225923342044</v>
+        <v>0.984532493118873</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.01039843948697537</v>
+        <v>0.01046293419893906</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9360197628461002</v>
+        <v>0.9377681166232442</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005389682398801431</v>
+        <v>0.005315531835310413</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.9495182886766423</v>
+        <v>0.9502984722141891</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.002295511352826723</v>
+        <v>0.002277703968291541</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.8194325120806389</v>
+        <v>0.8236463685043796</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.01705362614871232</v>
+        <v>0.01685346345701342</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5783,25 +5783,25 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4767246818589526</v>
+        <v>0.4746629412539786</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5516625159727202</v>
+        <v>0.5579799924711972</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -5810,16 +5810,16 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.852084868275818</v>
+        <v>3.848875145161648</v>
       </c>
       <c r="P51" t="n">
-        <v>4.425021504494057</v>
+        <v>4.425729460286711</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.928518635689824</v>
+        <v>0.9284225402021243</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01073767156444199</v>
+        <v>0.01074488669937242</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.9298020078864232</v>
+        <v>0.9294129968826711</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.01566393252059432</v>
+        <v>0.01570727440097024</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.7959709183259848</v>
+        <v>0.7965577171290564</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01442274227687904</v>
+        <v>0.01440198704484779</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-0.8079856495807261</v>
+        <v>-0.8051505386899462</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003373134653022638</v>
+        <v>0.003370488914467463</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.8918970998225999</v>
+        <v>0.8918658259067099</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01055632191053338</v>
+        <v>0.01055784873589891</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9956288507792258</v>
+        <v>0.9956408271332348</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0005474547176660709</v>
+        <v>0.0005467042269295646</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5887,25 +5887,25 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1577619308753721</v>
+        <v>0.101465410040746</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2332576237530504</v>
+        <v>0.1831499130629796</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.292754697312242</v>
+        <v>4.284078512333842</v>
       </c>
       <c r="P52" t="n">
-        <v>4.285138203429157</v>
+        <v>4.269826538405476</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9438578508547878</v>
+        <v>0.9409099603363811</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01144189036378144</v>
+        <v>0.01173844058261254</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9213683409175074</v>
+        <v>0.9170010657064158</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.01284086482256702</v>
+        <v>0.01319264306379424</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.8528322432347442</v>
+        <v>0.8521207495766849</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.002713810080924104</v>
+        <v>0.002720362231367404</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.7649466021748099</v>
+        <v>0.7508068405966803</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01740939618453367</v>
+        <v>0.01792538532876083</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.3437539527154617</v>
+        <v>0.3183274020097735</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.01335547456094254</v>
+        <v>0.01361174778928569</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.05764133052217757</v>
+        <v>0.02139274129615065</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0009359084779877782</v>
+        <v>0.0009537388612291783</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -5991,25 +5991,25 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3306984100273074</v>
+        <v>0.2727378027638814</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2222187220843617</v>
+        <v>0.2726287635947208</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6018,16 +6018,16 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.388506524434447</v>
+        <v>4.35109846563273</v>
       </c>
       <c r="P53" t="n">
-        <v>4.433029285114089</v>
+        <v>4.434421493170414</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.987816836719875</v>
+        <v>0.9863442294331061</v>
       </c>
       <c r="R53" t="n">
-        <v>0.004745620692211202</v>
+        <v>0.005024248325364421</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9846901797282983</v>
+        <v>0.9775572457437087</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.007170994494039955</v>
+        <v>0.008682252661680974</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.9248878354650139</v>
+        <v>0.9371056469774383</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.002813421705909762</v>
+        <v>0.002574456286801667</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9762568144864854</v>
+        <v>0.9718954043873925</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.003804235567470246</v>
+        <v>0.004138915678627068</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.9608967543252724</v>
+        <v>0.9755266950079378</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.005758634183792521</v>
+        <v>0.004555744914180935</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.987966082527848</v>
+        <v>0.9332617466523701</v>
       </c>
       <c r="AM53" t="n">
-        <v>4.858242130553261e-05</v>
+        <v>0.0001144097554973275</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6095,25 +6095,25 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1828418750194339</v>
+        <v>0.1507171304147058</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4220001080464181</v>
+        <v>0.3833015762255148</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -6122,16 +6122,16 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>4.170489229158358</v>
+        <v>4.160594641493467</v>
       </c>
       <c r="P54" t="n">
-        <v>4.303014583111808</v>
+        <v>4.281373017040605</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9067625262141346</v>
+        <v>0.8977877951689994</v>
       </c>
       <c r="R54" t="n">
-        <v>0.01108783010979986</v>
+        <v>0.0116092106692415</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.8595447656427713</v>
+        <v>0.8414482844104839</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.01930900227717032</v>
+        <v>0.02051522771385939</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.4067551151670381</v>
+        <v>0.4361268556992465</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.004441799033481543</v>
+        <v>0.0043304458222479</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.8112952659055621</v>
+        <v>0.8082064115584967</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.01288273300476303</v>
+        <v>0.01298774196051567</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.6639692896586624</v>
+        <v>0.60720908287616</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.007427913290475918</v>
+        <v>0.008030786130603743</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8854808721867133</v>
+        <v>0.8771242276391241</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.0009970103321812248</v>
+        <v>0.001032746597567763</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6199,25 +6199,25 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1383001117129508</v>
+        <v>0.09413185541746324</v>
       </c>
       <c r="L55" t="n">
-        <v>0.469718806022866</v>
+        <v>0.4783778245910579</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6226,16 +6226,16 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4.460797912271313</v>
+        <v>4.486646905356348</v>
       </c>
       <c r="P55" t="n">
-        <v>4.390400264149273</v>
+        <v>4.389950993753057</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8410234317987829</v>
+        <v>0.8226587915597545</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01607843613086387</v>
+        <v>0.0169817357168279</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.6886028526186868</v>
+        <v>0.6474763574611182</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.02693660828251536</v>
+        <v>0.02866023322636591</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.002049653051881539</v>
+        <v>-0.03966766555194545</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.004373974955361549</v>
+        <v>0.00446446162137651</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.4887791626445642</v>
+        <v>0.4333705449957882</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.02290295175637864</v>
+        <v>0.02411219560011628</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.8868827687464473</v>
+        <v>0.9072547464585476</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.004803734867970931</v>
+        <v>0.004349711904029629</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.8713466335423119</v>
+        <v>0.8758103965692023</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.0004969422086845115</v>
+        <v>0.0004882451394394965</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6303,25 +6303,25 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2039298221414741</v>
+        <v>0.1460704737966806</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3222654196083304</v>
+        <v>0.2351498245325966</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.981252851815452</v>
+        <v>3.92679468727763</v>
       </c>
       <c r="P56" t="n">
-        <v>4.305313728523216</v>
+        <v>4.295903185919488</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8140026743624541</v>
+        <v>0.8244306602963709</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01265400181587147</v>
+        <v>0.0122941605546842</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.6320085494266621</v>
+        <v>0.696273836658334</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.02117953657030387</v>
+        <v>0.01924148960139036</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>-0.02810911562099561</v>
+        <v>0.14570932502376</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.00888682273930924</v>
+        <v>0.008100834239050229</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.6507137560021403</v>
+        <v>0.5882595173686509</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.0156253701047111</v>
+        <v>0.0169649020658686</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.8767529975207164</v>
+        <v>0.8641818561177234</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.005104112906601275</v>
+        <v>0.005358102107242078</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.8724483612498279</v>
+        <v>0.8506402572303703</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001693004009184952</v>
+        <v>0.00183202646723182</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6407,25 +6407,25 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3806411666965068</v>
+        <v>0.3372330102865788</v>
       </c>
       <c r="L57" t="n">
-        <v>0.446908871038932</v>
+        <v>0.4422700652767724</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.256768970266466</v>
+        <v>4.259702116978529</v>
       </c>
       <c r="P57" t="n">
-        <v>4.367295926384822</v>
+        <v>4.360264441256886</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9003983522957966</v>
+        <v>0.8987579024912619</v>
       </c>
       <c r="R57" t="n">
-        <v>0.009596819889347217</v>
+        <v>0.009675527455599754</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.7858990746237033</v>
+        <v>0.7772525994953501</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01751351879881869</v>
+        <v>0.01786366076274804</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.6377957646282724</v>
+        <v>0.6410965661821657</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.008676343508065438</v>
+        <v>0.008636718854951706</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.7497121235996479</v>
+        <v>0.7575282678596247</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.007680300061801535</v>
+        <v>0.007559426307468216</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9469764606982166</v>
+        <v>0.9532260355223445</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.004237528805731705</v>
+        <v>0.003979975496935578</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6899976100324631</v>
+        <v>0.7216388582182561</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.001244517230741319</v>
+        <v>0.001179295654215196</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6511,25 +6511,25 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1189716300414537</v>
+        <v>0.09167383144256949</v>
       </c>
       <c r="L58" t="n">
-        <v>0.4893927656651046</v>
+        <v>0.4860138653013357</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -6538,16 +6538,16 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>4.137219511845506</v>
+        <v>4.152556949971706</v>
       </c>
       <c r="P58" t="n">
-        <v>4.399918490664566</v>
+        <v>4.396539664493827</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9543845781816904</v>
+        <v>0.9491108848610297</v>
       </c>
       <c r="R58" t="n">
-        <v>0.008981029054341408</v>
+        <v>0.009485990893583554</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9774854388160339</v>
+        <v>0.9736092914810801</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.008706225352617539</v>
+        <v>0.009425918622346683</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.9615695805706699</v>
+        <v>0.963834983810236</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.001804237029368015</v>
+        <v>0.001750251109316293</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.9749377991538332</v>
+        <v>0.9723896939066873</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.006082801182041506</v>
+        <v>0.006384540251165347</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.5644150435155564</v>
+        <v>0.5188094650512077</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.01693185986705981</v>
+        <v>0.01779617907006115</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.955957926644607</v>
+        <v>0.9567537931783014</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0007432593409593535</v>
+        <v>0.0007365131584383678</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6615,25 +6615,25 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4654669130886756</v>
+        <v>0.4454560940571964</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5135266407365338</v>
+        <v>0.5298941681217869</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.192052202289072</v>
+        <v>4.193144733448825</v>
       </c>
       <c r="P59" t="n">
-        <v>4.383827840564227</v>
+        <v>4.384068460531969</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.8047445056530412</v>
+        <v>0.8126010847893519</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01891378881081737</v>
+        <v>0.01852936089226071</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.781230944941273</v>
+        <v>0.7917578857052692</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.02932140296772496</v>
+        <v>0.02860724816865818</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.4412019164161227</v>
+        <v>0.4438808761107462</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02310131047756706</v>
+        <v>0.02304586841877636</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.1387715782668283</v>
+        <v>0.1377844534069149</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.01076620816955282</v>
+        <v>0.01077237639240744</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-0.7744006991037902</v>
+        <v>-0.5932706166532085</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.01652317940717141</v>
+        <v>0.0156571438570961</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.5584973427889075</v>
+        <v>-0.4829820038351713</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.002512990659079899</v>
+        <v>0.00245135258948054</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6719,25 +6719,25 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3195516907355711</v>
+        <v>0.2701213903358244</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2337909910577463</v>
+        <v>0.2197642545761248</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.041987989944264</v>
+        <v>4.028615073796866</v>
       </c>
       <c r="P60" t="n">
-        <v>4.211312034823191</v>
+        <v>4.210097226686176</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.8938767987070141</v>
+        <v>0.9374859094892489</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02026178555644128</v>
+        <v>0.01555111389188623</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.6153863286901591</v>
+        <v>0.7864208390366414</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.04344884916800898</v>
+        <v>0.03237765246310964</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.405634905383364</v>
+        <v>-1.493919976812546</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.008220313021881646</v>
+        <v>0.0083697937094382</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.618216638052747</v>
+        <v>0.602707475221207</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.006814296643099133</v>
+        <v>0.006951327221777</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-9.226993784798434</v>
+        <v>-7.532698183515887</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.007115568369428657</v>
+        <v>0.006499482743844156</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9316574957294248</v>
+        <v>0.9322176893133124</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0005077179470773505</v>
+        <v>0.0005056328212029454</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6823,25 +6823,25 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.2918937862084307</v>
+        <v>0.2352207679818123</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2592866857253662</v>
+        <v>0.352001824778164</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -6850,16 +6850,16 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.826202503798687</v>
+        <v>3.90269338648964</v>
       </c>
       <c r="P61" t="n">
-        <v>4.250481613740231</v>
+        <v>4.26360888051367</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.9854262650018197</v>
+        <v>0.9834855753748406</v>
       </c>
       <c r="R61" t="n">
-        <v>0.008606971874534824</v>
+        <v>0.009162134717867467</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.9752119446031777</v>
+        <v>0.9707015464739549</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.01754678782678737</v>
+        <v>0.01907650208540938</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.4549475854479135</v>
+        <v>0.3647660186118008</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.004002056052950329</v>
+        <v>0.004320468957709931</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.6691623413986479</v>
+        <v>0.7266945492695671</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.005827783288800277</v>
+        <v>0.005296879240619079</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.8770649536774233</v>
+        <v>0.926596778514992</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.002802682361596211</v>
+        <v>0.002165676513655375</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.2124452246588369</v>
+        <v>0.2593441127386837</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.00241751992615767</v>
+        <v>0.002344433476636395</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6929,25 +6929,25 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1532581908813461</v>
+        <v>0.1179114706658067</v>
       </c>
       <c r="L62" t="n">
-        <v>0.205888269250832</v>
+        <v>0.2754525624894467</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -6956,16 +6956,16 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.148400063035928</v>
+        <v>4.133780946112486</v>
       </c>
       <c r="P62" t="n">
-        <v>4.187206950687719</v>
+        <v>4.207162668976927</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.9879952491638674</v>
+        <v>0.9867851552063307</v>
       </c>
       <c r="R62" t="n">
-        <v>0.007225939848626735</v>
+        <v>0.007581389338084221</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.9821729147992779</v>
+        <v>0.9790912100548086</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01392648449424006</v>
+        <v>0.01508223765231657</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>0.2171056861960092</v>
+        <v>0.1576324405933822</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.002945569699425672</v>
+        <v>0.00305540334834084</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.7197751873727491</v>
+        <v>0.754132793129531</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.007087553712570922</v>
+        <v>0.006638857901740868</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.9766334051031885</v>
+        <v>0.9830246792518017</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.0022693602443811</v>
+        <v>0.001934259427567105</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.8473824521030451</v>
+        <v>0.8624298617537403</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.001957124392450518</v>
+        <v>0.001858139352765948</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7035,25 +7035,25 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2693602879820832</v>
+        <v>0.2141960782563756</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2793775025536183</v>
+        <v>0.3478614695877192</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -7062,16 +7062,16 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.977065693514069</v>
+        <v>3.988319022978723</v>
       </c>
       <c r="P63" t="n">
-        <v>4.244548958727303</v>
+        <v>4.244604686393206</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9884784553519506</v>
+        <v>0.9861480480365411</v>
       </c>
       <c r="R63" t="n">
-        <v>0.007850722641286927</v>
+        <v>0.008608148872540919</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.9762472684388346</v>
+        <v>0.9713089524903108</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.01697057388669265</v>
+        <v>0.01865146505449873</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.9351969766443148</v>
+        <v>0.9040138122119051</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.001111583733859145</v>
+        <v>0.001352847733513924</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9884700934306769</v>
+        <v>0.9776196674708821</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.001194200754899445</v>
+        <v>0.001663786956822548</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.8222616305817994</v>
+        <v>0.8113070360657777</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.003759864652942834</v>
+        <v>0.003873998690220017</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.210003811879761</v>
+        <v>0.292693967362438</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.002052600746476849</v>
+        <v>0.001942207667950637</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7141,25 +7141,25 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2066785242826841</v>
+        <v>0.1809408828464476</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2647111967065329</v>
+        <v>0.3517383293875291</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -7168,16 +7168,16 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.70690274747437</v>
+        <v>3.842031705252123</v>
       </c>
       <c r="P64" t="n">
-        <v>4.231895232607643</v>
+        <v>4.255130796122556</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9835394022992645</v>
+        <v>0.9832179225483965</v>
       </c>
       <c r="R64" t="n">
-        <v>0.008596139023805634</v>
+        <v>0.008679675538555</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9764635681404795</v>
+        <v>0.9746115027146149</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.01620237327667081</v>
+        <v>0.01682777976396323</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.6398359905773952</v>
+        <v>0.575343248919759</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.003241018231091507</v>
+        <v>0.003519251758618904</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.4255190091363108</v>
+        <v>0.5087474584055145</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.009223070556417044</v>
+        <v>0.008528842695872629</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9661375902218116</v>
+        <v>0.979761154745306</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.002655779487025484</v>
+        <v>0.002053174900749675</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8306508125883827</v>
+        <v>0.8369451178385234</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002326138549123357</v>
+        <v>0.002282500723972777</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7247,25 +7247,25 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.2856673816535896</v>
+        <v>0.2343549687378016</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3398983205520008</v>
+        <v>0.4001994464598023</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -7274,16 +7274,16 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.911375026612862</v>
+        <v>3.934277280939161</v>
       </c>
       <c r="P65" t="n">
-        <v>4.265875734099185</v>
+        <v>4.272507516353746</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9787530097409418</v>
+        <v>0.9773748504963572</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01049932781855502</v>
+        <v>0.01083449105219619</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.9645502345986847</v>
+        <v>0.9614404833935521</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02152494675556764</v>
+        <v>0.02244921677032847</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.7181168119953099</v>
+        <v>0.7161351591936943</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.00359515641117737</v>
+        <v>0.003607771331999769</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.6683665106236629</v>
+        <v>0.6945174418221582</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008105584173975852</v>
+        <v>0.007779440068484432</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.9151777346320565</v>
+        <v>0.9102245351061181</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.002512798020149233</v>
+        <v>0.002585124595851902</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.5535815122448711</v>
+        <v>0.5797906342655783</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001909283918479396</v>
+        <v>0.001852389423211578</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7353,25 +7353,25 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.252410987791241</v>
+        <v>0.2127213958762116</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2761950151118719</v>
+        <v>0.3636318836753884</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -7380,16 +7380,16 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3.951261926227352</v>
+        <v>3.974061279508674</v>
       </c>
       <c r="P66" t="n">
-        <v>4.237208873362007</v>
+        <v>4.258883120631724</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9814948522944399</v>
+        <v>0.9809376368835094</v>
       </c>
       <c r="R66" t="n">
-        <v>0.009201101500784705</v>
+        <v>0.009338602989329677</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.970699643601635</v>
+        <v>0.9687473782707321</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.01801844370020395</v>
+        <v>0.01860904359804696</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.7248711456326986</v>
+        <v>0.6865443124741343</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.003233424438140572</v>
+        <v>0.003451300102791382</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.6872153313053242</v>
+        <v>0.714554183135692</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.008544751503997802</v>
+        <v>0.008162788606769335</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.9413728331013935</v>
+        <v>0.9607364747122922</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.00336754185387246</v>
+        <v>0.00275586661225097</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8438067066347505</v>
+        <v>0.8525873545881274</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002187715921193056</v>
+        <v>0.002125333592851551</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7459,25 +7459,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4199481606275527</v>
+        <v>0.3806197152985694</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3946866443520776</v>
+        <v>0.4180147577290543</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.396330197414215</v>
+        <v>4.399192715745249</v>
       </c>
       <c r="P67" t="n">
-        <v>4.347009083049031</v>
+        <v>4.34145712925918</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8548503604283604</v>
+        <v>0.8898399228646471</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02755623317484084</v>
+        <v>0.02400623127839077</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.80378112428995</v>
+        <v>0.7180164833557325</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0007699850337809299</v>
+        <v>0.0009230468691235292</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.595704131102072</v>
+        <v>0.6994413514564134</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.06551773306075803</v>
+        <v>0.05649029269309142</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7655115302033604</v>
+        <v>0.6660639308675809</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.002652909289289455</v>
+        <v>0.003165871764133855</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6425545208618427</v>
+        <v>0.6218938227456987</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01311360028112063</v>
+        <v>0.01348726609519165</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8046679413695343</v>
+        <v>0.8282022900406446</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.009152940352235572</v>
+        <v>0.00858385854084563</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.8180787262487923</v>
+        <v>0.8677465395533979</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.0001138300924851284</v>
+        <v>9.705521994018908e-05</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7567,25 +7567,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4285023488478826</v>
+        <v>0.388632156297176</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3889409181159572</v>
+        <v>0.4210165808157574</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.480408325582514</v>
+        <v>4.486141889112795</v>
       </c>
       <c r="P68" t="n">
-        <v>4.346259938439426</v>
+        <v>4.34454134008564</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.7773944471011516</v>
+        <v>0.8070682754010212</v>
       </c>
       <c r="R68" t="n">
-        <v>0.03147385872425638</v>
+        <v>0.02930109276895657</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.4874330963895895</v>
+        <v>0.3800336424515129</v>
       </c>
       <c r="X68" t="n">
-        <v>0.001170820268360175</v>
+        <v>0.00128765350218419</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.3955701583959702</v>
+        <v>0.478623370989525</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.07562618598838711</v>
+        <v>0.070238467802064</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.469554711490021</v>
+        <v>0.3639139077140873</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003886918030831972</v>
+        <v>0.004256405875266298</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.7501050205864542</v>
+        <v>0.7727300283277616</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.007351066799483733</v>
+        <v>0.007010397346188644</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.6990502232559257</v>
+        <v>0.7084523352743886</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01237078195200235</v>
+        <v>0.01217600791725849</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.2480682877727682</v>
+        <v>0.4075440562341889</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.0007706699380659424</v>
+        <v>0.0006840805606788316</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7675,25 +7675,25 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1574541057329026</v>
+        <v>0.1010562527983535</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2051976353952231</v>
+        <v>0.172739751808195</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.332138796392004</v>
+        <v>4.331832199947486</v>
       </c>
       <c r="P69" t="n">
-        <v>4.301408134638223</v>
+        <v>4.292703203954071</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.971964674427934</v>
+        <v>0.9719051072258843</v>
       </c>
       <c r="R69" t="n">
-        <v>0.009813396774144721</v>
+        <v>0.009823816601049489</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9659052190880125</v>
+        <v>0.9674888851315926</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.0102295534510854</v>
+        <v>0.009989152775492493</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.4411317996927842</v>
+        <v>0.421250872053186</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.004747446593787831</v>
+        <v>0.004831150459858264</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8485263686173259</v>
+        <v>0.8495371887650479</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01576023512306844</v>
+        <v>0.01570756117380479</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9048103366427537</v>
+        <v>0.8973026549048775</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.009361233507072192</v>
+        <v>0.009723391915422036</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5187109619344599</v>
+        <v>0.5232367987441527</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004279493469577684</v>
+        <v>0.00425932468211163</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7779,25 +7779,25 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1548184556465437</v>
+        <v>0.09856641470047335</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2818792756835835</v>
+        <v>0.2502590843189873</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.393884558299479</v>
+        <v>4.407350183726711</v>
       </c>
       <c r="P70" t="n">
-        <v>4.357184331136191</v>
+        <v>4.347882044824999</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.9634331301343807</v>
+        <v>0.9647039526405778</v>
       </c>
       <c r="R70" t="n">
-        <v>0.009384186172923768</v>
+        <v>0.009219678113608272</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.9218597383630527</v>
+        <v>0.930672366284089</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01248178308088512</v>
+        <v>0.01175688821623678</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.9266093425400458</v>
+        <v>0.9240889124308331</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.00314246754918454</v>
+        <v>0.003195972393453977</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9388867506727477</v>
+        <v>0.9394095586078465</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.01122532965866805</v>
+        <v>0.01117721163068067</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8165577140446746</v>
+        <v>0.8126445252812737</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.0119960427732964</v>
+        <v>0.01212331732950899</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7678154532435362</v>
+        <v>0.7709015693836885</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.002175240515435225</v>
+        <v>0.002160735896618032</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7883,25 +7883,25 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3259372932035616</v>
+        <v>0.2690457232237147</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3494710513158307</v>
+        <v>0.336838240195768</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4.435983776929537</v>
+        <v>4.440211154547947</v>
       </c>
       <c r="P71" t="n">
-        <v>4.438832259590852</v>
+        <v>4.434133063266349</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9612297414408516</v>
+        <v>0.9604536770887365</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01075114070648084</v>
+        <v>0.01085821036214753</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9443525028410662</v>
+        <v>0.9442451431865208</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01403952725295853</v>
+        <v>0.01405306382722071</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.7407701143739539</v>
+        <v>0.7392837204760156</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004510071003479276</v>
+        <v>0.004522982631774063</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9068221352270809</v>
+        <v>0.9040248606392435</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.009735558561486977</v>
+        <v>0.009880612599764315</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.8424493369054318</v>
+        <v>0.8377069949097226</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01626850963332324</v>
+        <v>0.01651153890356238</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9318214537722059</v>
+        <v>0.9148053965080073</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.001020078583288297</v>
+        <v>0.001140291284495174</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -7987,25 +7987,25 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3247916833722452</v>
+        <v>0.2663662166319356</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4124836133381382</v>
+        <v>0.3913727454368565</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.528094939538367</v>
+        <v>4.543373877819946</v>
       </c>
       <c r="P72" t="n">
-        <v>4.500901129508024</v>
+        <v>4.497358585254873</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9568065162032868</v>
+        <v>0.9561162007394569</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01186831162414009</v>
+        <v>0.01196277498651009</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.8752494535083658</v>
+        <v>0.8830911649878134</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01475156371906827</v>
+        <v>0.01428040411402661</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.7983015200767887</v>
+        <v>0.7983088114153877</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.004946910977776198</v>
+        <v>0.004946821562305755</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.9507928490029101</v>
+        <v>0.9513887364444562</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006951589258913556</v>
+        <v>0.00690936997168195</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8448082008498964</v>
+        <v>0.8352209609270952</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.02029269727636362</v>
+        <v>0.02091011280270681</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.8996920647228908</v>
+        <v>0.895779428219033</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001444087145549991</v>
+        <v>0.001471981940328361</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8091,25 +8091,25 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.08004889403840529</v>
+        <v>0.04025276581779436</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08114029233833665</v>
+        <v>0.05531300081131266</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.341167164957967</v>
+        <v>4.33317781811658</v>
       </c>
       <c r="P73" t="n">
-        <v>4.328595964617172</v>
+        <v>4.324615292479916</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.99396379112802</v>
+        <v>0.9936981635915378</v>
       </c>
       <c r="R73" t="n">
-        <v>0.005166950074523005</v>
+        <v>0.005279413735731034</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9488331545213385</v>
+        <v>0.9483509134037805</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007766523935344358</v>
+        <v>0.007803037364015429</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.6127159826583171</v>
+        <v>0.6032814013844053</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001244029882727097</v>
+        <v>0.001259091540086999</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9644744443477057</v>
+        <v>0.9605307910978553</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.00632388875759245</v>
+        <v>0.006665657467192313</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8257202694666327</v>
+        <v>0.8208989497700422</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005104321817953664</v>
+        <v>0.005174443809277187</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>-0.07098117044569197</v>
+        <v>-0.09169008203468731</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.002361078299427955</v>
+        <v>0.002383796373284529</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8195,25 +8195,25 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08447253359755409</v>
+        <v>0.04324396691802901</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1625861730063674</v>
+        <v>0.1245895439735921</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.398896242437559</v>
+        <v>4.406169628486518</v>
       </c>
       <c r="P74" t="n">
-        <v>4.385988636559583</v>
+        <v>4.378776631394294</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9699037097953491</v>
+        <v>0.970957657729604</v>
       </c>
       <c r="R74" t="n">
-        <v>0.008218108308150958</v>
+        <v>0.008072930196269696</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.8562060852926054</v>
+        <v>0.8783227290839413</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.0090596866307125</v>
+        <v>0.008333887870798445</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.869576474525089</v>
+        <v>0.8632656661549138</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.001200122034053473</v>
+        <v>0.001228814227989385</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.876850564028685</v>
+        <v>0.8767150937823314</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01381821233874606</v>
+        <v>0.0138258105906954</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.8554129943330487</v>
+        <v>0.8542083210209618</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007688291201432815</v>
+        <v>0.007720253498077811</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.7046206404802793</v>
+        <v>0.7027191336525436</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.002028667602754216</v>
+        <v>0.002035186909081587</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8299,25 +8299,25 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2074205046880389</v>
+        <v>0.148541542472987</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2623019147692786</v>
+        <v>0.2363112797801991</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.197065933067138</v>
+        <v>4.193647807726889</v>
       </c>
       <c r="P75" t="n">
-        <v>4.282679100501563</v>
+        <v>4.27147382243856</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9696018005531949</v>
+        <v>0.9698381187427204</v>
       </c>
       <c r="R75" t="n">
-        <v>0.006885544761191853</v>
+        <v>0.006858728134933284</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.897979515517643</v>
+        <v>0.898979055058998</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.0114134118736275</v>
+        <v>0.011357363150794</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8477274891773257</v>
+        <v>0.8250969026943455</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002354569719791642</v>
+        <v>0.002523478159703676</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9214214556774813</v>
+        <v>0.9224145021196758</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.007357059870722868</v>
+        <v>0.007310424151293011</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8717190818218886</v>
+        <v>0.873575375278968</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.006793859121008478</v>
+        <v>0.006744524623290516</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9745856468645073</v>
+        <v>0.9756068556912962</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.0009802104018786931</v>
+        <v>0.000960314905190899</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8403,25 +8403,25 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02053193225236777</v>
+        <v>0.006369374504835267</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02513713782882519</v>
+        <v>0.01260698180666621</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>4.359073588567345</v>
+        <v>4.367107409264443</v>
       </c>
       <c r="P76" t="n">
-        <v>4.318198983664887</v>
+        <v>4.315908343694489</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9931707686457668</v>
+        <v>0.9932149855734457</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005185565888156932</v>
+        <v>0.005168751247521983</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.93675925131047</v>
+        <v>0.9425553369556715</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.007154829605321983</v>
+        <v>0.006819077666223203</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.8857275559793568</v>
+        <v>0.890662221592333</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.0009320009634825621</v>
+        <v>0.000911655436169076</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.9550001528143828</v>
+        <v>0.9528409311207018</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.008955009780613477</v>
+        <v>0.009167336141046728</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9887224260797791</v>
+        <v>0.9886453352739725</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.0008925362178492035</v>
+        <v>0.0008955816053299255</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.5683726274645649</v>
+        <v>0.5666913847295185</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001183821926602156</v>
+        <v>0.001186125249192821</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8507,25 +8507,25 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03782537579660925</v>
+        <v>0.014699157934358</v>
       </c>
       <c r="L77" t="n">
-        <v>0.0810297545649466</v>
+        <v>0.04739321233627111</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.268656568147811</v>
+        <v>4.273959898801073</v>
       </c>
       <c r="P77" t="n">
-        <v>4.245264030884003</v>
+        <v>4.239814421759615</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9704404554184087</v>
+        <v>0.9676120471436305</v>
       </c>
       <c r="R77" t="n">
-        <v>0.010309958460805</v>
+        <v>0.01079194679217427</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.5341118493949091</v>
+        <v>0.4533149481641617</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.01243572554487824</v>
+        <v>0.01347097083709219</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-0.582295642587052</v>
+        <v>-0.5704224762109016</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.00123012437861722</v>
+        <v>0.001225500409086378</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.8994691169864605</v>
+        <v>0.8876250599523513</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01374480870856579</v>
+        <v>0.01453194307933653</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.1670451556864152</v>
+        <v>0.1591295178557787</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01362937384140957</v>
+        <v>0.0136939812661015</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8761432611718952</v>
+        <v>0.8716583729562278</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0007975862080373175</v>
+        <v>0.0008118982089698126</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8611,25 +8611,25 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02723295651487582</v>
+        <v>0.009272849175076056</v>
       </c>
       <c r="L78" t="n">
-        <v>0.07672500489828572</v>
+        <v>0.04508385870996436</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.413573948301897</v>
+        <v>4.409715680264562</v>
       </c>
       <c r="P78" t="n">
-        <v>4.378228133504346</v>
+        <v>4.363262961524207</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9788302541138123</v>
+        <v>0.9766505938335436</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0105654922158259</v>
+        <v>0.01109608645566583</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.113949239312316</v>
+        <v>0.008862025101789239</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.01141110164775913</v>
+        <v>0.01206883447620343</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.7001184909678355</v>
+        <v>0.03827036897672387</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.0006405333600049204</v>
+        <v>0.00114707920877698</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8316565248884472</v>
+        <v>0.8080364544675139</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01687303880176016</v>
+        <v>0.01801791538146744</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.2331874867252572</v>
+        <v>-0.2395043446452791</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.01169910140580508</v>
+        <v>0.01172902682715175</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-1.732284807928274</v>
+        <v>-1.948612323383598</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.002440531274866863</v>
+        <v>0.002535305075741843</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8709,31 +8709,31 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2905655997701949</v>
+        <v>0.2305198222631793</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3193146508064549</v>
+        <v>0.2944371202333186</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.384688376048642</v>
+        <v>4.376078257807563</v>
       </c>
       <c r="P79" t="n">
-        <v>4.414698453051978</v>
+        <v>4.375318599479638</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9815531322839578</v>
+        <v>0.9806003627502462</v>
       </c>
       <c r="R79" t="n">
-        <v>0.01997891499838656</v>
+        <v>0.02048836898984656</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.9196623074491694</v>
+        <v>0.9150865299752611</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04402501071364347</v>
+        <v>0.0452614109088064</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.3516903794273151</v>
+        <v>0.3228512901398958</v>
       </c>
       <c r="X79" t="n">
-        <v>0.002266105277930717</v>
+        <v>0.002315959053874718</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9944839157949258</v>
+        <v>0.9970757539125313</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.005804358405889685</v>
+        <v>0.004226158066282786</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.5717723827826132</v>
+        <v>0.5385535671933877</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.004945920136422913</v>
+        <v>0.005134171950720905</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.9905129846447099</v>
+        <v>0.9910427757209966</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.003125066478163995</v>
+        <v>0.003036555220087941</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.8635593018077488</v>
+        <v>0.8492675055953676</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.009870716514327103</v>
+        <v>0.01037481007765759</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8817,31 +8817,31 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1624757209231998</v>
+        <v>0.1040560020796793</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2461187518334399</v>
+        <v>0.2182783969412355</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -8850,58 +8850,58 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.522041228329741</v>
+        <v>4.534282997629987</v>
       </c>
       <c r="P80" t="n">
-        <v>4.467278865581495</v>
+        <v>4.421241098153468</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9950344922844104</v>
+        <v>0.9952313022505453</v>
       </c>
       <c r="R80" t="n">
-        <v>0.009739621713846859</v>
+        <v>0.009544653286716316</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.983543339462064</v>
+        <v>0.9844496798822913</v>
       </c>
       <c r="U80" t="n">
-        <v>0.02037113569480754</v>
+        <v>0.01980222784462607</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.7897403724063593</v>
+        <v>0.7776461804996959</v>
       </c>
       <c r="X80" t="n">
-        <v>0.001226565936104548</v>
+        <v>0.001261348952731682</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.998808074989621</v>
+        <v>0.9995980590174857</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.002216587522656439</v>
+        <v>0.001287186754747993</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.8188547743234074</v>
+        <v>0.8050772905177508</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.00354124519466525</v>
+        <v>0.003673446946320415</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9865905088871375</v>
+        <v>0.9869243608870329</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.006142155035295631</v>
+        <v>0.006065213454383066</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.9619852004538377</v>
+        <v>0.9552178947138319</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.006387661091562089</v>
+        <v>0.006932945183578117</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8925,31 +8925,31 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2764885304045394</v>
+        <v>0.2134461779680059</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2568286701518031</v>
+        <v>0.2375282140764085</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -8958,54 +8958,54 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.543506980364979</v>
+        <v>4.524759522719838</v>
       </c>
       <c r="P81" t="n">
-        <v>4.588445430399664</v>
+        <v>4.590071296898006</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9918002331716165</v>
+        <v>0.9929697355870981</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01230600608964529</v>
+        <v>0.0113946818552248</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9763557255443277</v>
+        <v>0.9796800266109782</v>
       </c>
       <c r="U81" t="n">
-        <v>0.02304360710559567</v>
+        <v>0.02136235035036412</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9798635035761157</v>
+        <v>0.9853410814960082</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.009352291342153818</v>
+        <v>0.007979524970249126</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.7584733060188198</v>
+        <v>0.7219455128399838</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.002984266516061312</v>
+        <v>0.003201990150697815</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9655619273180496</v>
+        <v>0.9686619719390606</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.00595363571757831</v>
+        <v>0.005679350498711044</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.95989773350931</v>
+        <v>0.9631703893385645</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.009714119759908293</v>
+        <v>0.009309311395266535</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9029,31 +9029,31 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1873857992577476</v>
+        <v>0.1218395255999014</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1460921444003908</v>
+        <v>0.1528835923146188</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -9062,54 +9062,54 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>4.465612453484066</v>
+        <v>4.428003213484716</v>
       </c>
       <c r="P82" t="n">
-        <v>4.594217847754331</v>
+        <v>4.607661238421611</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9714687721076888</v>
+        <v>0.9771191400892514</v>
       </c>
       <c r="R82" t="n">
-        <v>0.02278585315533167</v>
+        <v>0.02040521776515144</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.9212106949275343</v>
+        <v>0.9376478997937704</v>
       </c>
       <c r="U82" t="n">
-        <v>0.04382375428874774</v>
+        <v>0.03898535453934408</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.949703879837641</v>
+        <v>0.9663091012677492</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.01501654052092727</v>
+        <v>0.01229019994216133</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>0.3185226822350521</v>
+        <v>0.3925274446539728</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.002422869185144003</v>
+        <v>0.002287534194789798</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.727865715427144</v>
+        <v>0.7407430315431258</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.01876771528507156</v>
+        <v>0.01831829274857542</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9670968389740151</v>
+        <v>0.9748677683562811</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.009584370547650798</v>
+        <v>0.008376456000287811</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9133,29 +9133,29 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1900383461359677</v>
+        <v>0.1274211052633809</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1856317839407446</v>
+        <v>0.159579580816888</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9164,54 +9164,54 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.580927191812872</v>
+        <v>4.571265893551568</v>
       </c>
       <c r="P83" t="n">
-        <v>4.571235328818583</v>
+        <v>4.569184206748631</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.9757404407581288</v>
+        <v>0.9748948897595334</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01864765519030246</v>
+        <v>0.01896984765791054</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9249197679761967</v>
+        <v>0.9217262055168085</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03551167767854237</v>
+        <v>0.03625906333452</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.9595537246507585</v>
+        <v>0.9578638381404871</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.009697847508947198</v>
+        <v>0.009898367399192004</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.2748498321819083</v>
+        <v>0.2525032063413997</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.009517551833251826</v>
+        <v>0.009663088427794949</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.9182823089316973</v>
+        <v>0.9166668486835614</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.0109736207374806</v>
+        <v>0.01108155748789063</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.87585213908829</v>
+        <v>0.8773929954311899</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.0131355844042773</v>
+        <v>0.01305381382718253</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9235,29 +9235,29 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1700871734410854</v>
+        <v>0.1109470721818669</v>
       </c>
       <c r="L84" t="n">
-        <v>0.230632505156051</v>
+        <v>0.2280459734205627</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9266,54 +9266,54 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.554043371413063</v>
+        <v>4.586544133145753</v>
       </c>
       <c r="P84" t="n">
-        <v>4.502795030495846</v>
+        <v>4.494727715007937</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9948887639565135</v>
+        <v>0.989965360901395</v>
       </c>
       <c r="R84" t="n">
-        <v>0.008395638170334084</v>
+        <v>0.01176363724853049</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.9920505547613314</v>
+        <v>0.9840583522801022</v>
       </c>
       <c r="U84" t="n">
-        <v>0.01192481307821156</v>
+        <v>0.01688689383730707</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9949403542211152</v>
+        <v>0.9913303141936692</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.00485279159118447</v>
+        <v>0.006352333109818426</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.26012084473174</v>
+        <v>0.08148706545592155</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.007787586637965768</v>
+        <v>0.008676911929500451</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.9283595202945578</v>
+        <v>0.8296384584276383</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.01103116421793434</v>
+        <v>0.01701092343445331</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9958075410492805</v>
+        <v>0.9983266529600704</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.002085631465824958</v>
+        <v>0.001317638205030274</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9337,29 +9337,31 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.234087371719241</v>
+        <v>0.2332956893959356</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2801892349008259</v>
+        <v>0.256747815056807</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -9368,54 +9370,54 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.488615918273156</v>
+        <v>4.323756426548535</v>
       </c>
       <c r="P85" t="n">
-        <v>4.486831162584882</v>
+        <v>4.388006981668388</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9818367647150974</v>
+        <v>0.9914277545313992</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01684313277916491</v>
+        <v>0.01171263100708735</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9556639838304075</v>
+        <v>0.972423715441383</v>
       </c>
       <c r="U85" t="n">
-        <v>0.02703215146365415</v>
+        <v>0.02343702495212267</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9930839207702232</v>
+        <v>0.9946332173138098</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.006408754386141705</v>
+        <v>0.005958471367620098</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>-0.17773506303766</v>
+        <v>0.5054935831298185</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.01695864834316122</v>
+        <v>0.005600797017149213</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.6562344056870232</v>
+        <v>0.9503707123380436</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.01893694208448688</v>
+        <v>0.006851009482500486</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9994565910971632</v>
+        <v>0.9650532100160338</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.0006653829039369449</v>
+        <v>0.00477764039449726</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9439,29 +9441,31 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1246919775437176</v>
+        <v>0.1064698714707798</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1551042893757214</v>
+        <v>0.1908591283697716</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -9470,54 +9474,54 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.567691173450372</v>
+        <v>4.52106968442537</v>
       </c>
       <c r="P86" t="n">
-        <v>4.512783918100642</v>
+        <v>4.434878396731823</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.9909039273174141</v>
+        <v>0.9930133210035428</v>
       </c>
       <c r="R86" t="n">
-        <v>0.01137490837087109</v>
+        <v>0.01039652552741771</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.9863386789774761</v>
+        <v>0.9824451100680783</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01624672726569851</v>
+        <v>0.0206057920671333</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9964264413668207</v>
+        <v>0.9988764993655422</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.003477268628531569</v>
+        <v>0.002131626476374783</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>-0.3971742526560873</v>
+        <v>0.7269071225521778</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.01769304384414355</v>
+        <v>0.00439255624001767</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.9870512751829403</v>
+        <v>0.9721423745242257</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.005817777186068403</v>
+        <v>0.008725374196155815</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.977272647402363</v>
+        <v>0.9853925344698127</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.004899472054219723</v>
+        <v>0.003983655592275062</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9541,29 +9545,31 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.183694725148222</v>
+        <v>0.1378578795676572</v>
       </c>
       <c r="L87" t="n">
-        <v>0.2688474743262207</v>
+        <v>0.1484317265455228</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -9572,54 +9578,54 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>4.672692369942369</v>
+        <v>4.414858197264242</v>
       </c>
       <c r="P87" t="n">
-        <v>4.61659166222085</v>
+        <v>4.605724310078727</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9489765942097669</v>
+        <v>0.9753564015939339</v>
       </c>
       <c r="R87" t="n">
-        <v>0.02532288468306964</v>
+        <v>0.02099288846594416</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.8878441276801524</v>
+        <v>0.9419432426356056</v>
       </c>
       <c r="U87" t="n">
-        <v>0.04342413674544995</v>
+        <v>0.03974457584153179</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.8462759144958198</v>
+        <v>0.970543666749637</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.02191344498156324</v>
+        <v>0.01177256762688585</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.624274520849071</v>
+        <v>0.6252208318606942</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.007184923430444914</v>
+        <v>0.002394947697601653</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.4004261644671419</v>
+        <v>0.7529426064998856</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.02735836512242576</v>
+        <v>0.0198625150682019</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9840845622868911</v>
+        <v>0.9714781129050715</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.006347003500815207</v>
+        <v>0.009221002876921184</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9643,29 +9649,31 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2274032847723464</v>
+        <v>0.1889560953604738</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1675068427290309</v>
+        <v>0.2442333571921136</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -9674,54 +9682,54 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.517087837474207</v>
+        <v>4.526684391662236</v>
       </c>
       <c r="P88" t="n">
-        <v>4.646604940518612</v>
+        <v>4.593178487559175</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9909630568523573</v>
+        <v>0.990858749080137</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01114552268937772</v>
+        <v>0.01286305915514072</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9736241675452526</v>
+        <v>0.9754526630564618</v>
       </c>
       <c r="U88" t="n">
-        <v>0.02046908389554157</v>
+        <v>0.02434378931209624</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9848870200707512</v>
+        <v>0.9819166785943552</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.006955664161586903</v>
+        <v>0.009147465401779176</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>0.5478493839436035</v>
+        <v>0.8219553884160457</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.004194451846699765</v>
+        <v>0.002586237765225376</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.9639096713033238</v>
+        <v>0.96776647700211</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.005662453394593703</v>
+        <v>0.005873490958696223</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.9498262460345144</v>
+        <v>0.9573154353942153</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.01020254457992885</v>
+        <v>0.01047896612145515</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9745,29 +9753,29 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3272038829542777</v>
+        <v>0.2890984316053696</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3219674696609041</v>
+        <v>0.2888791601221938</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -9776,54 +9784,54 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4.487315914632268</v>
+        <v>4.444533540889832</v>
       </c>
       <c r="P89" t="n">
-        <v>4.608123537931807</v>
+        <v>4.575040290169465</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9958059891449169</v>
+        <v>0.9940667227925103</v>
       </c>
       <c r="R89" t="n">
-        <v>0.007663827826780576</v>
+        <v>0.009115453592844944</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9944415435805271</v>
+        <v>0.9878612926964644</v>
       </c>
       <c r="U89" t="n">
-        <v>0.01018871889114236</v>
+        <v>0.01505666186784892</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.995533289421654</v>
+        <v>0.9980386557820786</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.005093219753805592</v>
+        <v>0.003375012752314473</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.7638270589650684</v>
+        <v>0.6691737361725032</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.004709665993263534</v>
+        <v>0.005574102992926246</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9804964205878667</v>
+        <v>0.9808665939001004</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.003393038729608771</v>
+        <v>0.003360684955265016</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9371144262296756</v>
+        <v>0.9348100001422941</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.01141169308650897</v>
+        <v>0.01161890122994571</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9849,27 +9857,29 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2282474838080587</v>
+        <v>0.4644377694824607</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4815095950712526</v>
+        <v>0.5368567785676415</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -9878,54 +9888,56 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4.491846084938333</v>
+        <v>4.563637114762271</v>
       </c>
       <c r="P90" t="n">
-        <v>4.281860044428253</v>
+        <v>4.29883651537904</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9854607249708324</v>
+        <v>0.9841480987197712</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01594450949846223</v>
+        <v>0.01494858636472264</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.9687393740684985</v>
+        <v>0.9648079656291003</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02863417809017151</v>
+        <v>0.02732140805483219</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
+      <c r="X90" t="n">
+        <v>5.204170427930421e-18</v>
+      </c>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9923311350084326</v>
+        <v>0.9900173881468745</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.01131281298188015</v>
+        <v>0.01085762481405565</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.7968267709119459</v>
+        <v>0.8676154488903312</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.005135468464758191</v>
+        <v>0.005657318858946709</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9880354695611064</v>
+        <v>0.947988722009905</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.0008331399577912225</v>
+        <v>0.0007529111167506019</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9875934251901958</v>
+        <v>0.9844096163769492</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.003650955881924697</v>
+        <v>0.003840207243528159</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>
